--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Zinc, Lead, Silver, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V2" t="n">
-        <v>49.01028</v>
+        <v>45.3192</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.00369999999999</v>
+        <v>-71.92023</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>45.3192</v>
+        <v>45.43568</v>
       </c>
       <c r="W3" t="n">
-        <v>-71.92023</v>
+        <v>-70.91788</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Jackson (Minerais Lac)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>49.83681</v>
+        <v>45.52972</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.57877999999999</v>
+        <v>-71.65783999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>46W</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Gold, Arsenic, Silver, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.82919</v>
+        <v>48.29961</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.58076</v>
+        <v>-67.12675</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,12 +897,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Zinc, Silver, Molybdenum, Cadmium, Barium</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -913,12 +913,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>871 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>45.40941</v>
+        <v>48.33048</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.81791</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -960,11 +960,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H-1456-009</t>
+          <t>Pari (Zone 30)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 8.47 g/t, Cu 0.303%, Ag 9.60 g/t, As 0.565%</t>
+          <t>Au 13.50 g/t, Cu 0.57%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>50.62126</v>
+        <v>53.5301</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.35012</v>
+        <v>-76.55025999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4342</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>Filion</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Gold, Silver</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>45.32298</v>
+        <v>46.61092</v>
       </c>
       <c r="W8" t="n">
-        <v>-71.90649999999999</v>
+        <v>-75.97769</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rochelom</t>
+          <t>Hall (et Extension)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,17 +1126,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>4 kt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
+          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>49.77064</v>
+        <v>46.04018</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.01858</v>
+        <v>-71.28144</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Goshawk</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Lead, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>61.56992</v>
+        <v>45.44349</v>
       </c>
       <c r="W10" t="n">
-        <v>-75.20258</v>
+        <v>-70.91244</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lac Dunphy</t>
+          <t>Bourdon</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
+          <t>Au 21.80 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>56.05097</v>
+        <v>53.62313</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.71257</v>
+        <v>-71.96111999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1350,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Dead Mouse extension</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Au 18.36 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>56.40258</v>
+        <v>53.61747</v>
       </c>
       <c r="W12" t="n">
-        <v>-67.9023</v>
+        <v>-71.97382</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chibtown</t>
+          <t>de l'Ours</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
+          <t>Au 27.00 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>56.39152</v>
+        <v>53.61441</v>
       </c>
       <c r="W13" t="n">
-        <v>-67.87103</v>
+        <v>-71.97407</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Projet 70-Landome</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Silver, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>49.84595</v>
+        <v>48.46123</v>
       </c>
       <c r="W14" t="n">
-        <v>-70.57626</v>
+        <v>-77.95265999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>50.85296</v>
+        <v>45.40513</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.47398</v>
+        <v>-70.9376</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Transfiguration (Labrador Expl.)</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Lead</t>
+          <t>Copper, Silver, Zinc, Lead, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 3.08%, Pb 21.1%, Zn 8.52%, Ag 97.37 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>47.93876</v>
+        <v>48.37403</v>
       </c>
       <c r="W16" t="n">
-        <v>-68.75702</v>
+        <v>-65.44089</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4162</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Transfiguration: Zone E3</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Copper, Gold, Zinc, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>47.9394</v>
+        <v>45.42257</v>
       </c>
       <c r="W17" t="n">
-        <v>-68.76391</v>
+        <v>-70.92541</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,17 +1828,17 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Silver, Gold, Lead, Copper</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 5.00 g/t</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>50.8451</v>
+        <v>45.42731</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.45574000000001</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4236</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sond. PIK20-001</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 3.38%, Ag 25.50 g/t, Zn 0.147%</t>
+          <t>Au 32.73 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>53.53043</v>
+        <v>53.51886</v>
       </c>
       <c r="W19" t="n">
-        <v>-74.33239</v>
+        <v>-76.60854</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66837</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gémini - A sud</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Lead, Gold, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 3.43 g/t, Ag 6.20 g/t</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.42712</v>
+        <v>45.45582</v>
       </c>
       <c r="W20" t="n">
-        <v>-79.27181</v>
+        <v>-70.90786</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4008</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gémini - A Nord</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.43645</v>
+        <v>45.43447</v>
       </c>
       <c r="W21" t="n">
-        <v>-79.26394999999999</v>
+        <v>-70.9088</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gémini - B (Zone à cuivre)</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold</t>
+          <t>Gold, Uranium, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 3.78%, Ag 130.00 g/t, Au 1.38 g/t, Zn 3.87%</t>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.38069</v>
+        <v>56.43038</v>
       </c>
       <c r="W22" t="n">
-        <v>-79.25882</v>
+        <v>-68.09914000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4012</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monts Peacock-Sud</t>
+          <t>Train No 4 (Lac Crabe)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Copper, Nickel, Silver</t>
+          <t>Copper, Uranium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 2.77%, Au 1.06 g/t, Ni 0.73%, Ag 14.10 g/t</t>
+          <t>Cu 3.71%, U 0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>49.20789</v>
+        <v>56.39584</v>
       </c>
       <c r="W23" t="n">
-        <v>-78.41656999999999</v>
+        <v>-68.39176999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4030</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claims Peacock</t>
+          <t>SGR-09</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Uranium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 7.50 g/t</t>
+          <t>Au 3.31 g/t, U 0.11%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>49.16788</v>
+        <v>56.43951</v>
       </c>
       <c r="W24" t="n">
-        <v>-78.43522</v>
+        <v>-68.10245999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vior-Zone Nord</t>
+          <t>Lullwitz-Kaeppeli</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Silver</t>
+          <t>Gold, Ir, Gallium, Zr</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 5.55 g/t, Ag 2.00 g/t, Cu 0.06%, Zn 0.17%</t>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>49.01288</v>
+        <v>47.76432</v>
       </c>
       <c r="W25" t="n">
-        <v>-78.48756</v>
+        <v>-70.46635000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gold Fields</t>
+          <t>Lac Marcaut</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 19.04 g/t</t>
+          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>49.09287</v>
+        <v>51.08117</v>
       </c>
       <c r="W26" t="n">
-        <v>-78.42254</v>
+        <v>-77.6185</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D-91-01 (Option Dejour)</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>49.02527</v>
+        <v>58.81627</v>
       </c>
       <c r="W27" t="n">
-        <v>-78.38705</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G-H-2-79 (Hudbay Mining)</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 3.26%, Ni 1.12%</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>51.50451</v>
+        <v>58.81552</v>
       </c>
       <c r="W28" t="n">
-        <v>-67.92737</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Iron, Nickel, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Au 251.66 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.63941</v>
+        <v>53.53343</v>
       </c>
       <c r="W29" t="n">
-        <v>-76.90893</v>
+        <v>-76.53331</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Zone 35-L11W</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Au 35.31 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>49.59836</v>
+        <v>53.52296</v>
       </c>
       <c r="W30" t="n">
-        <v>-76.92194000000001</v>
+        <v>-76.59889</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ouest-Goldfield</t>
+          <t>As</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 3.75 g/t, Ag 1.10 g/t</t>
+          <t>Au 36.38 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.06302</v>
+        <v>53.52499</v>
       </c>
       <c r="W31" t="n">
-        <v>-78.47202</v>
+        <v>-76.58275</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4039</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
         </is>
       </c>
     </row>
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CaribGold 99-07</t>
+          <t>TRH-96-07</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Platinum, Palladium, Egp, Nickel, Zinc, Chromium, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
+          <t>Au 19.59 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>50.75408</v>
+        <v>53.52311</v>
       </c>
       <c r="W32" t="n">
-        <v>-76.84898</v>
+        <v>-76.61015</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Labrie</t>
+          <t>Zone 32 (Mico-Milan)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 48.80 g/t</t>
+          <t>Au 72.69 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>48.95238</v>
+        <v>53.52891</v>
       </c>
       <c r="W33" t="n">
-        <v>-76.4864</v>
+        <v>-76.56541</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4277</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
         </is>
       </c>
     </row>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bloc Est</t>
+          <t>Zone 32 (Tonalite-Zone Veine)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>50.84188</v>
+        <v>53.5291</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.39422</v>
+        <v>-76.56155</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4235</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Midrim</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Egp, Nickel, Copper, Silver</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 3.54%, Ni 2.94%, EGP 0.000422%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>47.47178</v>
+        <v>49.82919</v>
       </c>
       <c r="W35" t="n">
-        <v>-79.23383</v>
+        <v>-70.58076</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4692</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lac De Maurès-Est</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 12.6%, Au 5.79 g/t, Ag 50.00 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>50.65811</v>
+        <v>49.83681</v>
       </c>
       <c r="W36" t="n">
-        <v>-74.36593999999999</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4292</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lac Odon</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Silver</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 19.20 g/t, Cu 3.51%, Mo 0.96%, Ag 8.40 g/t</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>50.68338</v>
+        <v>48.70382</v>
       </c>
       <c r="W37" t="n">
-        <v>-74.36037</v>
+        <v>-78.25041</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4293</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lac Rocher</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,17 +3388,17 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platinum, Egp, Copper, Nickel, Palladium, Cobalt, Gold</t>
+          <t>Silver, Lead, Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>50.58471</v>
+        <v>47.86378</v>
       </c>
       <c r="W38" t="n">
-        <v>-76.34242</v>
+        <v>-67.38485</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AT-32-91</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>48.89509</v>
+        <v>47.99637</v>
       </c>
       <c r="W39" t="n">
-        <v>-78.79843</v>
+        <v>-67.11127</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 26.78 g/t</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>50.8534</v>
+        <v>50.31401</v>
       </c>
       <c r="W40" t="n">
-        <v>-76.53675</v>
+        <v>-62.73908</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4238</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H-1451-032</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>50.79734</v>
+        <v>46.27176</v>
       </c>
       <c r="W41" t="n">
-        <v>-76.70574000000001</v>
+        <v>-71.28612</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold, Silver, Nickel, Chromium, Zinc</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>48.31932</v>
+        <v>46.26109</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.9713</v>
+        <v>-71.22866</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -3768,22 +3768,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>48.37403</v>
+        <v>45.03676</v>
       </c>
       <c r="W43" t="n">
-        <v>-65.44089</v>
+        <v>-72.77243</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>47.26406</v>
+        <v>48.57696</v>
       </c>
       <c r="W44" t="n">
-        <v>-79.40157000000001</v>
+        <v>-78.14164</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>45.43568</v>
+        <v>48.71945</v>
       </c>
       <c r="W45" t="n">
-        <v>-70.91788</v>
+        <v>-78.33144</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>As-3</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Au 6.38 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>45.43447</v>
+        <v>53.52425</v>
       </c>
       <c r="W46" t="n">
-        <v>-70.9088</v>
+        <v>-76.57341</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fraser (Zones 3, 4 &amp; 5)</t>
+          <t>Zone 32</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
+          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>48.32289</v>
+        <v>53.52649</v>
       </c>
       <c r="W47" t="n">
-        <v>-67.05</v>
+        <v>-76.56404999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>Pari</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Au 730.77 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>48.33048</v>
+        <v>53.53306</v>
       </c>
       <c r="W48" t="n">
-        <v>-67.01985999999999</v>
+        <v>-76.55201</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>46W</t>
+          <t>Brèche</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
+          <t>Au 8.56 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>48.29961</v>
+        <v>53.53187</v>
       </c>
       <c r="W49" t="n">
-        <v>-67.12675</v>
+        <v>-76.54353</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>45.44349</v>
+        <v>49.84595</v>
       </c>
       <c r="W50" t="n">
-        <v>-70.91244</v>
+        <v>-70.57626</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -4470,22 +4470,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Guettard-Nord</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>50.01478</v>
+        <v>46.265</v>
       </c>
       <c r="W52" t="n">
-        <v>-75.39858</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lac Marcaut</t>
+          <t>Guettard-Nord</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
+          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4600,23 +4600,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U53" t="n">
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>51.08117</v>
+        <v>50.01478</v>
       </c>
       <c r="W53" t="n">
-        <v>-77.6185</v>
+        <v>-75.39858</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lullwitz-Kaeppeli</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ir, Gold, Zr, Gallium</t>
+          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>47.76432</v>
+        <v>46.26265</v>
       </c>
       <c r="W54" t="n">
-        <v>-70.46635000000001</v>
+        <v>-71.21769</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Obamska</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,12 +4714,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 9.50 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>50.8353</v>
+        <v>46.26532</v>
       </c>
       <c r="W55" t="n">
-        <v>-78.66648000000001</v>
+        <v>-71.28788</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Guimond</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Gold, Bismuth, Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>47.37388</v>
+        <v>47.43121</v>
       </c>
       <c r="W56" t="n">
-        <v>-79.13840999999999</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pike</t>
+          <t>Lartic Est</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Copper, Mg, Silver</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 12.3%, Au 2.54 g/t, Ni 0.28%, Ag 9.60 g/t</t>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T57" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U57" t="n">
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>47.32819</v>
+        <v>48.173</v>
       </c>
       <c r="W57" t="n">
-        <v>-79.07715</v>
+        <v>-78.14212999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4703</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Silver, Molybdenum, Copper, Bismuth, Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>47.43121</v>
+        <v>55.15269</v>
       </c>
       <c r="W58" t="n">
-        <v>-79.32868999999999</v>
+        <v>-66.35399</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zullo</t>
+          <t>Lac Retty - Lac Bleu</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,12 +5026,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Copper</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Niobium, Cobalt</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Cu 3.35%, Ni 2.7%, Au 1.35 g/t</t>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>47.43373</v>
+        <v>55.22879</v>
       </c>
       <c r="W59" t="n">
-        <v>-79.24794</v>
+        <v>-66.12246</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4696</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gémini - B (Amas SF zincifère)</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,12 +5104,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lead, Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold, Silver</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Au 2.59 g/t, Cu 1.8%, Ag 118.80 g/t, Zn 2.98%, Pb 2.29%</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>49.38378</v>
+        <v>55.23261</v>
       </c>
       <c r="W60" t="n">
-        <v>-79.25754000000001</v>
+        <v>-66.16073</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4004</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Brisebois</t>
+          <t>Sond. SER-21-040</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 27.97 g/t, Ag 5.90 g/t</t>
+          <t>Au 8.71 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>47.35141</v>
+        <v>53.08409</v>
       </c>
       <c r="W61" t="n">
-        <v>-79.04821</v>
+        <v>-77.20562</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4705</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Sond. DDH-20-2023</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Nickel, Copper, Iron, Cobalt</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>53.56991</v>
+        <v>46.36809</v>
       </c>
       <c r="W62" t="n">
-        <v>-77.31073000000001</v>
+        <v>-73.97731</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Meilleur (Chess Uranium)</t>
+          <t>Boulder Shear (Cuvier-Est)</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold</t>
+          <t>Gold, Zinc, Arsenic, Copper</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
+          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T63" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U63" t="n">
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>45.6921</v>
+        <v>49.9399</v>
       </c>
       <c r="W63" t="n">
-        <v>-76.64127999999999</v>
+        <v>-74.70344</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>Lac Barlow</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,14 +5467,14 @@
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>47.68996</v>
+        <v>49.94431</v>
       </c>
       <c r="W64" t="n">
-        <v>-76.66074999999999</v>
+        <v>-74.71456000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kogaluc 4</t>
+          <t>Sond. PLP24-019</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,12 +5494,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth, Gold</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Au 5.60 g/t</t>
+          <t>Au 4.76 g/t, Bi 0.1%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5545,14 +5545,14 @@
         <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>58.81552</v>
+        <v>52.59612</v>
       </c>
       <c r="W65" t="n">
-        <v>-74.68685000000001</v>
+        <v>-77.37366</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lac Rivon-Ouest</t>
+          <t>Sond. K2-22-10</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zinc, Molybdenum, Gold, Silver, Copper</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
+          <t>Au 3.64 g/t, Zn 0.55%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>51.72313</v>
+        <v>52.28963</v>
       </c>
       <c r="W66" t="n">
-        <v>-72.79697</v>
+        <v>-77.78149999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sond. VER-21-06</t>
+          <t>Kan</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Silver, Copper</t>
+          <t>Gold, Zinc, Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Au 2.61 g/t, Zn 1.57%, Cu 0.321%, Ag 11.50 g/t</t>
+          <t>Au 6.72 g/t, Ag 390.00 g/t, Zn 17.4%, Pb 9.04%, Cu 0.115%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5701,14 +5701,14 @@
         <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>51.03789</v>
+        <v>57.4579</v>
       </c>
       <c r="W67" t="n">
-        <v>-77.71702000000001</v>
+        <v>-69.21342</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=65174</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3769</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rivière Pontois</t>
+          <t>Fenton 98-18</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Gold, Arsenic, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
+          <t>Au 5.47 g/t</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5779,14 +5779,14 @@
         <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>53.51426</v>
+        <v>49.51092</v>
       </c>
       <c r="W68" t="n">
-        <v>-74.51608</v>
+        <v>-75.36535000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>LA-93-04</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5806,12 +5806,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 36.07 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5857,14 +5857,14 @@
         <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>45.03676</v>
+        <v>49.55796</v>
       </c>
       <c r="W69" t="n">
-        <v>-72.77243</v>
+        <v>-75.37448000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Perch River</t>
+          <t>Sond. LF-93-03</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,12 +5884,12 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Cu 9.06%, Ag 19.20 g/t</t>
+          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5935,14 +5935,14 @@
         <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>50.33998</v>
+        <v>49.5436</v>
       </c>
       <c r="W70" t="n">
-        <v>-73.71023</v>
+        <v>-75.41676</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Rosembaum</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>46.26532</v>
+        <v>49.50469</v>
       </c>
       <c r="W71" t="n">
-        <v>-71.28788</v>
+        <v>-75.32402999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Copper, Silver, Manganese, Zinc</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T72" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U72" t="n">
         <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>46.26265</v>
+        <v>46.00535</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.21769</v>
+        <v>-71.70357</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Train No 4 (Lac Crabe)</t>
+          <t>Lepage No 2</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Gold, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Cu 3.71%, U 0.07%</t>
+          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>56.39584</v>
+        <v>48.33322</v>
       </c>
       <c r="W73" t="n">
-        <v>-68.39176999999999</v>
+        <v>-66.99834</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SGR-09</t>
+          <t>Lac Mina-Est</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Uranium, Gold</t>
+          <t>Gold, Zinc, Copper, Silver, Nickel</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
+          <t>Au 2.63 g/t, Cu 1.35%, Zn 1.57%, Ag 6.90 g/t, Ni 0.02%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6247,14 +6247,14 @@
         <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>56.43951</v>
+        <v>49.5435</v>
       </c>
       <c r="W74" t="n">
-        <v>-68.10245999999999</v>
+        <v>-75.32167</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3592</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lac Mina-Guercheville</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,12 +6274,12 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Uranium, Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
+          <t>Au 20.57 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6325,14 +6325,14 @@
         <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>56.43038</v>
+        <v>49.54166</v>
       </c>
       <c r="W75" t="n">
-        <v>-68.09914000000001</v>
+        <v>-75.33825</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3591</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Fenton-Sud</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Lead, Silver</t>
+          <t>Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Au 53.08 g/t, Ag 53.00 g/t, Zn 1.96%, Cu 0.23%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6403,14 +6403,14 @@
         <v>55</v>
       </c>
       <c r="V76" t="n">
-        <v>52.20175</v>
+        <v>49.51684</v>
       </c>
       <c r="W76" t="n">
-        <v>-70.89798</v>
+        <v>-75.36571000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3589</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>Lac Lapointe-SE</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6430,12 +6430,12 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Au 3.12 g/t, Cu 1.05%, Ag 3.70 g/t</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6472,23 +6472,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U77" t="n">
         <v>55</v>
       </c>
       <c r="V77" t="n">
-        <v>58.81627</v>
+        <v>49.5341</v>
       </c>
       <c r="W77" t="n">
-        <v>-74.70458000000001</v>
+        <v>-75.44531000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3587</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Robidoux-appalaches</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,14 +6559,14 @@
         <v>55</v>
       </c>
       <c r="V78" t="n">
-        <v>46.26109</v>
+        <v>48.35381</v>
       </c>
       <c r="W78" t="n">
-        <v>-71.22866</v>
+        <v>-65.56434</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Pyrite Falls</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Au 22.20 g/t, Ag 11.00 g/t</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6637,638 +6637,14 @@
         <v>55</v>
       </c>
       <c r="V79" t="n">
-        <v>46.27176</v>
+        <v>57.44105</v>
       </c>
       <c r="W79" t="n">
-        <v>-71.28612</v>
+        <v>-69.21915</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Copper, Uranium, Silver</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>13</v>
-      </c>
-      <c r="T80" t="n">
-        <v>325</v>
-      </c>
-      <c r="U80" t="n">
-        <v>55</v>
-      </c>
-      <c r="V80" t="n">
-        <v>46.265</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-71.21259999999999</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Lac Barlow</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>13</v>
-      </c>
-      <c r="T81" t="n">
-        <v>325</v>
-      </c>
-      <c r="U81" t="n">
-        <v>55</v>
-      </c>
-      <c r="V81" t="n">
-        <v>49.94431</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-74.71456000000001</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Sond. K2-22-10</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Gold, Zinc</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Au 3.64 g/t, Zn 0.55%</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>12</v>
-      </c>
-      <c r="T82" t="n">
-        <v>300</v>
-      </c>
-      <c r="U82" t="n">
-        <v>55</v>
-      </c>
-      <c r="V82" t="n">
-        <v>52.28963</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-77.78149999999999</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Lartic Est</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="n">
-        <v>250</v>
-      </c>
-      <c r="U83" t="n">
-        <v>55</v>
-      </c>
-      <c r="V83" t="n">
-        <v>48.173</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-78.14212999999999</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Ruisseau Basket</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>325</v>
-      </c>
-      <c r="U84" t="n">
-        <v>55</v>
-      </c>
-      <c r="V84" t="n">
-        <v>48.09296</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-66.78681</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Boulder Shear (Cuvier-Est)</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Zinc, Gold, Copper, Arsenic</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>12</v>
-      </c>
-      <c r="T85" t="n">
-        <v>300</v>
-      </c>
-      <c r="U85" t="n">
-        <v>55</v>
-      </c>
-      <c r="V85" t="n">
-        <v>49.9399</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-74.70344</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deux Orignaux</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Au 3.60 g/t</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>13</v>
-      </c>
-      <c r="T86" t="n">
-        <v>325</v>
-      </c>
-      <c r="U86" t="n">
-        <v>55</v>
-      </c>
-      <c r="V86" t="n">
-        <v>49.88535</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-75.3155</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66976</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Amaruk</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>9</v>
-      </c>
-      <c r="T87" t="n">
-        <v>225</v>
-      </c>
-      <c r="U87" t="n">
-        <v>55</v>
-      </c>
-      <c r="V87" t="n">
-        <v>59.60263</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-74.86282</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3770</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:X87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>45.3192</v>
+        <v>49.01028</v>
       </c>
       <c r="W2" t="n">
-        <v>-71.92023</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="V3" t="n">
-        <v>45.43568</v>
+        <v>45.3192</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.91788</v>
+        <v>-71.92023</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jackson (Minerais Lac)</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>45.52972</v>
+        <v>49.83681</v>
       </c>
       <c r="W4" t="n">
-        <v>-71.65783999999999</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46W</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver, Zinc</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>48.29961</v>
+        <v>49.82919</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.12675</v>
+        <v>-70.58076</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>Mine Aldermac Moulton Hill</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,12 +897,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Copper, Lead, Zinc, Silver, Molybdenum, Cadmium, Barium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -913,12 +913,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>871 kt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>48.33048</v>
+        <v>45.40941</v>
       </c>
       <c r="W6" t="n">
-        <v>-67.01985999999999</v>
+        <v>-71.81791</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
         </is>
       </c>
     </row>
@@ -960,11 +960,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pari (Zone 30)</t>
+          <t>H-1456-009</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Arsenic, Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 13.50 g/t, Cu 0.57%</t>
+          <t>Au 8.47 g/t, Cu 0.303%, Ag 9.60 g/t, As 0.565%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>53.5301</v>
+        <v>50.62126</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.55025999999999</v>
+        <v>-77.35012</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4342</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Filion</t>
+          <t>Mine Capelton (Albert)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Copper, Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>300 kt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
+          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>46.61092</v>
+        <v>45.32298</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.97769</v>
+        <v>-71.90649999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hall (et Extension)</t>
+          <t>Rochelom</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,17 +1126,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chromium, Egp, Nickel, Platinum, Rh, Palladium</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ni 4.2%, Pt 2.60 g/t, Cr 56%, Cr2O3 3.96%, EGP 0.000264%</t>
+          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04018</v>
+        <v>49.77064</v>
       </c>
       <c r="W9" t="n">
-        <v>-71.28144</v>
+        <v>-76.01858</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5557</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Goshawk</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Zinc, Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>45.44349</v>
+        <v>61.56992</v>
       </c>
       <c r="W10" t="n">
-        <v>-70.91244</v>
+        <v>-75.20258</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bourdon</t>
+          <t>Lac Dunphy</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 21.80 g/t</t>
+          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>53.62313</v>
+        <v>56.05097</v>
       </c>
       <c r="W11" t="n">
-        <v>-71.96111999999999</v>
+        <v>-67.71257</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1350,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dead Mouse extension</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 18.36 g/t</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.61747</v>
+        <v>56.40258</v>
       </c>
       <c r="W12" t="n">
-        <v>-71.97382</v>
+        <v>-67.9023</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>de l'Ours</t>
+          <t>Chibtown</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 27.00 g/t</t>
+          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.61441</v>
+        <v>56.39152</v>
       </c>
       <c r="W13" t="n">
-        <v>-71.97407</v>
+        <v>-67.87103</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Projet 70-Landome</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Gold</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>48.46123</v>
+        <v>49.84595</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.95265999999999</v>
+        <v>-70.57626</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>H-1429-046</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.40513</v>
+        <v>50.85296</v>
       </c>
       <c r="W15" t="n">
-        <v>-70.9376</v>
+        <v>-76.47398</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Transfiguration (Labrador Expl.)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Lead, Gold</t>
+          <t>Copper, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 3.08%, Pb 21.1%, Zn 8.52%, Ag 97.37 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>48.37403</v>
+        <v>47.93876</v>
       </c>
       <c r="W16" t="n">
-        <v>-65.44089</v>
+        <v>-68.75702</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4162</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Transfiguration: Zone E3</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Lead, Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>45.42257</v>
+        <v>47.9394</v>
       </c>
       <c r="W17" t="n">
-        <v>-70.92541</v>
+        <v>-68.76391</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,17 +1828,17 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Lead, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 5.00 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.42731</v>
+        <v>50.8451</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.92610999999999</v>
+        <v>-76.45574000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4236</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>Sond. PIK20-001</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 32.73 g/t</t>
+          <t>Cu 3.38%, Ag 25.50 g/t, Zn 0.147%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>53.51886</v>
+        <v>53.53043</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.60854</v>
+        <v>-74.33239</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66837</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Gémini - A sud</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Gold, Copper, Zinc, Silver</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Au 3.43 g/t, Ag 6.20 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.45582</v>
+        <v>49.42712</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.90786</v>
+        <v>-79.27181</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4008</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Gémini - A Nord</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead, Gold</t>
+          <t>Zinc, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>45.43447</v>
+        <v>49.43645</v>
       </c>
       <c r="W21" t="n">
-        <v>-70.9088</v>
+        <v>-79.26394999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Gémini - B (Zone à cuivre)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Uranium, Copper</t>
+          <t>Zinc, Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
+          <t>Cu 3.78%, Ag 130.00 g/t, Au 1.38 g/t, Zn 3.87%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>56.43038</v>
+        <v>49.38069</v>
       </c>
       <c r="W22" t="n">
-        <v>-68.09914000000001</v>
+        <v>-79.25882</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4012</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Train No 4 (Lac Crabe)</t>
+          <t>Monts Peacock-Sud</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Uranium</t>
+          <t>Gold, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 3.71%, U 0.07%</t>
+          <t>Cu 2.77%, Au 1.06 g/t, Ni 0.73%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>56.39584</v>
+        <v>49.20789</v>
       </c>
       <c r="W23" t="n">
-        <v>-68.39176999999999</v>
+        <v>-78.41656999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4030</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SGR-09</t>
+          <t>Claims Peacock</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
+          <t>Au 7.50 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>56.43951</v>
+        <v>49.16788</v>
       </c>
       <c r="W24" t="n">
-        <v>-68.10245999999999</v>
+        <v>-78.43522</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4032</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lullwitz-Kaeppeli</t>
+          <t>Vior-Zone Nord</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Ir, Gallium, Zr</t>
+          <t>Gold, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
+          <t>Au 5.55 g/t, Ag 2.00 g/t, Cu 0.06%, Zn 0.17%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>47.76432</v>
+        <v>49.01288</v>
       </c>
       <c r="W25" t="n">
-        <v>-70.46635000000001</v>
+        <v>-78.48756</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4034</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lac Marcaut</t>
+          <t>Gold Fields</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
+          <t>Au 19.04 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>51.08117</v>
+        <v>49.09287</v>
       </c>
       <c r="W26" t="n">
-        <v>-77.6185</v>
+        <v>-78.42254</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>D-91-01 (Option Dejour)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U27" t="n">
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>58.81627</v>
+        <v>49.02527</v>
       </c>
       <c r="W27" t="n">
-        <v>-74.70458000000001</v>
+        <v>-78.38705</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kogaluc 4</t>
+          <t>G-H-2-79 (Hudbay Mining)</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 5.60 g/t</t>
+          <t>Cu 3.26%, Ni 1.12%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>58.81552</v>
+        <v>51.50451</v>
       </c>
       <c r="W28" t="n">
-        <v>-74.68685000000001</v>
+        <v>-67.92737</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Iron, Nickel, Copper</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 251.66 g/t</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>53.53343</v>
+        <v>49.63941</v>
       </c>
       <c r="W29" t="n">
-        <v>-76.53331</v>
+        <v>-76.90893</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zone 35-L11W</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 35.31 g/t</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>53.52296</v>
+        <v>49.59836</v>
       </c>
       <c r="W30" t="n">
-        <v>-76.59889</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Ouest-Goldfield</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 36.38 g/t</t>
+          <t>Au 3.75 g/t, Ag 1.10 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>53.52499</v>
+        <v>49.06302</v>
       </c>
       <c r="W31" t="n">
-        <v>-76.58275</v>
+        <v>-78.47202</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4039</t>
         </is>
       </c>
     </row>
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRH-96-07</t>
+          <t>CaribGold 99-07</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth, Gold, Platinum, Palladium, Egp, Nickel, Zinc, Chromium, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 19.59 g/t</t>
+          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>53.52311</v>
+        <v>50.75408</v>
       </c>
       <c r="W32" t="n">
-        <v>-76.61015</v>
+        <v>-76.84898</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zone 32 (Mico-Milan)</t>
+          <t>Lac Labrie</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 72.69 g/t</t>
+          <t>Au 48.80 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>53.52891</v>
+        <v>48.95238</v>
       </c>
       <c r="W33" t="n">
-        <v>-76.56541</v>
+        <v>-76.4864</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4277</t>
         </is>
       </c>
     </row>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zone 32 (Tonalite-Zone Veine)</t>
+          <t>Bloc Est</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.5291</v>
+        <v>50.84188</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.56155</v>
+        <v>-76.39422</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4235</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Midrim</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Egp, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 3.54%, Ni 2.94%, EGP 0.000422%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.82919</v>
+        <v>47.47178</v>
       </c>
       <c r="W35" t="n">
-        <v>-70.58076</v>
+        <v>-79.23383</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4692</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Lac De Maurès-Est</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum, Egp, Palladium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Cu 12.6%, Au 5.79 g/t, Ag 50.00 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>49.83681</v>
+        <v>50.65811</v>
       </c>
       <c r="W36" t="n">
-        <v>-70.57877999999999</v>
+        <v>-74.36593999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4292</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Lac Odon</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold, Molybdenum, Copper, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 19.20 g/t, Cu 3.51%, Mo 0.96%, Ag 8.40 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>48.70382</v>
+        <v>50.68338</v>
       </c>
       <c r="W37" t="n">
-        <v>-78.25041</v>
+        <v>-74.36037</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4293</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Lac Rocher</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,17 +3388,17 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Gold, Zinc</t>
+          <t>Platinum, Egp, Copper, Nickel, Palladium, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>47.86378</v>
+        <v>50.58471</v>
       </c>
       <c r="W38" t="n">
-        <v>-67.38485</v>
+        <v>-76.34242</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>AT-32-91</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Lead, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Au 5.09 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>47.99637</v>
+        <v>48.89509</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.11127</v>
+        <v>-78.79843</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>Lightning</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Au 26.78 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>50.31401</v>
+        <v>50.8534</v>
       </c>
       <c r="W40" t="n">
-        <v>-62.73908</v>
+        <v>-76.53675</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4238</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>H-1451-032</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>46.27176</v>
+        <v>50.79734</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.28612</v>
+        <v>-76.70574000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Nickel, Chromium, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>46.26109</v>
+        <v>48.31932</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.22866</v>
+        <v>-64.9713</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -3768,22 +3768,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>45.03676</v>
+        <v>48.37403</v>
       </c>
       <c r="W43" t="n">
-        <v>-72.77243</v>
+        <v>-65.44089</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>48.57696</v>
+        <v>47.26406</v>
       </c>
       <c r="W44" t="n">
-        <v>-78.14164</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>48.71945</v>
+        <v>45.43568</v>
       </c>
       <c r="W45" t="n">
-        <v>-78.33144</v>
+        <v>-70.91788</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>As-3</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 6.38 g/t</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>53.52425</v>
+        <v>45.43447</v>
       </c>
       <c r="W46" t="n">
-        <v>-76.57341</v>
+        <v>-70.9088</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zone 32</t>
+          <t>Fraser (Zones 3, 4 &amp; 5)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
+          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>53.52649</v>
+        <v>48.32289</v>
       </c>
       <c r="W47" t="n">
-        <v>-76.56404999999999</v>
+        <v>-67.05</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pari</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 730.77 g/t</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>53.53306</v>
+        <v>48.33048</v>
       </c>
       <c r="W48" t="n">
-        <v>-76.55201</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brèche</t>
+          <t>46W</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic, Zinc, Silver</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 8.56 g/t</t>
+          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>53.53187</v>
+        <v>48.29961</v>
       </c>
       <c r="W49" t="n">
-        <v>-76.54353</v>
+        <v>-67.12675</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>49.84595</v>
+        <v>45.44349</v>
       </c>
       <c r="W50" t="n">
-        <v>-70.57626</v>
+        <v>-70.91244</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -4470,22 +4470,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Guettard-Nord</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>46.265</v>
+        <v>50.01478</v>
       </c>
       <c r="W52" t="n">
-        <v>-71.21259999999999</v>
+        <v>-75.39858</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Guettard-Nord</t>
+          <t>Lac Marcaut</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
+          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4600,23 +4600,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>50.01478</v>
+        <v>51.08117</v>
       </c>
       <c r="W53" t="n">
-        <v>-75.39858</v>
+        <v>-77.6185</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Lullwitz-Kaeppeli</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold, Zinc</t>
+          <t>Ir, Gold, Zr, Gallium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>46.26265</v>
+        <v>47.76432</v>
       </c>
       <c r="W54" t="n">
-        <v>-71.21769</v>
+        <v>-70.46635000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Obamska</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,12 +4714,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 9.50 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>46.26532</v>
+        <v>50.8353</v>
       </c>
       <c r="W55" t="n">
-        <v>-71.28788</v>
+        <v>-78.66648000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Guimond</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Silver, Gold, Bismuth, Copper, Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>47.43121</v>
+        <v>47.37388</v>
       </c>
       <c r="W56" t="n">
-        <v>-79.32868999999999</v>
+        <v>-79.13840999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>Pike</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Gold, Nickel, Copper, Mg, Silver</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Cu 12.3%, Au 2.54 g/t, Ni 0.28%, Ag 9.60 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>48.173</v>
+        <v>47.32819</v>
       </c>
       <c r="W57" t="n">
-        <v>-78.14212999999999</v>
+        <v>-79.07715</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4703</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lac Walsh-Ouest</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Silver, Molybdenum, Copper, Bismuth, Gold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>55.15269</v>
+        <v>47.43121</v>
       </c>
       <c r="W58" t="n">
-        <v>-66.35399</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Bleu</t>
+          <t>Zullo</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,12 +5026,12 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Niobium, Cobalt</t>
+          <t>Gold, Nickel, Copper</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
+          <t>Cu 3.35%, Ni 2.7%, Au 1.35 g/t</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>55.22879</v>
+        <v>47.43373</v>
       </c>
       <c r="W59" t="n">
-        <v>-66.12246</v>
+        <v>-79.24794</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4696</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Pogo</t>
+          <t>Gémini - B (Amas SF zincifère)</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,12 +5104,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold, Silver</t>
+          <t>Lead, Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+          <t>Au 2.59 g/t, Cu 1.8%, Ag 118.80 g/t, Zn 2.98%, Pb 2.29%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>55.23261</v>
+        <v>49.38378</v>
       </c>
       <c r="W60" t="n">
-        <v>-66.16073</v>
+        <v>-79.25754000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4004</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sond. SER-21-040</t>
+          <t>Brisebois</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 8.71 g/t</t>
+          <t>Au 27.97 g/t, Ag 5.90 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>53.08409</v>
+        <v>47.35141</v>
       </c>
       <c r="W61" t="n">
-        <v>-77.20562</v>
+        <v>-79.04821</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4705</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Iron, Cobalt</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>46.36809</v>
+        <v>53.56991</v>
       </c>
       <c r="W62" t="n">
-        <v>-73.97731</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Boulder Shear (Cuvier-Est)</t>
+          <t>Meilleur (Chess Uranium)</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Arsenic, Copper</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
+          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>49.9399</v>
+        <v>45.6921</v>
       </c>
       <c r="W63" t="n">
-        <v>-74.70344</v>
+        <v>-76.64127999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lac Barlow</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,14 +5467,14 @@
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>49.94431</v>
+        <v>47.68996</v>
       </c>
       <c r="W64" t="n">
-        <v>-74.71456000000001</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sond. PLP24-019</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,12 +5494,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bismuth, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Au 4.76 g/t, Bi 0.1%</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5545,14 +5545,14 @@
         <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>52.59612</v>
+        <v>58.81552</v>
       </c>
       <c r="W65" t="n">
-        <v>-77.37366</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sond. K2-22-10</t>
+          <t>Lac Rivon-Ouest</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Zinc, Molybdenum, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 3.64 g/t, Zn 0.55%</t>
+          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>52.28963</v>
+        <v>51.72313</v>
       </c>
       <c r="W66" t="n">
-        <v>-77.78149999999999</v>
+        <v>-72.79697</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kan</t>
+          <t>Sond. VER-21-06</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Lead, Silver, Copper</t>
+          <t>Zinc, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Au 6.72 g/t, Ag 390.00 g/t, Zn 17.4%, Pb 9.04%, Cu 0.115%</t>
+          <t>Au 2.61 g/t, Zn 1.57%, Cu 0.321%, Ag 11.50 g/t</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5701,14 +5701,14 @@
         <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>57.4579</v>
+        <v>51.03789</v>
       </c>
       <c r="W67" t="n">
-        <v>-69.21342</v>
+        <v>-77.71702000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3769</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=65174</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fenton 98-18</t>
+          <t>Rivière Pontois</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Au 5.47 g/t</t>
+          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5779,14 +5779,14 @@
         <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>49.51092</v>
+        <v>53.51426</v>
       </c>
       <c r="W68" t="n">
-        <v>-75.36535000000001</v>
+        <v>-74.51608</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LA-93-04</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5806,12 +5806,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Au 36.07 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5857,14 +5857,14 @@
         <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>49.55796</v>
+        <v>45.03676</v>
       </c>
       <c r="W69" t="n">
-        <v>-75.37448000000001</v>
+        <v>-72.77243</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sond. LF-93-03</t>
+          <t>Perch River</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5884,12 +5884,12 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Copper, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
+          <t>Cu 9.06%, Ag 19.20 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5935,14 +5935,14 @@
         <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>49.5436</v>
+        <v>50.33998</v>
       </c>
       <c r="W70" t="n">
-        <v>-75.41676</v>
+        <v>-73.71023</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rosembaum</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Copper</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>49.50469</v>
+        <v>46.26532</v>
       </c>
       <c r="W71" t="n">
-        <v>-75.32402999999999</v>
+        <v>-71.28788</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Copper, Silver, Manganese, Zinc</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>46.00535</v>
+        <v>46.26265</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.70357</v>
+        <v>-71.21769</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lepage No 2</t>
+          <t>Train No 4 (Lac Crabe)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6118,12 +6118,12 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold, Antimony, Arsenic</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+          <t>Cu 3.71%, U 0.07%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>48.33322</v>
+        <v>56.39584</v>
       </c>
       <c r="W73" t="n">
-        <v>-66.99834</v>
+        <v>-68.39176999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lac Mina-Est</t>
+          <t>SGR-09</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver, Nickel</t>
+          <t>Uranium, Gold</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 2.63 g/t, Cu 1.35%, Zn 1.57%, Ag 6.90 g/t, Ni 0.02%</t>
+          <t>Au 3.31 g/t, U 0.11%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6247,14 +6247,14 @@
         <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>49.5435</v>
+        <v>56.43951</v>
       </c>
       <c r="W74" t="n">
-        <v>-75.32167</v>
+        <v>-68.10245999999999</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3592</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lac Mina-Guercheville</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6274,12 +6274,12 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium, Gold, Copper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 20.57 g/t</t>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6325,14 +6325,14 @@
         <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>49.54166</v>
+        <v>56.43038</v>
       </c>
       <c r="W75" t="n">
-        <v>-75.33825</v>
+        <v>-68.09914000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fenton-Sud</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper</t>
+          <t>Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 53.08 g/t, Ag 53.00 g/t, Zn 1.96%, Cu 0.23%</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6403,14 +6403,14 @@
         <v>55</v>
       </c>
       <c r="V76" t="n">
-        <v>49.51684</v>
+        <v>52.20175</v>
       </c>
       <c r="W76" t="n">
-        <v>-75.36571000000001</v>
+        <v>-70.89798</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3589</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lac Lapointe-SE</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6430,12 +6430,12 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 3.12 g/t, Cu 1.05%, Ag 3.70 g/t</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6472,23 +6472,23 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T77" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U77" t="n">
         <v>55</v>
       </c>
       <c r="V77" t="n">
-        <v>49.5341</v>
+        <v>58.81627</v>
       </c>
       <c r="W77" t="n">
-        <v>-75.44531000000001</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Robidoux-appalaches</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,14 +6559,14 @@
         <v>55</v>
       </c>
       <c r="V78" t="n">
-        <v>48.35381</v>
+        <v>46.26109</v>
       </c>
       <c r="W78" t="n">
-        <v>-65.56434</v>
+        <v>-71.22866</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pyrite Falls</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 22.20 g/t, Ag 11.00 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6637,14 +6637,638 @@
         <v>55</v>
       </c>
       <c r="V79" t="n">
-        <v>57.44105</v>
+        <v>46.27176</v>
       </c>
       <c r="W79" t="n">
-        <v>-69.21915</v>
+        <v>-71.28612</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3770</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Copper, Uranium, Silver</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="n">
+        <v>325</v>
+      </c>
+      <c r="U80" t="n">
+        <v>55</v>
+      </c>
+      <c r="V80" t="n">
+        <v>46.265</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-71.21259999999999</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Lac Barlow</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Silver</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" t="n">
+        <v>325</v>
+      </c>
+      <c r="U81" t="n">
+        <v>55</v>
+      </c>
+      <c r="V81" t="n">
+        <v>49.94431</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-74.71456000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sond. K2-22-10</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Au 3.64 g/t, Zn 0.55%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>12</v>
+      </c>
+      <c r="T82" t="n">
+        <v>300</v>
+      </c>
+      <c r="U82" t="n">
+        <v>55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>52.28963</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-77.78149999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Lartic Est</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Silver</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="n">
+        <v>250</v>
+      </c>
+      <c r="U83" t="n">
+        <v>55</v>
+      </c>
+      <c r="V83" t="n">
+        <v>48.173</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-78.14212999999999</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ruisseau Basket</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>325</v>
+      </c>
+      <c r="U84" t="n">
+        <v>55</v>
+      </c>
+      <c r="V84" t="n">
+        <v>48.09296</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-66.78681</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Boulder Shear (Cuvier-Est)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Zinc, Gold, Copper, Arsenic</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>12</v>
+      </c>
+      <c r="T85" t="n">
+        <v>300</v>
+      </c>
+      <c r="U85" t="n">
+        <v>55</v>
+      </c>
+      <c r="V85" t="n">
+        <v>49.9399</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-74.70344</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deux Orignaux</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Au 3.60 g/t</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
+        <v>325</v>
+      </c>
+      <c r="U86" t="n">
+        <v>55</v>
+      </c>
+      <c r="V86" t="n">
+        <v>49.88535</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-75.3155</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66976</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Amaruk</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="n">
+        <v>250</v>
+      </c>
+      <c r="U87" t="n">
+        <v>55</v>
+      </c>
+      <c r="V87" t="n">
+        <v>59.60263</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-74.86282</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V2" t="n">
-        <v>49.01028</v>
+        <v>45.3192</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.00369999999999</v>
+        <v>-71.92023</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>45.3192</v>
+        <v>49.83681</v>
       </c>
       <c r="W3" t="n">
-        <v>-71.92023</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>49.83681</v>
+        <v>52.21818</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.57877999999999</v>
+        <v>-77.45902</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.82919</v>
+        <v>45.03676</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.58076</v>
+        <v>-72.77243</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,17 +892,17 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Zinc, Silver, Molybdenum, Cadmium, Barium</t>
+          <t>Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -913,12 +913,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>871 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
+          <t>Au 28.60 g/t, Zn 1.5%, Ag 5.40 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>45.40941</v>
+        <v>49.32164</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.81791</v>
+        <v>-74.99893</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=36151</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H-1456-009</t>
+          <t>Fox</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 8.47 g/t, Cu 0.303%, Ag 9.60 g/t, As 0.565%</t>
+          <t>Au 9.68 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>50.62126</v>
+        <v>49.39931</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.35012</v>
+        <v>-74.81483</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4342</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=36233</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Gold, Silver</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>45.32298</v>
+        <v>49.84595</v>
       </c>
       <c r="W8" t="n">
-        <v>-71.90649999999999</v>
+        <v>-70.57626</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rochelom</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
+          <t>Au 278.00 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>49.77064</v>
+        <v>52.1821</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.01858</v>
+        <v>-76.70099999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Goshawk</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Lead, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>61.56992</v>
+        <v>50.64946</v>
       </c>
       <c r="W10" t="n">
-        <v>-75.20258</v>
+        <v>-75.04613999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lac Dunphy</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Iron, Nickel, Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>56.05097</v>
+        <v>49.63941</v>
       </c>
       <c r="W11" t="n">
-        <v>-67.71257</v>
+        <v>-76.90893</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>56.40258</v>
+        <v>49.59836</v>
       </c>
       <c r="W12" t="n">
-        <v>-67.9023</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chibtown</t>
+          <t>Goshawk</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Zinc, Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
+          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>56.39152</v>
+        <v>61.56992</v>
       </c>
       <c r="W13" t="n">
-        <v>-67.87103</v>
+        <v>-75.20258</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>49.84595</v>
+        <v>49.82919</v>
       </c>
       <c r="W14" t="n">
-        <v>-70.57626</v>
+        <v>-70.58076</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>Lavallée : Zone 38</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+          <t>Au 8.77 g/t, Cu 0.68%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>50.85296</v>
+        <v>47.37311</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.47398</v>
+        <v>-78.98152</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33773</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Transfiguration (Labrador Expl.)</t>
+          <t>Lavallée : Zone 40</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Lead</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 3.08%, Pb 21.1%, Zn 8.52%, Ag 97.37 g/t</t>
+          <t>Au 2.76 g/t, Cu 0.921%, Ag 22.35 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>47.93876</v>
+        <v>47.3781</v>
       </c>
       <c r="W16" t="n">
-        <v>-68.75702</v>
+        <v>-78.97445</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4162</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33774</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Transfiguration: Zone E3</t>
+          <t>Renaissance</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Copper, Gold, Zinc, Silver</t>
+          <t>Copper, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
+          <t>Cu 2.11%, Zn 5.07%, Ag 43.40 g/t, Au 0.57 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>47.9394</v>
+        <v>49.77453</v>
       </c>
       <c r="W17" t="n">
-        <v>-68.76391</v>
+        <v>-78.15862</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67204</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Rivière Pontois</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 5.00 g/t</t>
+          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>50.8451</v>
+        <v>53.51426</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.45574000000001</v>
+        <v>-74.51608</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4236</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sond. PIK20-001</t>
+          <t>Rochelom</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 3.38%, Ag 25.50 g/t, Zn 0.147%</t>
+          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>53.53043</v>
+        <v>49.77064</v>
       </c>
       <c r="W19" t="n">
-        <v>-74.33239</v>
+        <v>-76.01858</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66837</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gémini - A sud</t>
+          <t>ELR-16-002</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 3.43 g/t, Ag 6.20 g/t</t>
+          <t>Au 9.13 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.42712</v>
+        <v>52.67859</v>
       </c>
       <c r="W20" t="n">
-        <v>-79.27181</v>
+        <v>-76.30803</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4008</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
         </is>
       </c>
     </row>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gémini - A Nord</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.43645</v>
+        <v>48.37403</v>
       </c>
       <c r="W21" t="n">
-        <v>-79.26394999999999</v>
+        <v>-65.44089</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gémini - B (Zone à cuivre)</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 3.78%, Ag 130.00 g/t, Au 1.38 g/t, Zn 3.87%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.38069</v>
+        <v>46.26532</v>
       </c>
       <c r="W22" t="n">
-        <v>-79.25882</v>
+        <v>-71.28788</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4012</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monts Peacock-Sud</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Copper, Nickel, Silver</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 2.77%, Au 1.06 g/t, Ni 0.73%, Ag 14.10 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>49.20789</v>
+        <v>46.26265</v>
       </c>
       <c r="W23" t="n">
-        <v>-78.41656999999999</v>
+        <v>-71.21769</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4030</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Claims Peacock</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 7.50 g/t</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>49.16788</v>
+        <v>46.26109</v>
       </c>
       <c r="W24" t="n">
-        <v>-78.43522</v>
+        <v>-71.22866</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vior-Zone Nord</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Silver</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 5.55 g/t, Ag 2.00 g/t, Cu 0.06%, Zn 0.17%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>49.01288</v>
+        <v>45.43447</v>
       </c>
       <c r="W25" t="n">
-        <v>-78.48756</v>
+        <v>-70.9088</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gold Fields</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 19.04 g/t</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>49.09287</v>
+        <v>45.44349</v>
       </c>
       <c r="W26" t="n">
-        <v>-78.42254</v>
+        <v>-70.91244</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D-91-01 (Option Dejour)</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>49.02527</v>
+        <v>45.45582</v>
       </c>
       <c r="W27" t="n">
-        <v>-78.38705</v>
+        <v>-70.90786</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G-H-2-79 (Hudbay Mining)</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 3.26%, Ni 1.12%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>51.50451</v>
+        <v>45.40513</v>
       </c>
       <c r="W28" t="n">
-        <v>-67.92737</v>
+        <v>-70.9376</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Iron, Nickel, Copper</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.63941</v>
+        <v>45.43568</v>
       </c>
       <c r="W29" t="n">
-        <v>-76.90893</v>
+        <v>-70.91788</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>MA-16-05</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Au 17.50 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>49.59836</v>
+        <v>49.89574</v>
       </c>
       <c r="W30" t="n">
-        <v>-76.92194000000001</v>
+        <v>-79.50295</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=44678</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ouest-Goldfield</t>
+          <t>Sheillan</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 3.75 g/t, Ag 1.10 g/t</t>
+          <t>Au 90.30 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.06302</v>
+        <v>49.10861</v>
       </c>
       <c r="W31" t="n">
-        <v>-78.47202</v>
+        <v>-76.22864</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4039</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CaribGold 99-07</t>
+          <t>Huckleberry</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Platinum, Palladium, Egp, Nickel, Zinc, Chromium, Silver</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
+          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Ag 26.60 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>50.75408</v>
+        <v>55.78035</v>
       </c>
       <c r="W32" t="n">
-        <v>-76.84898</v>
+        <v>-66.95337000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Labrie</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 48.80 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>48.95238</v>
+        <v>46.27176</v>
       </c>
       <c r="W33" t="n">
-        <v>-76.4864</v>
+        <v>-71.28612</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4277</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bloc Est</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>50.84188</v>
+        <v>46.265</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.39422</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4235</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Midrim</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Egp, Nickel, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 3.54%, Ni 2.94%, EGP 0.000422%</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>47.47178</v>
+        <v>53.43724</v>
       </c>
       <c r="W35" t="n">
-        <v>-79.23383</v>
+        <v>-75.04334</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4692</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lac De Maurès-Est</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 12.6%, Au 5.79 g/t, Ag 50.00 g/t</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>50.65811</v>
+        <v>60.2779</v>
       </c>
       <c r="W36" t="n">
-        <v>-74.36593999999999</v>
+        <v>-75.33311</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4292</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lac Odon</t>
+          <t>Lac Dunphy</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 19.20 g/t, Cu 3.51%, Mo 0.96%, Ag 8.40 g/t</t>
+          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>50.68338</v>
+        <v>56.05097</v>
       </c>
       <c r="W37" t="n">
-        <v>-74.36037</v>
+        <v>-67.71257</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4293</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lac Rocher</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,17 +3388,17 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platinum, Egp, Copper, Nickel, Palladium, Cobalt, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>50.58471</v>
+        <v>56.40258</v>
       </c>
       <c r="W38" t="n">
-        <v>-76.34242</v>
+        <v>-67.9023</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AT-32-91</t>
+          <t>Chibtown</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t</t>
+          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>48.89509</v>
+        <v>56.39152</v>
       </c>
       <c r="W39" t="n">
-        <v>-78.79843</v>
+        <v>-67.87103</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>Perch River</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 26.78 g/t</t>
+          <t>Cu 9.06%, Ag 19.20 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>50.8534</v>
+        <v>50.33998</v>
       </c>
       <c r="W40" t="n">
-        <v>-76.53675</v>
+        <v>-73.71023</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4238</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H-1451-032</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 2.20 g/t, Cu 0.66%, Zn 1.59%, Ag 21.80 g/t</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>50.79734</v>
+        <v>52.17253</v>
       </c>
       <c r="W41" t="n">
-        <v>-76.70574000000001</v>
+        <v>-76.55762</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4242</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Lac Barlow</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>48.31932</v>
+        <v>49.94431</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.9713</v>
+        <v>-74.71456000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Boulder Shear (Cuvier-Est)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Zinc, Gold, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>48.37403</v>
+        <v>49.9399</v>
       </c>
       <c r="W43" t="n">
-        <v>-65.44089</v>
+        <v>-74.70344</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Guimond</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>47.26406</v>
+        <v>47.37388</v>
       </c>
       <c r="W44" t="n">
-        <v>-79.40157000000001</v>
+        <v>-79.13840999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>45.43568</v>
+        <v>52.20175</v>
       </c>
       <c r="W45" t="n">
-        <v>-70.91788</v>
+        <v>-70.89798</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,3212 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>45.43447</v>
+        <v>53.56991</v>
       </c>
       <c r="W46" t="n">
-        <v>-70.9088</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Fraser (Zones 3, 4 &amp; 5)</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="n">
-        <v>13</v>
-      </c>
-      <c r="T47" t="n">
-        <v>325</v>
-      </c>
-      <c r="U47" t="n">
-        <v>55</v>
-      </c>
-      <c r="V47" t="n">
-        <v>48.32289</v>
-      </c>
-      <c r="W47" t="n">
-        <v>-67.05</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>36E</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Au 17.18 g/t, As 1%</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="n">
-        <v>13</v>
-      </c>
-      <c r="T48" t="n">
-        <v>325</v>
-      </c>
-      <c r="U48" t="n">
-        <v>55</v>
-      </c>
-      <c r="V48" t="n">
-        <v>48.33048</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-67.01985999999999</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>46W</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="n">
-        <v>13</v>
-      </c>
-      <c r="T49" t="n">
-        <v>325</v>
-      </c>
-      <c r="U49" t="n">
-        <v>55</v>
-      </c>
-      <c r="V49" t="n">
-        <v>48.29961</v>
-      </c>
-      <c r="W49" t="n">
-        <v>-67.12675</v>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Clinton C</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>13</v>
-      </c>
-      <c r="T50" t="n">
-        <v>325</v>
-      </c>
-      <c r="U50" t="n">
-        <v>55</v>
-      </c>
-      <c r="V50" t="n">
-        <v>45.44349</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-70.91244</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Monarch - Veine 1</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 83.00 g/t</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>13</v>
-      </c>
-      <c r="T51" t="n">
-        <v>325</v>
-      </c>
-      <c r="U51" t="n">
-        <v>55</v>
-      </c>
-      <c r="V51" t="n">
-        <v>48.23207</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-79.41287</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Guettard-Nord</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="n">
-        <v>13</v>
-      </c>
-      <c r="T52" t="n">
-        <v>325</v>
-      </c>
-      <c r="U52" t="n">
-        <v>55</v>
-      </c>
-      <c r="V52" t="n">
-        <v>50.01478</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-75.39858</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Lac Marcaut</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="n">
-        <v>13</v>
-      </c>
-      <c r="T53" t="n">
-        <v>325</v>
-      </c>
-      <c r="U53" t="n">
-        <v>55</v>
-      </c>
-      <c r="V53" t="n">
-        <v>51.08117</v>
-      </c>
-      <c r="W53" t="n">
-        <v>-77.6185</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Lullwitz-Kaeppeli</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Ir, Gold, Zr, Gallium</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>13</v>
-      </c>
-      <c r="T54" t="n">
-        <v>325</v>
-      </c>
-      <c r="U54" t="n">
-        <v>55</v>
-      </c>
-      <c r="V54" t="n">
-        <v>47.76432</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-70.46635000000001</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Obamska</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Au 9.50 g/t</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>13</v>
-      </c>
-      <c r="T55" t="n">
-        <v>325</v>
-      </c>
-      <c r="U55" t="n">
-        <v>55</v>
-      </c>
-      <c r="V55" t="n">
-        <v>50.8353</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-78.66648000000001</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Guimond</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>13</v>
-      </c>
-      <c r="T56" t="n">
-        <v>325</v>
-      </c>
-      <c r="U56" t="n">
-        <v>55</v>
-      </c>
-      <c r="V56" t="n">
-        <v>47.37388</v>
-      </c>
-      <c r="W56" t="n">
-        <v>-79.13840999999999</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Pike</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Gold, Nickel, Copper, Mg, Silver</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Cu 12.3%, Au 2.54 g/t, Ni 0.28%, Ag 9.60 g/t</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>325</v>
-      </c>
-      <c r="U57" t="n">
-        <v>55</v>
-      </c>
-      <c r="V57" t="n">
-        <v>47.32819</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-79.07715</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4703</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Silver, Molybdenum, Copper, Bismuth, Gold</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>325</v>
-      </c>
-      <c r="U58" t="n">
-        <v>55</v>
-      </c>
-      <c r="V58" t="n">
-        <v>47.43121</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-79.32868999999999</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Zullo</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Gold, Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Cu 3.35%, Ni 2.7%, Au 1.35 g/t</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>13</v>
-      </c>
-      <c r="T59" t="n">
-        <v>325</v>
-      </c>
-      <c r="U59" t="n">
-        <v>55</v>
-      </c>
-      <c r="V59" t="n">
-        <v>47.43373</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-79.24794</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4696</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Gémini - B (Amas SF zincifère)</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Lead, Gold, Copper, Silver, Zinc</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Au 2.59 g/t, Cu 1.8%, Ag 118.80 g/t, Zn 2.98%, Pb 2.29%</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>13</v>
-      </c>
-      <c r="T60" t="n">
-        <v>325</v>
-      </c>
-      <c r="U60" t="n">
-        <v>55</v>
-      </c>
-      <c r="V60" t="n">
-        <v>49.38378</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-79.25754000000001</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4004</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Brisebois</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Au 27.97 g/t, Ag 5.90 g/t</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>13</v>
-      </c>
-      <c r="T61" t="n">
-        <v>325</v>
-      </c>
-      <c r="U61" t="n">
-        <v>55</v>
-      </c>
-      <c r="V61" t="n">
-        <v>47.35141</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-79.04821</v>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4705</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Lac Janjandashi</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>325</v>
-      </c>
-      <c r="U62" t="n">
-        <v>55</v>
-      </c>
-      <c r="V62" t="n">
-        <v>53.56991</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-77.31073000000001</v>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Meilleur (Chess Uranium)</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>13</v>
-      </c>
-      <c r="T63" t="n">
-        <v>325</v>
-      </c>
-      <c r="U63" t="n">
-        <v>55</v>
-      </c>
-      <c r="V63" t="n">
-        <v>45.6921</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-76.64127999999999</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Lac Harris</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Cu 5.07%</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>13</v>
-      </c>
-      <c r="T64" t="n">
-        <v>325</v>
-      </c>
-      <c r="U64" t="n">
-        <v>55</v>
-      </c>
-      <c r="V64" t="n">
-        <v>47.68996</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-76.66074999999999</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Kogaluc 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Au 5.60 g/t</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>13</v>
-      </c>
-      <c r="T65" t="n">
-        <v>325</v>
-      </c>
-      <c r="U65" t="n">
-        <v>55</v>
-      </c>
-      <c r="V65" t="n">
-        <v>58.81552</v>
-      </c>
-      <c r="W65" t="n">
-        <v>-74.68685000000001</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Lac Rivon-Ouest</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Zinc, Molybdenum, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>13</v>
-      </c>
-      <c r="T66" t="n">
-        <v>325</v>
-      </c>
-      <c r="U66" t="n">
-        <v>55</v>
-      </c>
-      <c r="V66" t="n">
-        <v>51.72313</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-72.79697</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Sond. VER-21-06</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Zinc, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Au 2.61 g/t, Zn 1.57%, Cu 0.321%, Ag 11.50 g/t</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>13</v>
-      </c>
-      <c r="T67" t="n">
-        <v>325</v>
-      </c>
-      <c r="U67" t="n">
-        <v>55</v>
-      </c>
-      <c r="V67" t="n">
-        <v>51.03789</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-77.71702000000001</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=65174</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Rivière Pontois</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="n">
-        <v>13</v>
-      </c>
-      <c r="T68" t="n">
-        <v>325</v>
-      </c>
-      <c r="U68" t="n">
-        <v>55</v>
-      </c>
-      <c r="V68" t="n">
-        <v>53.51426</v>
-      </c>
-      <c r="W68" t="n">
-        <v>-74.51608</v>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="n">
-        <v>13</v>
-      </c>
-      <c r="T69" t="n">
-        <v>325</v>
-      </c>
-      <c r="U69" t="n">
-        <v>55</v>
-      </c>
-      <c r="V69" t="n">
-        <v>45.03676</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-72.77243</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Perch River</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Cu 9.06%, Ag 19.20 g/t</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>13</v>
-      </c>
-      <c r="T70" t="n">
-        <v>325</v>
-      </c>
-      <c r="U70" t="n">
-        <v>55</v>
-      </c>
-      <c r="V70" t="n">
-        <v>50.33998</v>
-      </c>
-      <c r="W70" t="n">
-        <v>-73.71023</v>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Grondin</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>13</v>
-      </c>
-      <c r="T71" t="n">
-        <v>325</v>
-      </c>
-      <c r="U71" t="n">
-        <v>55</v>
-      </c>
-      <c r="V71" t="n">
-        <v>46.26532</v>
-      </c>
-      <c r="W71" t="n">
-        <v>-71.28788</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Nutbrown</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="n">
-        <v>13</v>
-      </c>
-      <c r="T72" t="n">
-        <v>325</v>
-      </c>
-      <c r="U72" t="n">
-        <v>55</v>
-      </c>
-      <c r="V72" t="n">
-        <v>46.26265</v>
-      </c>
-      <c r="W72" t="n">
-        <v>-71.21769</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Train No 4 (Lac Crabe)</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Uranium, Copper</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Cu 3.71%, U 0.07%</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>13</v>
-      </c>
-      <c r="T73" t="n">
-        <v>325</v>
-      </c>
-      <c r="U73" t="n">
-        <v>55</v>
-      </c>
-      <c r="V73" t="n">
-        <v>56.39584</v>
-      </c>
-      <c r="W73" t="n">
-        <v>-68.39176999999999</v>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SGR-09</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Uranium, Gold</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>13</v>
-      </c>
-      <c r="T74" t="n">
-        <v>325</v>
-      </c>
-      <c r="U74" t="n">
-        <v>55</v>
-      </c>
-      <c r="V74" t="n">
-        <v>56.43951</v>
-      </c>
-      <c r="W74" t="n">
-        <v>-68.10245999999999</v>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Viking</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Uranium, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>13</v>
-      </c>
-      <c r="T75" t="n">
-        <v>325</v>
-      </c>
-      <c r="U75" t="n">
-        <v>55</v>
-      </c>
-      <c r="V75" t="n">
-        <v>56.43038</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-68.09914000000001</v>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Lac du Crapet</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>13</v>
-      </c>
-      <c r="T76" t="n">
-        <v>325</v>
-      </c>
-      <c r="U76" t="n">
-        <v>55</v>
-      </c>
-      <c r="V76" t="n">
-        <v>52.20175</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-70.89798</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Kogaluc 1</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>13</v>
-      </c>
-      <c r="T77" t="n">
-        <v>325</v>
-      </c>
-      <c r="U77" t="n">
-        <v>55</v>
-      </c>
-      <c r="V77" t="n">
-        <v>58.81627</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-74.70458000000001</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Foy</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>13</v>
-      </c>
-      <c r="T78" t="n">
-        <v>325</v>
-      </c>
-      <c r="U78" t="n">
-        <v>55</v>
-      </c>
-      <c r="V78" t="n">
-        <v>46.26109</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-71.22866</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Coleraine</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>325</v>
-      </c>
-      <c r="U79" t="n">
-        <v>55</v>
-      </c>
-      <c r="V79" t="n">
-        <v>46.27176</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-71.28612</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Copper, Uranium, Silver</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>13</v>
-      </c>
-      <c r="T80" t="n">
-        <v>325</v>
-      </c>
-      <c r="U80" t="n">
-        <v>55</v>
-      </c>
-      <c r="V80" t="n">
-        <v>46.265</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-71.21259999999999</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Lac Barlow</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>13</v>
-      </c>
-      <c r="T81" t="n">
-        <v>325</v>
-      </c>
-      <c r="U81" t="n">
-        <v>55</v>
-      </c>
-      <c r="V81" t="n">
-        <v>49.94431</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-74.71456000000001</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Sond. K2-22-10</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Gold, Zinc</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Au 3.64 g/t, Zn 0.55%</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>12</v>
-      </c>
-      <c r="T82" t="n">
-        <v>300</v>
-      </c>
-      <c r="U82" t="n">
-        <v>55</v>
-      </c>
-      <c r="V82" t="n">
-        <v>52.28963</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-77.78149999999999</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67103</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Lartic Est</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="n">
-        <v>250</v>
-      </c>
-      <c r="U83" t="n">
-        <v>55</v>
-      </c>
-      <c r="V83" t="n">
-        <v>48.173</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-78.14212999999999</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Ruisseau Basket</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>325</v>
-      </c>
-      <c r="U84" t="n">
-        <v>55</v>
-      </c>
-      <c r="V84" t="n">
-        <v>48.09296</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-66.78681</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Boulder Shear (Cuvier-Est)</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Zinc, Gold, Copper, Arsenic</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>12</v>
-      </c>
-      <c r="T85" t="n">
-        <v>300</v>
-      </c>
-      <c r="U85" t="n">
-        <v>55</v>
-      </c>
-      <c r="V85" t="n">
-        <v>49.9399</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-74.70344</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deux Orignaux</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Au 3.60 g/t</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>13</v>
-      </c>
-      <c r="T86" t="n">
-        <v>325</v>
-      </c>
-      <c r="U86" t="n">
-        <v>55</v>
-      </c>
-      <c r="V86" t="n">
-        <v>49.88535</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-75.3155</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66976</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Amaruk</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="n">
-        <v>250</v>
-      </c>
-      <c r="U87" t="n">
-        <v>55</v>
-      </c>
-      <c r="V87" t="n">
-        <v>59.60263</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-74.86282</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>45.3192</v>
+        <v>49.01028</v>
       </c>
       <c r="W2" t="n">
-        <v>-71.92023</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="V3" t="n">
-        <v>49.83681</v>
+        <v>45.3192</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.57877999999999</v>
+        <v>-71.92023</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lidge</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Arsenic</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>52.21818</v>
+        <v>48.09296</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.45902</v>
+        <v>-66.78681</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>45.03676</v>
+        <v>48.23154</v>
       </c>
       <c r="W5" t="n">
-        <v>-72.77243</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Silver</t>
+          <t>Copper, Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 28.60 g/t, Zn 1.5%, Ag 5.40 g/t</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.32164</v>
+        <v>49.78784</v>
       </c>
       <c r="W6" t="n">
-        <v>-74.99893</v>
+        <v>-77.08529</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=36151</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fox</t>
+          <t>Amaruk</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 9.68 g/t</t>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>49.39931</v>
+        <v>59.60263</v>
       </c>
       <c r="W7" t="n">
-        <v>-74.81483</v>
+        <v>-74.86282</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=36233</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>
@@ -1116,22 +1116,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Molybdenum, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 278.00 g/t</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1168,23 +1168,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U9" t="n">
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>52.1821</v>
+        <v>45.99171</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.70099999999999</v>
+        <v>-71.70617</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 7.60 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1246,23 +1246,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U10" t="n">
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>50.64946</v>
+        <v>45.44828</v>
       </c>
       <c r="W10" t="n">
-        <v>-75.04613999999999</v>
+        <v>-72.1057</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iron, Nickel, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>49.63941</v>
+        <v>45.32873</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.90893</v>
+        <v>-72.47421</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nickel, Copper</t>
+          <t>Nickel, Copper, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>49.59836</v>
+        <v>49.82919</v>
       </c>
       <c r="W12" t="n">
-        <v>-76.92194000000001</v>
+        <v>-70.58076</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Goshawk</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Lead, Silver</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>61.56992</v>
+        <v>49.83681</v>
       </c>
       <c r="W13" t="n">
-        <v>-75.20258</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>49.82919</v>
+        <v>45.03676</v>
       </c>
       <c r="W14" t="n">
-        <v>-70.58076</v>
+        <v>-72.77243</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -1584,22 +1584,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lavallée : Zone 38</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Lead, Cadmium, Zinc, Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 8.77 g/t, Cu 0.68%, Ag 7.20 g/t</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>47.37311</v>
+        <v>45.29835</v>
       </c>
       <c r="W15" t="n">
-        <v>-78.98152</v>
+        <v>-72.31643</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33773</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -1662,11 +1662,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lavallée : Zone 40</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 2.76 g/t, Cu 0.921%, Ag 22.35 g/t</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>47.3781</v>
+        <v>48.71945</v>
       </c>
       <c r="W16" t="n">
-        <v>-78.97445</v>
+        <v>-78.33144</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=33774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Renaissance</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 2.11%, Zn 5.07%, Ag 43.40 g/t, Au 0.57 g/t</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>49.77453</v>
+        <v>48.70382</v>
       </c>
       <c r="W17" t="n">
-        <v>-78.15862</v>
+        <v>-78.25041</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67204</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rivière Pontois</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Arsenic, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>53.51426</v>
+        <v>48.57696</v>
       </c>
       <c r="W18" t="n">
-        <v>-74.51608</v>
+        <v>-78.14164</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rochelom</t>
+          <t>Rambo</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.77064</v>
+        <v>49.93645</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.01858</v>
+        <v>-79.32689999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3919</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ELR-16-002</t>
+          <t>Zone Lynx</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 9.13 g/t</t>
+          <t>Au 7.78 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>52.67859</v>
+        <v>49.93762</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.30803</v>
+        <v>-79.3579</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3915</t>
         </is>
       </c>
     </row>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.37403</v>
+        <v>45.42257</v>
       </c>
       <c r="W21" t="n">
-        <v>-65.44089</v>
+        <v>-70.92541</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,17 +2140,17 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Lead, Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>46.26532</v>
+        <v>45.42731</v>
       </c>
       <c r="W22" t="n">
-        <v>-71.28788</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>46.26265</v>
+        <v>45.40513</v>
       </c>
       <c r="W23" t="n">
-        <v>-71.21769</v>
+        <v>-70.9376</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>46.26109</v>
+        <v>45.45582</v>
       </c>
       <c r="W24" t="n">
-        <v>-71.22866</v>
+        <v>-70.90786</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>45.43447</v>
+        <v>45.44349</v>
       </c>
       <c r="W25" t="n">
-        <v>-70.9088</v>
+        <v>-70.91244</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>46W</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold, Arsenic, Zinc, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>45.44349</v>
+        <v>48.29961</v>
       </c>
       <c r="W26" t="n">
-        <v>-70.91244</v>
+        <v>-67.12675</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Josselin-Tonnancourt (Greenland)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Au 121.80 g/t, Cu 20%, Zn 13.1%, Ag 130.40 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>45.45582</v>
+        <v>48.86335</v>
       </c>
       <c r="W27" t="n">
-        <v>-70.90786</v>
+        <v>-76.99204</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3877</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Ouf</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Cu 11.8%, Ag 204.00 g/t, Zn 8.7%, Pb 1.6%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>45.40513</v>
+        <v>53.90478</v>
       </c>
       <c r="W28" t="n">
-        <v>-70.9376</v>
+        <v>-74.69878</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3841</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Au 29.25 g/t, W 0.122%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>45.43568</v>
+        <v>52.64108</v>
       </c>
       <c r="W29" t="n">
-        <v>-70.91788</v>
+        <v>-75.67010999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MA-16-05</t>
+          <t>Gémini - B (Zone à cuivre)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 17.50 g/t</t>
+          <t>Cu 3.78%, Ag 130.00 g/t, Au 1.38 g/t, Zn 3.87%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>49.89574</v>
+        <v>49.38069</v>
       </c>
       <c r="W30" t="n">
-        <v>-79.50295</v>
+        <v>-79.25882</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=44678</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4012</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sheillan</t>
+          <t>Gémini - A Nord</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 90.30 g/t</t>
+          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.10861</v>
+        <v>49.43645</v>
       </c>
       <c r="W31" t="n">
-        <v>-76.22864</v>
+        <v>-79.26394999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Huckleberry</t>
+          <t>Gémini - A sud</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Ag 26.60 g/t</t>
+          <t>Au 3.43 g/t, Ag 6.20 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>55.78035</v>
+        <v>49.42712</v>
       </c>
       <c r="W32" t="n">
-        <v>-66.95337000000001</v>
+        <v>-79.27181</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4008</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Gémini - B (Amas SF zincifère)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Lead, Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Au 2.59 g/t, Cu 1.8%, Ag 118.80 g/t, Zn 2.98%, Pb 2.29%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>46.27176</v>
+        <v>49.38378</v>
       </c>
       <c r="W33" t="n">
-        <v>-71.28612</v>
+        <v>-79.25754000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4004</t>
         </is>
       </c>
     </row>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>46.265</v>
+        <v>48.33048</v>
       </c>
       <c r="W34" t="n">
-        <v>-71.21259999999999</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Lac Foubert</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Cu 6.1%, Au 5.52 g/t, Mo 0.448%, Ag 38.10 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>53.43724</v>
+        <v>49.80466</v>
       </c>
       <c r="W35" t="n">
-        <v>-75.04334</v>
+        <v>-79.28044</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3927</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAP Nord (Camp A-1)</t>
+          <t>Claims Peacock</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+          <t>Au 7.50 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>60.2779</v>
+        <v>49.16788</v>
       </c>
       <c r="W36" t="n">
-        <v>-75.33311</v>
+        <v>-78.43522</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4032</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lac Dunphy</t>
+          <t>Monts Peacock-Sud</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
+          <t>Cu 2.77%, Au 1.06 g/t, Ni 0.73%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>56.05097</v>
+        <v>49.20789</v>
       </c>
       <c r="W37" t="n">
-        <v>-67.71257</v>
+        <v>-78.41656999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4030</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Fraser (Zones 3, 4 &amp; 5)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>56.40258</v>
+        <v>48.32289</v>
       </c>
       <c r="W38" t="n">
-        <v>-67.9023</v>
+        <v>-67.05</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chibtown</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>56.39152</v>
+        <v>46.26532</v>
       </c>
       <c r="W39" t="n">
-        <v>-67.87103</v>
+        <v>-71.28788</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Perch River</t>
+          <t>LA-93-04</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 9.06%, Ag 19.20 g/t</t>
+          <t>Au 36.07 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3586,23 +3586,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>50.33998</v>
+        <v>49.55796</v>
       </c>
       <c r="W40" t="n">
-        <v>-73.71023</v>
+        <v>-75.37448000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>Sond. LF-93-03</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>52.17253</v>
+        <v>49.5436</v>
       </c>
       <c r="W41" t="n">
-        <v>-76.55762</v>
+        <v>-75.41676</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Barlow</t>
+          <t>Lac Mina-Guercheville</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+          <t>Au 20.57 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.94431</v>
+        <v>49.54166</v>
       </c>
       <c r="W42" t="n">
-        <v>-74.71456000000001</v>
+        <v>-75.33825</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3591</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boulder Shear (Cuvier-Est)</t>
+          <t>Fenton-Sud</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Copper, Arsenic</t>
+          <t>Zinc, Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
+          <t>Au 53.08 g/t, Ag 53.00 g/t, Zn 1.96%, Cu 0.23%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3820,23 +3820,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>49.9399</v>
+        <v>49.51684</v>
       </c>
       <c r="W43" t="n">
-        <v>-74.70344</v>
+        <v>-75.36571000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3589</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guimond</t>
+          <t>Lac Lapointe-SE</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
+          <t>Au 3.12 g/t, Cu 1.05%, Ag 3.70 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>47.37388</v>
+        <v>49.5341</v>
       </c>
       <c r="W44" t="n">
-        <v>-79.13840999999999</v>
+        <v>-75.44531000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3587</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Sond. DDH-20-2023</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold, Lead, Silver</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>52.20175</v>
+        <v>46.36809</v>
       </c>
       <c r="W45" t="n">
-        <v>-70.89798</v>
+        <v>-73.97731</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Lac Mina-Est</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Zinc, Gold, Nickel, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Au 2.63 g/t, Cu 1.35%, Zn 1.57%, Ag 6.90 g/t, Ni 0.02%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,1964 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>53.56991</v>
+        <v>49.5435</v>
       </c>
       <c r="W46" t="n">
-        <v>-77.31073000000001</v>
+        <v>-75.32167</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3592</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Copper, Uranium, Silver</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>13</v>
+      </c>
+      <c r="T47" t="n">
+        <v>325</v>
+      </c>
+      <c r="U47" t="n">
+        <v>55</v>
+      </c>
+      <c r="V47" t="n">
+        <v>46.265</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-71.21259999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Coleraine</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>13</v>
+      </c>
+      <c r="T48" t="n">
+        <v>325</v>
+      </c>
+      <c r="U48" t="n">
+        <v>55</v>
+      </c>
+      <c r="V48" t="n">
+        <v>46.27176</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-71.28612</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nutbrown</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="n">
+        <v>325</v>
+      </c>
+      <c r="U49" t="n">
+        <v>55</v>
+      </c>
+      <c r="V49" t="n">
+        <v>46.26265</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-71.21769</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Foy</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="n">
+        <v>325</v>
+      </c>
+      <c r="U50" t="n">
+        <v>55</v>
+      </c>
+      <c r="V50" t="n">
+        <v>46.26109</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-71.22866</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Fenton 98-18</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 5.47 g/t</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>13</v>
+      </c>
+      <c r="T51" t="n">
+        <v>325</v>
+      </c>
+      <c r="U51" t="n">
+        <v>55</v>
+      </c>
+      <c r="V51" t="n">
+        <v>49.51092</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-75.36535000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Clinton V</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="n">
+        <v>325</v>
+      </c>
+      <c r="U52" t="n">
+        <v>55</v>
+      </c>
+      <c r="V52" t="n">
+        <v>45.43447</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-70.9088</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Clinton D</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>13</v>
+      </c>
+      <c r="T53" t="n">
+        <v>325</v>
+      </c>
+      <c r="U53" t="n">
+        <v>55</v>
+      </c>
+      <c r="V53" t="n">
+        <v>45.43568</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-70.91788</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Lepage No 2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Antimony</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>13</v>
+      </c>
+      <c r="T54" t="n">
+        <v>325</v>
+      </c>
+      <c r="U54" t="n">
+        <v>55</v>
+      </c>
+      <c r="V54" t="n">
+        <v>48.33322</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-66.99834</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Robidoux-appalaches</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lead, Silver, Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>13</v>
+      </c>
+      <c r="T55" t="n">
+        <v>325</v>
+      </c>
+      <c r="U55" t="n">
+        <v>55</v>
+      </c>
+      <c r="V55" t="n">
+        <v>48.35381</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-65.56434</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sond. Umex 132</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Cu 4%, Zn 6%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>13</v>
+      </c>
+      <c r="T56" t="n">
+        <v>325</v>
+      </c>
+      <c r="U56" t="n">
+        <v>55</v>
+      </c>
+      <c r="V56" t="n">
+        <v>49.79699</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-75.81529</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Umex-2</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="n">
+        <v>225</v>
+      </c>
+      <c r="U57" t="n">
+        <v>55</v>
+      </c>
+      <c r="V57" t="n">
+        <v>49.81674</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-75.52503</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GD-32</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Au 4.40 g/t</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>13</v>
+      </c>
+      <c r="T58" t="n">
+        <v>325</v>
+      </c>
+      <c r="U58" t="n">
+        <v>55</v>
+      </c>
+      <c r="V58" t="n">
+        <v>49.49854</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-75.14399</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3646</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>House</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Au 11.00 g/t, Cu 3.3%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>13</v>
+      </c>
+      <c r="T59" t="n">
+        <v>325</v>
+      </c>
+      <c r="U59" t="n">
+        <v>55</v>
+      </c>
+      <c r="V59" t="n">
+        <v>49.49222</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-75.32478999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3643</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Drouet</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Au 6.00 g/t</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>13</v>
+      </c>
+      <c r="T60" t="n">
+        <v>325</v>
+      </c>
+      <c r="U60" t="n">
+        <v>55</v>
+      </c>
+      <c r="V60" t="n">
+        <v>49.49319</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-75.12523</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Rosembaum</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>13</v>
+      </c>
+      <c r="T61" t="n">
+        <v>325</v>
+      </c>
+      <c r="U61" t="n">
+        <v>55</v>
+      </c>
+      <c r="V61" t="n">
+        <v>49.50469</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-75.32402999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Reboul : Zone Nord-Est</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>13</v>
+      </c>
+      <c r="T62" t="n">
+        <v>325</v>
+      </c>
+      <c r="U62" t="n">
+        <v>55</v>
+      </c>
+      <c r="V62" t="n">
+        <v>48.37403</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-65.44089</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Filon Baker (Lac Arseneault)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Zinc, Lead, Copper</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>13</v>
+      </c>
+      <c r="T63" t="n">
+        <v>325</v>
+      </c>
+      <c r="U63" t="n">
+        <v>55</v>
+      </c>
+      <c r="V63" t="n">
+        <v>48.37895</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-65.22886</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Lac Phooey</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gold, Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>13</v>
+      </c>
+      <c r="T64" t="n">
+        <v>325</v>
+      </c>
+      <c r="U64" t="n">
+        <v>55</v>
+      </c>
+      <c r="V64" t="n">
+        <v>49.32384</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-75.02628</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lac Rond</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Palladium</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Palladium, Egp, Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>13</v>
+      </c>
+      <c r="T65" t="n">
+        <v>325</v>
+      </c>
+      <c r="U65" t="n">
+        <v>55</v>
+      </c>
+      <c r="V65" t="n">
+        <v>55.28891</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-65.74114</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Dussault</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Silver, Copper, Zinc, Manganese</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="T66" t="n">
+        <v>150</v>
+      </c>
+      <c r="U66" t="n">
+        <v>55</v>
+      </c>
+      <c r="V66" t="n">
+        <v>46.00535</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-71.70357</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pio - Filons Est et Ouest</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>325</v>
+      </c>
+      <c r="U67" t="n">
+        <v>55</v>
+      </c>
+      <c r="V67" t="n">
+        <v>58.96701</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-69.59563</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Franelle</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cu 60%, Ag 43.49 g/t</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>13</v>
+      </c>
+      <c r="T68" t="n">
+        <v>325</v>
+      </c>
+      <c r="U68" t="n">
+        <v>55</v>
+      </c>
+      <c r="V68" t="n">
+        <v>55.55824</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-67.34804</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lac Retty - Lac Pogo</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>13</v>
+      </c>
+      <c r="T69" t="n">
+        <v>325</v>
+      </c>
+      <c r="U69" t="n">
+        <v>55</v>
+      </c>
+      <c r="V69" t="n">
+        <v>55.23261</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-66.16073</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lac Walsh-Ouest</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Nickel, Copper</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Cu 3.05%, Ni 0.67%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>13</v>
+      </c>
+      <c r="T70" t="n">
+        <v>325</v>
+      </c>
+      <c r="U70" t="n">
+        <v>55</v>
+      </c>
+      <c r="V70" t="n">
+        <v>55.15269</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-66.35399</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lac Retty - Lac Bleu</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Niobium</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>13</v>
+      </c>
+      <c r="T71" t="n">
+        <v>325</v>
+      </c>
+      <c r="U71" t="n">
+        <v>55</v>
+      </c>
+      <c r="V71" t="n">
+        <v>55.22879</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-66.12246</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X71"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V2" t="n">
-        <v>49.01028</v>
+        <v>45.3192</v>
       </c>
       <c r="W2" t="n">
-        <v>-66.00369999999999</v>
+        <v>-71.92023</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>45.3192</v>
+        <v>53.40779</v>
       </c>
       <c r="W3" t="n">
-        <v>-71.92023</v>
+        <v>-77.28636</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Gold, Tungsten, Lead, Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>48.09296</v>
+        <v>53.39458</v>
       </c>
       <c r="W4" t="n">
-        <v>-66.78681</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>48.23154</v>
+        <v>49.82919</v>
       </c>
       <c r="W5" t="n">
-        <v>-66.80576000000001</v>
+        <v>-70.58076</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.78784</v>
+        <v>49.84595</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.08529</v>
+        <v>-70.57626</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amaruk</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>59.60263</v>
+        <v>49.83681</v>
       </c>
       <c r="W7" t="n">
-        <v>-74.86282</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Lac Viking</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>49.84595</v>
+        <v>47.20549</v>
       </c>
       <c r="W8" t="n">
-        <v>-70.57626</v>
+        <v>-72.45211999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
         </is>
       </c>
     </row>
@@ -1116,22 +1116,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lead, Molybdenum, Copper, Zinc, Silver</t>
+          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1168,23 +1168,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>45.99171</v>
+        <v>53.39996</v>
       </c>
       <c r="W9" t="n">
-        <v>-71.70617</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Silver, Gold</t>
+          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1246,23 +1246,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>45.44828</v>
+        <v>53.39786</v>
       </c>
       <c r="W10" t="n">
-        <v>-72.1057</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>45.32873</v>
+        <v>53.35887</v>
       </c>
       <c r="W11" t="n">
-        <v>-72.47421</v>
+        <v>-77.31016</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Cobalt</t>
+          <t>Chromium, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>49.82919</v>
+        <v>53.38014</v>
       </c>
       <c r="W12" t="n">
-        <v>-70.58076</v>
+        <v>-77.28712</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>49.83681</v>
+        <v>53.40387</v>
       </c>
       <c r="W13" t="n">
-        <v>-70.57877999999999</v>
+        <v>-77.30118</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>45.03676</v>
+        <v>53.39936</v>
       </c>
       <c r="W14" t="n">
-        <v>-72.77243</v>
+        <v>-77.29407</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lead, Cadmium, Zinc, Gold, Copper, Silver</t>
+          <t>Palladium, Egp, Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.29835</v>
+        <v>53.34013</v>
       </c>
       <c r="W15" t="n">
-        <v>-72.31643</v>
+        <v>-77.32316</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Au 278.00 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>48.71945</v>
+        <v>52.1821</v>
       </c>
       <c r="W16" t="n">
-        <v>-78.33144</v>
+        <v>-76.70099999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>48.70382</v>
+        <v>50.64946</v>
       </c>
       <c r="W17" t="n">
-        <v>-78.25041</v>
+        <v>-75.04613999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Comtois NW</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>48.57696</v>
+        <v>49.18766</v>
       </c>
       <c r="W18" t="n">
-        <v>-78.14164</v>
+        <v>-77.31872</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rambo</t>
+          <t>Jedi</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 7.60 g/t</t>
+          <t>Au 11.50 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.93645</v>
+        <v>54.84385</v>
       </c>
       <c r="W19" t="n">
-        <v>-79.32689999999999</v>
+        <v>-69.86212</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zone Lynx</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 7.78 g/t</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>49.93762</v>
+        <v>58.23464</v>
       </c>
       <c r="W20" t="n">
-        <v>-79.3579</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3915</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>45.42257</v>
+        <v>53.41679</v>
       </c>
       <c r="W21" t="n">
-        <v>-70.92541</v>
+        <v>-77.27167</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,17 +2140,17 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc, Copper</t>
+          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>45.42731</v>
+        <v>53.39256</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.92610999999999</v>
+        <v>-77.43714</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Filon Baker (Lac Arseneault)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Lead, Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>45.40513</v>
+        <v>48.37895</v>
       </c>
       <c r="W23" t="n">
-        <v>-70.9376</v>
+        <v>-65.22886</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>45.45582</v>
+        <v>53.43724</v>
       </c>
       <c r="W24" t="n">
-        <v>-70.90786</v>
+        <v>-75.04334</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Sond. DDH-20-2023</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>45.44349</v>
+        <v>46.36809</v>
       </c>
       <c r="W25" t="n">
-        <v>-70.91244</v>
+        <v>-73.97731</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>46W</t>
+          <t>Perch River</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Zinc, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
+          <t>Cu 9.06%, Ag 19.20 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>48.29961</v>
+        <v>50.33998</v>
       </c>
       <c r="W26" t="n">
-        <v>-67.12675</v>
+        <v>-73.71023</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Josselin-Tonnancourt (Greenland)</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper</t>
+          <t>Copper, Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 121.80 g/t, Cu 20%, Zn 13.1%, Ag 130.40 g/t</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>48.86335</v>
+        <v>49.78784</v>
       </c>
       <c r="W27" t="n">
-        <v>-76.99204</v>
+        <v>-77.08529</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3877</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ouf</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Ag 204.00 g/t, Zn 8.7%, Pb 1.6%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>53.90478</v>
+        <v>45.42257</v>
       </c>
       <c r="W28" t="n">
-        <v>-74.69878</v>
+        <v>-70.92541</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3841</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Fraser (Zones 3, 4 &amp; 5)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>52.64108</v>
+        <v>48.32289</v>
       </c>
       <c r="W29" t="n">
-        <v>-75.67010999999999</v>
+        <v>-67.05</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gémini - B (Zone à cuivre)</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 3.78%, Ag 130.00 g/t, Au 1.38 g/t, Zn 3.87%</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>49.38069</v>
+        <v>48.33048</v>
       </c>
       <c r="W30" t="n">
-        <v>-79.25882</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4012</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gémini - A Nord</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 6.37%, Au 2.68 g/t, Zn 8.1%, Ag 5.06 g/t</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.43645</v>
+        <v>48.09296</v>
       </c>
       <c r="W31" t="n">
-        <v>-79.26394999999999</v>
+        <v>-66.78681</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4009</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gémini - A sud</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 3.43 g/t, Ag 6.20 g/t</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>49.42712</v>
+        <v>48.23154</v>
       </c>
       <c r="W32" t="n">
-        <v>-79.27181</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4008</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -2988,22 +2988,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gémini - B (Amas SF zincifère)</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lead, Gold, Copper, Silver, Zinc</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 2.59 g/t, Cu 1.8%, Ag 118.80 g/t, Zn 2.98%, Pb 2.29%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>49.38378</v>
+        <v>48.37403</v>
       </c>
       <c r="W33" t="n">
-        <v>-79.25754000000001</v>
+        <v>-65.44089</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4004</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>ELR-16-002</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Au 9.13 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>48.33048</v>
+        <v>52.67859</v>
       </c>
       <c r="W34" t="n">
-        <v>-67.01985999999999</v>
+        <v>-76.30803</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lac Foubert</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 6.1%, Au 5.52 g/t, Mo 0.448%, Ag 38.10 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.80466</v>
+        <v>45.43568</v>
       </c>
       <c r="W35" t="n">
-        <v>-79.28044</v>
+        <v>-70.91788</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3927</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Claims Peacock</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 7.50 g/t</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>49.16788</v>
+        <v>45.43447</v>
       </c>
       <c r="W36" t="n">
-        <v>-78.43522</v>
+        <v>-70.9088</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Monts Peacock-Sud</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Copper, Nickel, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 2.77%, Au 1.06 g/t, Ni 0.73%, Ag 14.10 g/t</t>
+          <t>Au 8.48 g/t, Cu 2.31%, Ag 10.40 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>49.20789</v>
+        <v>49.11452</v>
       </c>
       <c r="W37" t="n">
-        <v>-78.41656999999999</v>
+        <v>-75.12036999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4030</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=45470</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fraser (Zones 3, 4 &amp; 5)</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U38" t="n">
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>48.32289</v>
+        <v>48.32328</v>
       </c>
       <c r="W38" t="n">
-        <v>-67.05</v>
+        <v>-79.44637</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>46.26532</v>
+        <v>45.03676</v>
       </c>
       <c r="W39" t="n">
-        <v>-71.28788</v>
+        <v>-72.77243</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LA-93-04</t>
+          <t>Huckleberry</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 36.07 g/t</t>
+          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Ag 26.60 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>49.55796</v>
+        <v>55.78035</v>
       </c>
       <c r="W40" t="n">
-        <v>-75.37448000000001</v>
+        <v>-66.95337000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sond. LF-93-03</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>49.5436</v>
+        <v>49.24734</v>
       </c>
       <c r="W41" t="n">
-        <v>-75.41676</v>
+        <v>-71.98866</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Mina-Guercheville</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 20.57 g/t</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.54166</v>
+        <v>53.48752</v>
       </c>
       <c r="W42" t="n">
-        <v>-75.33825</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fenton-Sud</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Gold, Copper</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 53.08 g/t, Ag 53.00 g/t, Zn 1.96%, Cu 0.23%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>49.51684</v>
+        <v>46.26109</v>
       </c>
       <c r="W43" t="n">
-        <v>-75.36571000000001</v>
+        <v>-71.22866</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3589</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac Lapointe-SE</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 3.12 g/t, Cu 1.05%, Ag 3.70 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>49.5341</v>
+        <v>46.27176</v>
       </c>
       <c r="W44" t="n">
-        <v>-75.44531000000001</v>
+        <v>-71.28612</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3587</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3924,22 +3924,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>46.36809</v>
+        <v>46.265</v>
       </c>
       <c r="W45" t="n">
-        <v>-73.97731</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lac Mina-Est</t>
+          <t>Obamska</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Nickel, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 2.63 g/t, Cu 1.35%, Zn 1.57%, Ag 6.90 g/t, Ni 0.02%</t>
+          <t>Au 9.50 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>49.5435</v>
+        <v>50.8353</v>
       </c>
       <c r="W46" t="n">
-        <v>-75.32167</v>
+        <v>-78.66648000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3592</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
         </is>
       </c>
     </row>
@@ -4080,11 +4080,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>46.265</v>
+        <v>56.40258</v>
       </c>
       <c r="W47" t="n">
-        <v>-71.21259999999999</v>
+        <v>-67.9023</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Chibtown</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>46.27176</v>
+        <v>56.39152</v>
       </c>
       <c r="W48" t="n">
-        <v>-71.28612</v>
+        <v>-67.87103</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Lac Barlow</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>46.26265</v>
+        <v>49.94431</v>
       </c>
       <c r="W49" t="n">
-        <v>-71.21769</v>
+        <v>-74.71456000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Lac Marcaut</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>46.26109</v>
+        <v>51.08117</v>
       </c>
       <c r="W50" t="n">
-        <v>-71.22866</v>
+        <v>-77.6185</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fenton 98-18</t>
+          <t>Lullwitz-Kaeppeli</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Ir, Zr, Gallium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 5.47 g/t</t>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>49.51092</v>
+        <v>47.76432</v>
       </c>
       <c r="W51" t="n">
-        <v>-75.36535000000001</v>
+        <v>-70.46635000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>45.43447</v>
+        <v>46.26265</v>
       </c>
       <c r="W52" t="n">
-        <v>-70.9088</v>
+        <v>-71.21769</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>45.43568</v>
+        <v>46.26532</v>
       </c>
       <c r="W53" t="n">
-        <v>-70.91788</v>
+        <v>-71.28788</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lepage No 2</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Antimony</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>48.33322</v>
+        <v>48.31932</v>
       </c>
       <c r="W54" t="n">
-        <v>-66.99834</v>
+        <v>-64.9713</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Robidoux-appalaches</t>
+          <t>Timtu</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,17 +4714,17 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc</t>
+          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>48.35381</v>
+        <v>61.43006</v>
       </c>
       <c r="W55" t="n">
-        <v>-65.56434</v>
+        <v>-74.84983</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Getty</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,17 +4792,17 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>49.79699</v>
+        <v>61.39535</v>
       </c>
       <c r="W56" t="n">
-        <v>-75.81529</v>
+        <v>-75.00066</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Umex-2</t>
+          <t>Lac Rivon-Ouest</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Zinc, Molybdenum, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
+          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4912,23 +4912,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>49.81674</v>
+        <v>51.72313</v>
       </c>
       <c r="W57" t="n">
-        <v>-75.52503</v>
+        <v>-72.79697</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GD-32</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Au 4.40 g/t</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>49.49854</v>
+        <v>52.21818</v>
       </c>
       <c r="W58" t="n">
-        <v>-75.14399</v>
+        <v>-77.45902</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3646</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Sylvie</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5026,17 +5026,17 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Au 11.00 g/t, Cu 3.3%</t>
+          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>49.49222</v>
+        <v>61.39737</v>
       </c>
       <c r="W59" t="n">
-        <v>-75.32478999999999</v>
+        <v>-74.97753</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3643</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Drouet</t>
+          <t>Relique</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t</t>
+          <t>Au 10.40 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>49.49319</v>
+        <v>49.61809</v>
       </c>
       <c r="W60" t="n">
-        <v>-75.12523</v>
+        <v>-75.69525</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2962</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rosembaum</t>
+          <t>Lartic Est</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5224,23 +5224,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T61" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U61" t="n">
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>49.50469</v>
+        <v>48.173</v>
       </c>
       <c r="W61" t="n">
-        <v>-75.32402999999999</v>
+        <v>-78.14212999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
         </is>
       </c>
     </row>
@@ -5250,22 +5250,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Train No 4 (Lac Crabe)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 3.71%, U 0.07%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>48.37403</v>
+        <v>56.39584</v>
       </c>
       <c r="W62" t="n">
-        <v>-65.44089</v>
+        <v>-68.39176999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Filon Baker (Lac Arseneault)</t>
+          <t>SGR-09</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Lead, Copper</t>
+          <t>Uranium, Gold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+          <t>Au 3.31 g/t, U 0.11%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5389,14 +5389,14 @@
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>48.37895</v>
+        <v>56.43951</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.22886</v>
+        <v>-68.10245999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lac Phooey</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Uranium, Gold, Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,560 +5467,14 @@
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>49.32384</v>
+        <v>56.43038</v>
       </c>
       <c r="W64" t="n">
-        <v>-75.02628</v>
+        <v>-68.09914000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Lac Rond</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Palladium</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Palladium, Egp, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>13</v>
-      </c>
-      <c r="T65" t="n">
-        <v>325</v>
-      </c>
-      <c r="U65" t="n">
-        <v>55</v>
-      </c>
-      <c r="V65" t="n">
-        <v>55.28891</v>
-      </c>
-      <c r="W65" t="n">
-        <v>-65.74114</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Dussault</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Silver, Copper, Zinc, Manganese</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>6</v>
-      </c>
-      <c r="T66" t="n">
-        <v>150</v>
-      </c>
-      <c r="U66" t="n">
-        <v>55</v>
-      </c>
-      <c r="V66" t="n">
-        <v>46.00535</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-71.70357</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Pio - Filons Est et Ouest</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Cobalt, Silver</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Cu 9.86%, Ni 2.49%, Pd 1.81 g/t, Ag 21.20 g/t, Pt 0.61 g/t</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>13</v>
-      </c>
-      <c r="T67" t="n">
-        <v>325</v>
-      </c>
-      <c r="U67" t="n">
-        <v>55</v>
-      </c>
-      <c r="V67" t="n">
-        <v>58.96701</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-69.59563</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1587</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Franelle</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="n">
-        <v>13</v>
-      </c>
-      <c r="T68" t="n">
-        <v>325</v>
-      </c>
-      <c r="U68" t="n">
-        <v>55</v>
-      </c>
-      <c r="V68" t="n">
-        <v>55.55824</v>
-      </c>
-      <c r="W68" t="n">
-        <v>-67.34804</v>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Lac Retty - Lac Pogo</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Gold, Platinum, Palladium, Egp, Nickel, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="n">
-        <v>13</v>
-      </c>
-      <c r="T69" t="n">
-        <v>325</v>
-      </c>
-      <c r="U69" t="n">
-        <v>55</v>
-      </c>
-      <c r="V69" t="n">
-        <v>55.23261</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-66.16073</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Lac Walsh-Ouest</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>13</v>
-      </c>
-      <c r="T70" t="n">
-        <v>325</v>
-      </c>
-      <c r="U70" t="n">
-        <v>55</v>
-      </c>
-      <c r="V70" t="n">
-        <v>55.15269</v>
-      </c>
-      <c r="W70" t="n">
-        <v>-66.35399</v>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Lac Retty - Lac Bleu</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Niobium</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>13</v>
-      </c>
-      <c r="T71" t="n">
-        <v>325</v>
-      </c>
-      <c r="U71" t="n">
-        <v>55</v>
-      </c>
-      <c r="V71" t="n">
-        <v>55.22879</v>
-      </c>
-      <c r="W71" t="n">
-        <v>-66.12246</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Croix-3</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>53.40779</v>
+        <v>49.05483</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.28636</v>
+        <v>-75.39637999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Lead, Copper</t>
+          <t>Copper, Nickel, Palladium, Cobalt, Egp</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>53.39458</v>
+        <v>58.23464</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.44683999999999</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 21.70 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.82919</v>
+        <v>57.94973</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.58076</v>
+        <v>-69.51281</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.84595</v>
+        <v>49.82919</v>
       </c>
       <c r="W6" t="n">
-        <v>-70.57626</v>
+        <v>-70.58076</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lac Viking</t>
+          <t>Lac Fecteau Est</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
+          <t>Au 8.80 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>47.20549</v>
+        <v>49.03096</v>
       </c>
       <c r="W8" t="n">
-        <v>-72.45211999999999</v>
+        <v>-75.24721</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>53.39996</v>
+        <v>48.31932</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.33163999999999</v>
+        <v>-64.9713</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>53.39786</v>
+        <v>49.84595</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.30625000000001</v>
+        <v>-70.57626</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Golden Butterfly</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Iron, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,23 +1324,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>53.35887</v>
+        <v>51.99697</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.31016</v>
+        <v>-75.22655</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Copper, Silver</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.38014</v>
+        <v>51.6436</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.28712</v>
+        <v>-67.33749</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,17 +1438,17 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.40387</v>
+        <v>45.42731</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.30118</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
+          <t>Lead, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.39936</v>
+        <v>45.40513</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.29407</v>
+        <v>-70.9376</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper, Silver</t>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.34013</v>
+        <v>45.43447</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.32316</v>
+        <v>-70.9088</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 278.00 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>52.1821</v>
+        <v>45.43568</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.70099999999999</v>
+        <v>-70.91788</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 7.60 g/t</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>50.64946</v>
+        <v>49.79699</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.04613999999999</v>
+        <v>-75.81529</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Comtois NW</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>49.18766</v>
+        <v>45.45582</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.31872</v>
+        <v>-70.90786</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jedi</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 11.50 g/t</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>54.84385</v>
+        <v>45.44349</v>
       </c>
       <c r="W19" t="n">
-        <v>-69.86212</v>
+        <v>-70.91244</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>58.23464</v>
+        <v>45.42257</v>
       </c>
       <c r="W20" t="n">
-        <v>-69.92364000000001</v>
+        <v>-70.92541</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Gold, Arsenic</t>
+          <t>Silver, Copper, Manganese, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>53.41679</v>
+        <v>46.00535</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.27167</v>
+        <v>-71.70357</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>53.39256</v>
+        <v>48.09296</v>
       </c>
       <c r="W22" t="n">
-        <v>-77.43714</v>
+        <v>-66.78681</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Filon Baker (Lac Arseneault)</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc, Copper</t>
+          <t>Gold, Silver, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>48.37895</v>
+        <v>49.78784</v>
       </c>
       <c r="W23" t="n">
-        <v>-65.22886</v>
+        <v>-77.08529</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>53.43724</v>
+        <v>45.03676</v>
       </c>
       <c r="W24" t="n">
-        <v>-75.04334</v>
+        <v>-72.77243</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>46.36809</v>
+        <v>46.26109</v>
       </c>
       <c r="W25" t="n">
-        <v>-73.97731</v>
+        <v>-71.22866</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Perch River</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 9.06%, Ag 19.20 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>50.33998</v>
+        <v>46.26265</v>
       </c>
       <c r="W26" t="n">
-        <v>-73.71023</v>
+        <v>-71.21769</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>49.78784</v>
+        <v>46.26532</v>
       </c>
       <c r="W27" t="n">
-        <v>-77.08529</v>
+        <v>-71.28788</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Lac Viking</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Zinc, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>45.42257</v>
+        <v>47.20549</v>
       </c>
       <c r="W28" t="n">
-        <v>-70.92541</v>
+        <v>-72.45211999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fraser (Zones 3, 4 &amp; 5)</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>48.32289</v>
+        <v>46.27176</v>
       </c>
       <c r="W29" t="n">
-        <v>-67.05</v>
+        <v>-71.28612</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>48.33048</v>
+        <v>46.265</v>
       </c>
       <c r="W30" t="n">
-        <v>-67.01985999999999</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2832,11 +2832,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Silver, Zinc, Gold, Lead</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.09296</v>
+        <v>48.37403</v>
       </c>
       <c r="W31" t="n">
-        <v>-66.78681</v>
+        <v>-65.44089</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>Filon Baker (Lac Arseneault)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>48.23154</v>
+        <v>48.37895</v>
       </c>
       <c r="W32" t="n">
-        <v>-66.80576000000001</v>
+        <v>-65.22886</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
         </is>
       </c>
     </row>
@@ -2988,22 +2988,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Lartic Est</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,23 +3040,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U33" t="n">
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>48.37403</v>
+        <v>48.173</v>
       </c>
       <c r="W33" t="n">
-        <v>-65.44089</v>
+        <v>-78.14212999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ELR-16-002</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 9.13 g/t</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>52.67859</v>
+        <v>55.15269</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.30803</v>
+        <v>-66.35399</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Lac Retty - Lac Bleu</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Niobium, Cobalt</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>45.43568</v>
+        <v>55.22879</v>
       </c>
       <c r="W35" t="n">
-        <v>-70.91788</v>
+        <v>-66.12246</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>45.43447</v>
+        <v>55.23261</v>
       </c>
       <c r="W36" t="n">
-        <v>-70.9088</v>
+        <v>-66.16073</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 8.48 g/t, Cu 2.31%, Ag 10.40 g/t</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>49.11452</v>
+        <v>48.70382</v>
       </c>
       <c r="W37" t="n">
-        <v>-75.12036999999999</v>
+        <v>-78.25041</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=45470</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -3378,22 +3378,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="U38" t="n">
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>48.32328</v>
+        <v>45.99171</v>
       </c>
       <c r="W38" t="n">
-        <v>-79.44637</v>
+        <v>-71.70617</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>45.03676</v>
+        <v>45.44828</v>
       </c>
       <c r="W39" t="n">
-        <v>-72.77243</v>
+        <v>-72.1057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huckleberry</t>
+          <t>Mont Opémiska No 1</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Ag 26.60 g/t</t>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>55.78035</v>
+        <v>49.95224</v>
       </c>
       <c r="W40" t="n">
-        <v>-66.95337000000001</v>
+        <v>-74.8797</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Amaruk</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,1817 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T41" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U41" t="n">
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>49.24734</v>
+        <v>59.60263</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.98866</v>
+        <v>-74.86282</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Galexis</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>13</v>
-      </c>
-      <c r="T42" t="n">
-        <v>325</v>
-      </c>
-      <c r="U42" t="n">
-        <v>55</v>
-      </c>
-      <c r="V42" t="n">
-        <v>53.48752</v>
-      </c>
-      <c r="W42" t="n">
-        <v>-75.33392000000001</v>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Foy</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="n">
-        <v>13</v>
-      </c>
-      <c r="T43" t="n">
-        <v>325</v>
-      </c>
-      <c r="U43" t="n">
-        <v>55</v>
-      </c>
-      <c r="V43" t="n">
-        <v>46.26109</v>
-      </c>
-      <c r="W43" t="n">
-        <v>-71.22866</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Coleraine</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="n">
-        <v>13</v>
-      </c>
-      <c r="T44" t="n">
-        <v>325</v>
-      </c>
-      <c r="U44" t="n">
-        <v>55</v>
-      </c>
-      <c r="V44" t="n">
-        <v>46.27176</v>
-      </c>
-      <c r="W44" t="n">
-        <v>-71.28612</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Copper, Uranium, Silver</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="n">
-        <v>13</v>
-      </c>
-      <c r="T45" t="n">
-        <v>325</v>
-      </c>
-      <c r="U45" t="n">
-        <v>55</v>
-      </c>
-      <c r="V45" t="n">
-        <v>46.265</v>
-      </c>
-      <c r="W45" t="n">
-        <v>-71.21259999999999</v>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Obamska</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Au 9.50 g/t</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="n">
-        <v>13</v>
-      </c>
-      <c r="T46" t="n">
-        <v>325</v>
-      </c>
-      <c r="U46" t="n">
-        <v>55</v>
-      </c>
-      <c r="V46" t="n">
-        <v>50.8353</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-78.66648000000001</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Delhi Pacific</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="n">
-        <v>13</v>
-      </c>
-      <c r="T47" t="n">
-        <v>325</v>
-      </c>
-      <c r="U47" t="n">
-        <v>55</v>
-      </c>
-      <c r="V47" t="n">
-        <v>56.40258</v>
-      </c>
-      <c r="W47" t="n">
-        <v>-67.9023</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Chibtown</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Cu 16.2%, Au 3.40 g/t, Ag 42.90 g/t</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="n">
-        <v>13</v>
-      </c>
-      <c r="T48" t="n">
-        <v>325</v>
-      </c>
-      <c r="U48" t="n">
-        <v>55</v>
-      </c>
-      <c r="V48" t="n">
-        <v>56.39152</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-67.87103</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4640</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Lac Barlow</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="n">
-        <v>13</v>
-      </c>
-      <c r="T49" t="n">
-        <v>325</v>
-      </c>
-      <c r="U49" t="n">
-        <v>55</v>
-      </c>
-      <c r="V49" t="n">
-        <v>49.94431</v>
-      </c>
-      <c r="W49" t="n">
-        <v>-74.71456000000001</v>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Lac Marcaut</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>13</v>
-      </c>
-      <c r="T50" t="n">
-        <v>325</v>
-      </c>
-      <c r="U50" t="n">
-        <v>55</v>
-      </c>
-      <c r="V50" t="n">
-        <v>51.08117</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-77.6185</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Lullwitz-Kaeppeli</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Gold, Ir, Zr, Gallium</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>13</v>
-      </c>
-      <c r="T51" t="n">
-        <v>325</v>
-      </c>
-      <c r="U51" t="n">
-        <v>55</v>
-      </c>
-      <c r="V51" t="n">
-        <v>47.76432</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-70.46635000000001</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Nutbrown</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="n">
-        <v>13</v>
-      </c>
-      <c r="T52" t="n">
-        <v>325</v>
-      </c>
-      <c r="U52" t="n">
-        <v>55</v>
-      </c>
-      <c r="V52" t="n">
-        <v>46.26265</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-71.21769</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Grondin</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="n">
-        <v>13</v>
-      </c>
-      <c r="T53" t="n">
-        <v>325</v>
-      </c>
-      <c r="U53" t="n">
-        <v>55</v>
-      </c>
-      <c r="V53" t="n">
-        <v>46.26532</v>
-      </c>
-      <c r="W53" t="n">
-        <v>-71.28788</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Hunt (Port Daniel No. 2)</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Cu 9.35%</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>13</v>
-      </c>
-      <c r="T54" t="n">
-        <v>325</v>
-      </c>
-      <c r="U54" t="n">
-        <v>55</v>
-      </c>
-      <c r="V54" t="n">
-        <v>48.31932</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-64.9713</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Timtu</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>13</v>
-      </c>
-      <c r="T55" t="n">
-        <v>325</v>
-      </c>
-      <c r="U55" t="n">
-        <v>55</v>
-      </c>
-      <c r="V55" t="n">
-        <v>61.43006</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-74.84983</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Getty</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Palladium</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>13</v>
-      </c>
-      <c r="T56" t="n">
-        <v>325</v>
-      </c>
-      <c r="U56" t="n">
-        <v>55</v>
-      </c>
-      <c r="V56" t="n">
-        <v>61.39535</v>
-      </c>
-      <c r="W56" t="n">
-        <v>-75.00066</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Lac Rivon-Ouest</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Zinc, Molybdenum, Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>325</v>
-      </c>
-      <c r="U57" t="n">
-        <v>55</v>
-      </c>
-      <c r="V57" t="n">
-        <v>51.72313</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-72.79697</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Lidge</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Silver, Copper, Gold, Arsenic</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>325</v>
-      </c>
-      <c r="U58" t="n">
-        <v>55</v>
-      </c>
-      <c r="V58" t="n">
-        <v>52.21818</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-77.45902</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Sylvie</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>13</v>
-      </c>
-      <c r="T59" t="n">
-        <v>325</v>
-      </c>
-      <c r="U59" t="n">
-        <v>55</v>
-      </c>
-      <c r="V59" t="n">
-        <v>61.39737</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-74.97753</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Relique</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Au 10.40 g/t</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>13</v>
-      </c>
-      <c r="T60" t="n">
-        <v>325</v>
-      </c>
-      <c r="U60" t="n">
-        <v>55</v>
-      </c>
-      <c r="V60" t="n">
-        <v>49.61809</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-75.69525</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2962</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lartic Est</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Silver</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>6</v>
-      </c>
-      <c r="T61" t="n">
-        <v>150</v>
-      </c>
-      <c r="U61" t="n">
-        <v>55</v>
-      </c>
-      <c r="V61" t="n">
-        <v>48.173</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-78.14212999999999</v>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Train No 4 (Lac Crabe)</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Uranium, Copper</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Cu 3.71%, U 0.07%</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>325</v>
-      </c>
-      <c r="U62" t="n">
-        <v>55</v>
-      </c>
-      <c r="V62" t="n">
-        <v>56.39584</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-68.39176999999999</v>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>SGR-09</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Uranium, Gold</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>13</v>
-      </c>
-      <c r="T63" t="n">
-        <v>325</v>
-      </c>
-      <c r="U63" t="n">
-        <v>55</v>
-      </c>
-      <c r="V63" t="n">
-        <v>56.43951</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-68.10245999999999</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Viking</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Uranium, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>13</v>
-      </c>
-      <c r="T64" t="n">
-        <v>325</v>
-      </c>
-      <c r="U64" t="n">
-        <v>55</v>
-      </c>
-      <c r="V64" t="n">
-        <v>56.43038</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-68.09914000000001</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:X48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Croix-3</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>49.05483</v>
+        <v>49.84595</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.39637999999999</v>
+        <v>-70.57626</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Palladium, Cobalt, Egp</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>58.23464</v>
+        <v>49.63941</v>
       </c>
       <c r="W4" t="n">
-        <v>-69.92364000000001</v>
+        <v>-76.90893</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lac Dupuy-Est / Golden Tooth / GTN / SP</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Tungsten, Tellurium, Arsenic, Copper, Silver, Cobalt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 21.70 g/t</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>57.94973</v>
+        <v>59.80634</v>
       </c>
       <c r="W5" t="n">
-        <v>-69.51281</v>
+        <v>-75.01831</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2666</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Drouet</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 6.00 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.82919</v>
+        <v>49.49319</v>
       </c>
       <c r="W6" t="n">
-        <v>-70.58076</v>
+        <v>-75.12523</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lac Fecteau Est</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>49.03096</v>
+        <v>49.82919</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.24721</v>
+        <v>-70.58076</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Copper, Manganese, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1168,23 +1168,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U9" t="n">
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>48.31932</v>
+        <v>46.00535</v>
       </c>
       <c r="W9" t="n">
-        <v>-64.9713</v>
+        <v>-71.70357</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Lac Rond</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Egp, Palladium, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>49.84595</v>
+        <v>55.28891</v>
       </c>
       <c r="W10" t="n">
-        <v>-70.57626</v>
+        <v>-65.74114</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Golden Butterfly</t>
+          <t>Sond. PLP24-019</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Iron, Silver</t>
+          <t>Gold, Bismuth</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
+          <t>Au 4.76 g/t, Bi 0.1%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,23 +1324,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>51.99697</v>
+        <v>52.59612</v>
       </c>
       <c r="W11" t="n">
-        <v>-75.22655</v>
+        <v>-77.37366</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Robidoux-appalaches</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>51.6436</v>
+        <v>48.35381</v>
       </c>
       <c r="W12" t="n">
-        <v>-67.33749</v>
+        <v>-65.56434</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Lac Phooey</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,17 +1438,17 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>45.42731</v>
+        <v>49.32384</v>
       </c>
       <c r="W13" t="n">
-        <v>-70.92610999999999</v>
+        <v>-75.02628</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Lepage No 2</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Silver</t>
+          <t>Gold, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>45.40513</v>
+        <v>48.33322</v>
       </c>
       <c r="W14" t="n">
-        <v>-70.9376</v>
+        <v>-66.99834</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead, Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1636,23 +1636,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U15" t="n">
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.43447</v>
+        <v>48.32328</v>
       </c>
       <c r="W15" t="n">
-        <v>-70.9088</v>
+        <v>-79.44637</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>45.43568</v>
+        <v>52.03235</v>
       </c>
       <c r="W16" t="n">
-        <v>-70.91788</v>
+        <v>-69.13816</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1740,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zinc, Copper</t>
+          <t>Copper, Silver, Zinc, Gold, Lead</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>49.79699</v>
+        <v>48.37403</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.81529</v>
+        <v>-65.44089</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.45582</v>
+        <v>46.26109</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.90786</v>
+        <v>-71.22866</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>45.44349</v>
+        <v>46.26265</v>
       </c>
       <c r="W19" t="n">
-        <v>-70.91244</v>
+        <v>-71.21769</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.42257</v>
+        <v>45.03676</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.92541</v>
+        <v>-72.77243</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Copper, Manganese, Zinc</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>46.00535</v>
+        <v>47.86378</v>
       </c>
       <c r="W21" t="n">
-        <v>-71.70357</v>
+        <v>-67.38485</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>48.09296</v>
+        <v>47.99637</v>
       </c>
       <c r="W22" t="n">
-        <v>-66.78681</v>
+        <v>-67.11127</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Au 32.73 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>49.78784</v>
+        <v>53.51886</v>
       </c>
       <c r="W23" t="n">
-        <v>-77.08529</v>
+        <v>-76.60854</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>45.03676</v>
+        <v>45.42257</v>
       </c>
       <c r="W24" t="n">
-        <v>-72.77243</v>
+        <v>-70.92541</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>46.26109</v>
+        <v>45.42731</v>
       </c>
       <c r="W25" t="n">
-        <v>-71.22866</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
+          <t>Lead, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>46.26265</v>
+        <v>45.40513</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.21769</v>
+        <v>-70.9376</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Copper, Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>46.26532</v>
+        <v>45.45582</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.28788</v>
+        <v>-70.90786</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lac Viking</t>
+          <t>Sond. VER-21-06</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold, Silver</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 1.67 g/t, Zn 5.48%, Cu 0.68%, Ag 6.80 g/t</t>
+          <t>Au 2.61 g/t, Zn 1.57%, Cu 0.321%, Ag 11.50 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>47.20549</v>
+        <v>51.03789</v>
       </c>
       <c r="W28" t="n">
-        <v>-72.45211999999999</v>
+        <v>-77.71702000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3298</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=65174</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Umex-2</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>46.27176</v>
+        <v>49.81674</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.28612</v>
+        <v>-75.52503</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Rivière Pontois</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Gold, Copper, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>46.265</v>
+        <v>53.51426</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.21259999999999</v>
+        <v>-74.51608</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
         </is>
       </c>
     </row>
@@ -2832,11 +2832,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold, Lead</t>
+          <t>Copper, Egp, Palladium, Platinum, Nickel</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.37403</v>
+        <v>61.55073</v>
       </c>
       <c r="W31" t="n">
-        <v>-65.44089</v>
+        <v>-72.66555</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Filon Baker (Lac Arseneault)</t>
+          <t>G-H-2-79 (Hudbay Mining)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+          <t>Cu 3.26%, Ni 1.12%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>48.37895</v>
+        <v>51.50451</v>
       </c>
       <c r="W32" t="n">
-        <v>-65.22886</v>
+        <v>-67.92737</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3040,23 +3040,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>48.173</v>
+        <v>48.70382</v>
       </c>
       <c r="W33" t="n">
-        <v>-78.14212999999999</v>
+        <v>-78.25041</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lac Walsh-Ouest</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>55.15269</v>
+        <v>46.27176</v>
       </c>
       <c r="W34" t="n">
-        <v>-66.35399</v>
+        <v>-71.28612</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Bleu</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Niobium, Cobalt</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>55.22879</v>
+        <v>46.26532</v>
       </c>
       <c r="W35" t="n">
-        <v>-66.12246</v>
+        <v>-71.28788</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Pogo</t>
+          <t>Jedi</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold, Silver</t>
+          <t>Gold, Silver, Copper, Zinc, Molybdenum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+          <t>Au 11.50 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>55.23261</v>
+        <v>54.84385</v>
       </c>
       <c r="W36" t="n">
-        <v>-66.16073</v>
+        <v>-69.86212</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>48.70382</v>
+        <v>48.09296</v>
       </c>
       <c r="W37" t="n">
-        <v>-78.25041</v>
+        <v>-66.78681</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -3378,22 +3378,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Lead, Zinc, Silver</t>
+          <t>Tungsten, Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>45.99171</v>
+        <v>53.39458</v>
       </c>
       <c r="W38" t="n">
-        <v>-71.70617</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold, Silver</t>
+          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>45.44828</v>
+        <v>53.39256</v>
       </c>
       <c r="W39" t="n">
-        <v>-72.1057</v>
+        <v>-77.43714</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>49.95224</v>
+        <v>53.41679</v>
       </c>
       <c r="W40" t="n">
-        <v>-74.8797</v>
+        <v>-77.27167</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amaruk</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,569 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>59.60263</v>
+        <v>53.40387</v>
       </c>
       <c r="W41" t="n">
-        <v>-74.86282</v>
+        <v>-77.30118</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mistass</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Iron, Cobalt</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>13</v>
+      </c>
+      <c r="T42" t="n">
+        <v>325</v>
+      </c>
+      <c r="U42" t="n">
+        <v>55</v>
+      </c>
+      <c r="V42" t="n">
+        <v>49.24734</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-71.98866</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Dead Mouse extension</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Au 18.36 g/t</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="n">
+        <v>325</v>
+      </c>
+      <c r="U43" t="n">
+        <v>55</v>
+      </c>
+      <c r="V43" t="n">
+        <v>53.61747</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-71.97382</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>de l'Ours</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Au 27.00 g/t</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" t="n">
+        <v>325</v>
+      </c>
+      <c r="U44" t="n">
+        <v>55</v>
+      </c>
+      <c r="V44" t="n">
+        <v>53.61441</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-71.97407</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Zone Nicholson (Puits Racicot)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="n">
+        <v>325</v>
+      </c>
+      <c r="U45" t="n">
+        <v>55</v>
+      </c>
+      <c r="V45" t="n">
+        <v>45.29835</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-72.31643</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H-1429-046</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>12</v>
+      </c>
+      <c r="T46" t="n">
+        <v>300</v>
+      </c>
+      <c r="U46" t="n">
+        <v>55</v>
+      </c>
+      <c r="V46" t="n">
+        <v>50.85296</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-76.47398</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mine Capelton (Albert)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>300 kt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>13</v>
+      </c>
+      <c r="T47" t="n">
+        <v>325</v>
+      </c>
+      <c r="U47" t="n">
+        <v>55</v>
+      </c>
+      <c r="V47" t="n">
+        <v>45.32298</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-71.90649999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Grand-Prix Zone 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Cu 10.1%, Au 1.41 g/t, Ag 39.30 g/t, Zn 1.56%, Pb 0.236%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>13</v>
+      </c>
+      <c r="T48" t="n">
+        <v>325</v>
+      </c>
+      <c r="U48" t="n">
+        <v>55</v>
+      </c>
+      <c r="V48" t="n">
+        <v>45.52677</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-71.75227</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5602</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X48"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>49.84595</v>
+        <v>45.43447</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.57626</v>
+        <v>-70.9088</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Mine Capelton (Albert)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,17 +736,17 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -757,12 +757,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>300 kt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>49.63941</v>
+        <v>45.32298</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.90893</v>
+        <v>-71.90649999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Mine Aldermac Moulton Hill</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,17 +814,17 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Tungsten, Tellurium, Arsenic, Copper, Silver, Cobalt</t>
+          <t>Silver, Gold, Copper, Lead, Zinc, Molybdenum, Cadmium, Barium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -835,12 +835,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>871 kt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>59.80634</v>
+        <v>45.40941</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.01831</v>
+        <v>-71.81791</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Drouet</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.49319</v>
+        <v>49.82919</v>
       </c>
       <c r="W6" t="n">
-        <v>-75.12523</v>
+        <v>-70.58076</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3640</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>49.82919</v>
+        <v>49.84595</v>
       </c>
       <c r="W8" t="n">
-        <v>-70.58076</v>
+        <v>-70.57626</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Silver, Copper, Manganese, Zinc</t>
+          <t>Gold, Copper, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1168,23 +1168,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>46.00535</v>
+        <v>47.99637</v>
       </c>
       <c r="W9" t="n">
-        <v>-71.70357</v>
+        <v>-67.11127</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lac Rond</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Egp, Palladium, Copper</t>
+          <t>Lead, Silver, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>55.28891</v>
+        <v>47.86378</v>
       </c>
       <c r="W10" t="n">
-        <v>-65.74114</v>
+        <v>-67.38485</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sond. PLP24-019</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Bismuth</t>
+          <t>Silver, Gold, Copper, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 4.76 g/t, Bi 0.1%</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>52.59612</v>
+        <v>50.31401</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.37366</v>
+        <v>-62.73908</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67125</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1350,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robidoux-appalaches</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 92.00 g/t, Ag 150.00 g/t, Zn 0.728%, Pb 1.34%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>48.35381</v>
+        <v>48.37403</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.56434</v>
+        <v>-65.44089</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3583</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lac Phooey</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>49.32384</v>
+        <v>46.26109</v>
       </c>
       <c r="W13" t="n">
-        <v>-75.02628</v>
+        <v>-71.22866</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lepage No 2</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Antimony, Arsenic</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 64.00 g/t, Sb 0.3%, As 13.6%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>48.33322</v>
+        <v>46.26265</v>
       </c>
       <c r="W14" t="n">
-        <v>-66.99834</v>
+        <v>-71.21769</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3584</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1636,23 +1636,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>48.32328</v>
+        <v>46.26532</v>
       </c>
       <c r="W15" t="n">
-        <v>-79.44637</v>
+        <v>-71.28788</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Guettard-Nord</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>52.03235</v>
+        <v>50.01478</v>
       </c>
       <c r="W16" t="n">
-        <v>-69.13816</v>
+        <v>-75.39858</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1740,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold, Lead</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>48.37403</v>
+        <v>45.45582</v>
       </c>
       <c r="W17" t="n">
-        <v>-65.44089</v>
+        <v>-70.90786</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
+          <t>Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>46.26109</v>
+        <v>45.40513</v>
       </c>
       <c r="W18" t="n">
-        <v>-71.22866</v>
+        <v>-70.9376</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>46.26265</v>
+        <v>46.27176</v>
       </c>
       <c r="W19" t="n">
-        <v>-71.21769</v>
+        <v>-71.28612</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Obamska</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 9.50 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.03676</v>
+        <v>50.8353</v>
       </c>
       <c r="W20" t="n">
-        <v>-72.77243</v>
+        <v>-78.66648000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Lullwitz-Kaeppeli</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Ir, Zr, Gallium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>47.86378</v>
+        <v>47.76432</v>
       </c>
       <c r="W21" t="n">
-        <v>-67.38485</v>
+        <v>-70.46635000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Lac Marcaut</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Zinc, Lead</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>47.99637</v>
+        <v>51.08117</v>
       </c>
       <c r="W22" t="n">
-        <v>-67.11127</v>
+        <v>-77.6185</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 32.73 g/t</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>53.51886</v>
+        <v>47.68996</v>
       </c>
       <c r="W23" t="n">
-        <v>-76.60854</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>45.42257</v>
+        <v>48.33048</v>
       </c>
       <c r="W24" t="n">
-        <v>-70.92541</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>46W</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,17 +2374,17 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Gold, Arsenic, Zinc, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>45.42731</v>
+        <v>48.29961</v>
       </c>
       <c r="W25" t="n">
-        <v>-70.92610999999999</v>
+        <v>-67.12675</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Silver</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>45.40513</v>
+        <v>45.44349</v>
       </c>
       <c r="W26" t="n">
-        <v>-70.9376</v>
+        <v>-70.91244</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Fraser (Zones 3, 4 &amp; 5)</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>45.45582</v>
+        <v>48.32289</v>
       </c>
       <c r="W27" t="n">
-        <v>-70.90786</v>
+        <v>-67.05</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
         </is>
       </c>
     </row>
@@ -2598,11 +2598,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sond. VER-21-06</t>
+          <t>Monarch - Veine 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 2.61 g/t, Zn 1.57%, Cu 0.321%, Ag 11.50 g/t</t>
+          <t>Au 83.00 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>51.03789</v>
+        <v>48.23207</v>
       </c>
       <c r="W28" t="n">
-        <v>-77.71702000000001</v>
+        <v>-79.41287</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=65174</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Umex-2</t>
+          <t>Perch River</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
+          <t>Cu 9.06%, Ag 19.20 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T29" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.81674</v>
+        <v>50.33998</v>
       </c>
       <c r="W29" t="n">
-        <v>-75.52503</v>
+        <v>-73.71023</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rivière Pontois</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Arsenic</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,23 +2806,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>53.51426</v>
+        <v>46.265</v>
       </c>
       <c r="W30" t="n">
-        <v>-74.51608</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,17 +2842,17 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Egp, Palladium, Platinum, Nickel</t>
+          <t>Lead, Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>61.55073</v>
+        <v>45.42731</v>
       </c>
       <c r="W31" t="n">
-        <v>-72.66555</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>G-H-2-79 (Hudbay Mining)</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 3.26%, Ni 1.12%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>51.50451</v>
+        <v>45.42257</v>
       </c>
       <c r="W32" t="n">
-        <v>-67.92737</v>
+        <v>-70.92541</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4136</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Kogaluc 4</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 5.60 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>48.70382</v>
+        <v>58.81552</v>
       </c>
       <c r="W33" t="n">
-        <v>-78.25041</v>
+        <v>-74.68685000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>46.27176</v>
+        <v>45.43568</v>
       </c>
       <c r="W34" t="n">
-        <v>-71.28612</v>
+        <v>-70.91788</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>46.26532</v>
+        <v>58.81627</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.28788</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jedi</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc, Molybdenum</t>
+          <t>Gold, Lead, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 11.50 g/t</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>54.84385</v>
+        <v>52.20175</v>
       </c>
       <c r="W36" t="n">
-        <v>-69.86212</v>
+        <v>-70.89798</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>48.09296</v>
+        <v>45.03676</v>
       </c>
       <c r="W37" t="n">
-        <v>-66.78681</v>
+        <v>-72.77243</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tungsten, Gold, Silver, Copper, Lead</t>
+          <t>Uranium, Gold, Copper</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>53.39458</v>
+        <v>56.43038</v>
       </c>
       <c r="W38" t="n">
-        <v>-77.44683999999999</v>
+        <v>-68.09914000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>SGR-09</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
+          <t>Uranium, Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Au 3.31 g/t, U 0.11%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>53.39256</v>
+        <v>56.43951</v>
       </c>
       <c r="W39" t="n">
-        <v>-77.43714</v>
+        <v>-68.10245999999999</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Train No 4 (Lac Crabe)</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Cu 3.71%, U 0.07%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>53.41679</v>
+        <v>56.39584</v>
       </c>
       <c r="W40" t="n">
-        <v>-77.27167</v>
+        <v>-68.39176999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T41" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U41" t="n">
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>53.40387</v>
+        <v>48.09296</v>
       </c>
       <c r="W41" t="n">
-        <v>-77.30118</v>
+        <v>-66.78681</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Lac Fecteau Est</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Iron, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 8.80 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.24734</v>
+        <v>49.03096</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.98866</v>
+        <v>-75.24721</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dead Mouse extension</t>
+          <t>Croix-3</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 18.36 g/t</t>
+          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>53.61747</v>
+        <v>49.05483</v>
       </c>
       <c r="W43" t="n">
-        <v>-71.97382</v>
+        <v>-75.39637999999999</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>de l'Ours</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Gold, Platinum, Palladium, Egp, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 27.00 g/t</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>53.61441</v>
+        <v>55.23261</v>
       </c>
       <c r="W44" t="n">
-        <v>-71.97407</v>
+        <v>-66.16073</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Rosembaum</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>45.29835</v>
+        <v>49.50469</v>
       </c>
       <c r="W45" t="n">
-        <v>-72.31643</v>
+        <v>-75.32402999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>Fenton 98-18</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+          <t>Au 5.47 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4054,23 +4054,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T46" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U46" t="n">
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>50.85296</v>
+        <v>49.51092</v>
       </c>
       <c r="W46" t="n">
-        <v>-76.47398</v>
+        <v>-75.36535000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>LA-93-04</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,17 +4090,17 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Au 36.07 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>45.32298</v>
+        <v>49.55796</v>
       </c>
       <c r="W47" t="n">
-        <v>-71.90649999999999</v>
+        <v>-75.37448000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Grand-Prix Zone 1</t>
+          <t>Sond. LF-93-03</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead, Gold</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 1.41 g/t, Ag 39.30 g/t, Zn 1.56%, Pb 0.236%</t>
+          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,482 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>45.52677</v>
+        <v>49.5436</v>
       </c>
       <c r="W48" t="n">
-        <v>-71.75227</v>
+        <v>-75.41676</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5602</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lac Mina-Est</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Zinc, Gold, Copper, Nickel, Silver</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Au 2.63 g/t, Cu 1.35%, Zn 1.57%, Ag 6.90 g/t, Ni 0.02%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="n">
+        <v>325</v>
+      </c>
+      <c r="U49" t="n">
+        <v>55</v>
+      </c>
+      <c r="V49" t="n">
+        <v>49.5435</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-75.32167</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3592</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lac Mina-Guercheville</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Au 20.57 g/t</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="n">
+        <v>325</v>
+      </c>
+      <c r="U50" t="n">
+        <v>55</v>
+      </c>
+      <c r="V50" t="n">
+        <v>49.54166</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-75.33825</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3591</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Amaruk</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="n">
+        <v>250</v>
+      </c>
+      <c r="U51" t="n">
+        <v>55</v>
+      </c>
+      <c r="V51" t="n">
+        <v>59.60263</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-74.86282</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sond. DDH-20-2023</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Iron, Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="n">
+        <v>325</v>
+      </c>
+      <c r="U52" t="n">
+        <v>55</v>
+      </c>
+      <c r="V52" t="n">
+        <v>46.36809</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-73.97731</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mont Opémiska No 1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>13</v>
+      </c>
+      <c r="T53" t="n">
+        <v>325</v>
+      </c>
+      <c r="U53" t="n">
+        <v>55</v>
+      </c>
+      <c r="V53" t="n">
+        <v>49.95224</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-74.8797</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Lartic Est</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Silver</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="n">
+        <v>250</v>
+      </c>
+      <c r="U54" t="n">
+        <v>55</v>
+      </c>
+      <c r="V54" t="n">
+        <v>48.173</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-78.14212999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X54"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Gold, Copper, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>45.43447</v>
+        <v>47.99637</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.9088</v>
+        <v>-67.11127</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,17 +736,17 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Lead, Silver, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -757,12 +757,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>45.32298</v>
+        <v>47.86378</v>
       </c>
       <c r="W4" t="n">
-        <v>-71.90649999999999</v>
+        <v>-67.38485</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,17 +814,17 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead, Zinc, Molybdenum, Cadmium, Barium</t>
+          <t>Copper, Nickel, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -835,12 +835,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>871 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>45.40941</v>
+        <v>49.82919</v>
       </c>
       <c r="W5" t="n">
-        <v>-71.81791</v>
+        <v>-70.58076</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Cobalt</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.82919</v>
+        <v>49.84595</v>
       </c>
       <c r="W6" t="n">
-        <v>-70.58076</v>
+        <v>-70.57626</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Silver, Gold, Copper, Lead</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>49.83681</v>
+        <v>50.31401</v>
       </c>
       <c r="W7" t="n">
-        <v>-70.57877999999999</v>
+        <v>-62.73908</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,23 +1090,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>49.84595</v>
+        <v>48.57696</v>
       </c>
       <c r="W8" t="n">
-        <v>-70.57626</v>
+        <v>-78.14164</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Verreault</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Zinc, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Cu 4.78%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>47.99637</v>
+        <v>48.71945</v>
       </c>
       <c r="W9" t="n">
-        <v>-67.11127</v>
+        <v>-78.33144</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold, Copper</t>
+          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>47.86378</v>
+        <v>53.39936</v>
       </c>
       <c r="W10" t="n">
-        <v>-67.38485</v>
+        <v>-77.29407</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>50.31401</v>
+        <v>48.70382</v>
       </c>
       <c r="W11" t="n">
-        <v>-62.73908</v>
+        <v>-78.25041</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -1350,22 +1350,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>48.37403</v>
+        <v>53.40387</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.44089</v>
+        <v>-77.30118</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>46.26109</v>
+        <v>49.83681</v>
       </c>
       <c r="W13" t="n">
-        <v>-71.22866</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Sylvie</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,17 +1516,17 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>46.26265</v>
+        <v>61.39737</v>
       </c>
       <c r="W14" t="n">
-        <v>-71.21769</v>
+        <v>-74.97753</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Timtu</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,17 +1594,17 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>46.26532</v>
+        <v>61.43006</v>
       </c>
       <c r="W15" t="n">
-        <v>-71.28788</v>
+        <v>-74.84983</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guettard-Nord</t>
+          <t>Getty</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,17 +1672,17 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
+          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1714,23 +1714,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>50.01478</v>
+        <v>61.39535</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.39858</v>
+        <v>-75.00066</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,17 +1750,17 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>45.45582</v>
+        <v>61.39368</v>
       </c>
       <c r="W17" t="n">
-        <v>-70.90786</v>
+        <v>-75.1713</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Destorbelle</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Au 8.20 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.40513</v>
+        <v>48.4465</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.9376</v>
+        <v>-78.85312999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>H-1429-046</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Copper, Gold, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>46.27176</v>
+        <v>50.85296</v>
       </c>
       <c r="W19" t="n">
-        <v>-71.28612</v>
+        <v>-76.47398</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Obamska</t>
+          <t>Mine Aldermac Moulton Hill</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,17 +1984,17 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Copper, Lead, Zinc, Molybdenum, Cadmium, Barium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>871 kt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 9.50 g/t</t>
+          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2026,23 +2026,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>50.8353</v>
+        <v>45.40941</v>
       </c>
       <c r="W20" t="n">
-        <v>-78.66648000000001</v>
+        <v>-71.81791</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
         </is>
       </c>
     </row>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lullwitz-Kaeppeli</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Ir, Zr, Gallium</t>
+          <t>Copper, Lead, Molybdenum, Zinc, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 27.44 g/t, Ga 0.0037%, Ir 0.00144%, Zr 0.12%</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>47.76432</v>
+        <v>45.99171</v>
       </c>
       <c r="W21" t="n">
-        <v>-70.46635000000001</v>
+        <v>-71.70617</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lac Marcaut</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 29.00 g/t, Ag 74.00 g/t</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>51.08117</v>
+        <v>52.17253</v>
       </c>
       <c r="W22" t="n">
-        <v>-77.6185</v>
+        <v>-76.55762</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4989</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>47.68996</v>
+        <v>60.2779</v>
       </c>
       <c r="W23" t="n">
-        <v>-76.66074999999999</v>
+        <v>-75.33311</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>48.33048</v>
+        <v>61.55073</v>
       </c>
       <c r="W24" t="n">
-        <v>-67.01985999999999</v>
+        <v>-72.66555</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>46W</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Zinc, Silver</t>
+          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>48.29961</v>
+        <v>53.39256</v>
       </c>
       <c r="W25" t="n">
-        <v>-67.12675</v>
+        <v>-77.43714</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Nickel, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>45.44349</v>
+        <v>45.44828</v>
       </c>
       <c r="W26" t="n">
-        <v>-70.91244</v>
+        <v>-72.1057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fraser (Zones 3, 4 &amp; 5)</t>
+          <t>Brompton Copper</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
+          <t>Copper, Silver, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
+          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>48.32289</v>
+        <v>45.48343</v>
       </c>
       <c r="W27" t="n">
-        <v>-67.05</v>
+        <v>-72.10835</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
         </is>
       </c>
     </row>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Monarch - Veine 1</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 83.00 g/t</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>48.23207</v>
+        <v>45.32873</v>
       </c>
       <c r="W28" t="n">
-        <v>-79.41287</v>
+        <v>-72.47421</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5219</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Perch River</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Lead, Cadmium, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 9.06%, Ag 19.20 g/t</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>50.33998</v>
+        <v>45.29835</v>
       </c>
       <c r="W29" t="n">
-        <v>-73.71023</v>
+        <v>-72.31643</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Silver, Gold, Tungsten, Lead, Copper</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>46.265</v>
+        <v>53.39458</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.21259999999999</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Umex-2</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,17 +2842,17 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc, Copper</t>
+          <t>Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T31" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U31" t="n">
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>45.42731</v>
+        <v>49.81674</v>
       </c>
       <c r="W31" t="n">
-        <v>-70.92610999999999</v>
+        <v>-75.52503</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
         </is>
       </c>
     </row>
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Zone 32 (Tonalite-Zone Veine)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>45.42257</v>
+        <v>53.5291</v>
       </c>
       <c r="W32" t="n">
-        <v>-70.92541</v>
+        <v>-76.56155</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kogaluc 4</t>
+          <t>Zone 32 (Mico-Milan)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 5.60 g/t</t>
+          <t>Au 72.69 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>58.81552</v>
+        <v>53.52891</v>
       </c>
       <c r="W33" t="n">
-        <v>-74.68685000000001</v>
+        <v>-76.56541</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4977</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
         </is>
       </c>
     </row>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>TRH-96-07</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Au 19.59 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>45.43568</v>
+        <v>53.52311</v>
       </c>
       <c r="W34" t="n">
-        <v>-70.91788</v>
+        <v>-76.61015</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Silver, Copper, Zinc, Manganese</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>58.81627</v>
+        <v>46.00535</v>
       </c>
       <c r="W35" t="n">
-        <v>-74.70458000000001</v>
+        <v>-71.70357</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Sond. LF-93-03</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Lead, Silver</t>
+          <t>Copper, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>52.20175</v>
+        <v>49.5436</v>
       </c>
       <c r="W36" t="n">
-        <v>-70.89798</v>
+        <v>-75.41676</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>45.03676</v>
+        <v>53.43724</v>
       </c>
       <c r="W37" t="n">
-        <v>-72.77243</v>
+        <v>-75.04334</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Fenton-Ouest</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Uranium, Gold, Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
+          <t>Au 19.17 g/t, Cu 0.72%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>56.43038</v>
+        <v>49.53598</v>
       </c>
       <c r="W38" t="n">
-        <v>-68.09914000000001</v>
+        <v>-75.42941</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22367</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SGR-09</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Uranium, Gold</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>56.43951</v>
+        <v>59.80634</v>
       </c>
       <c r="W39" t="n">
-        <v>-68.10245999999999</v>
+        <v>-75.01831</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Train No 4 (Lac Crabe)</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 3.71%, U 0.07%</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>56.39584</v>
+        <v>53.48752</v>
       </c>
       <c r="W40" t="n">
-        <v>-68.39176999999999</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Lac Shallow-Est</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Cu 4.4%, Ni 1.02%, Ag 7.89 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3664,23 +3664,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>48.09296</v>
+        <v>49.72004</v>
       </c>
       <c r="W41" t="n">
-        <v>-66.78681</v>
+        <v>-77.44344</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1470</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Fecteau Est</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.03096</v>
+        <v>52.1766</v>
       </c>
       <c r="W42" t="n">
-        <v>-75.24721</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Croix-3</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>49.05483</v>
+        <v>52.17024</v>
       </c>
       <c r="W43" t="n">
-        <v>-75.39637999999999</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Pogo</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Gold, Platinum, Palladium, Egp, Silver</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>55.23261</v>
+        <v>52.21818</v>
       </c>
       <c r="W44" t="n">
-        <v>-66.16073</v>
+        <v>-77.45902</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rosembaum</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Zn 4.16%, Cu 0.63%</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>49.50469</v>
+        <v>53.40779</v>
       </c>
       <c r="W45" t="n">
-        <v>-75.32402999999999</v>
+        <v>-77.28636</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3604</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fenton 98-18</t>
+          <t>Lac Rond</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium, Egp, Gold, Copper</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 5.47 g/t</t>
+          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>49.51092</v>
+        <v>55.28891</v>
       </c>
       <c r="W46" t="n">
-        <v>-75.36535000000001</v>
+        <v>-65.74114</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3601</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA-93-04</t>
+          <t>Lac Phooey</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Copper</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 36.07 g/t</t>
+          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>49.55796</v>
+        <v>49.32384</v>
       </c>
       <c r="W47" t="n">
-        <v>-75.37448000000001</v>
+        <v>-75.02628</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3600</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sond. LF-93-03</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
+          <t>Au 11.00 g/t, Cu 3.3%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>49.5436</v>
+        <v>49.49222</v>
       </c>
       <c r="W48" t="n">
-        <v>-75.41676</v>
+        <v>-75.32478999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3643</t>
         </is>
       </c>
     </row>
@@ -4236,11 +4236,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lac Mina-Est</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Copper, Nickel, Silver</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 2.63 g/t, Cu 1.35%, Zn 1.57%, Ag 6.90 g/t, Ni 0.02%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>49.5435</v>
+        <v>48.37403</v>
       </c>
       <c r="W49" t="n">
-        <v>-75.32167</v>
+        <v>-65.44089</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3592</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lac Mina-Guercheville</t>
+          <t>Mine Capelton (Albert)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,17 +4324,17 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I50" t="b">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>300 kt</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Au 20.57 g/t</t>
+          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>49.54166</v>
+        <v>45.32298</v>
       </c>
       <c r="W50" t="n">
-        <v>-75.33825</v>
+        <v>-71.90649999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Amaruk</t>
+          <t>Ferricrete</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Vanadium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Vanadium, Gold, Zinc</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+          <t>Au 280.30 g/t, V 0.158%, Zn 0.3%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,23 +4444,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>59.60263</v>
+        <v>57.51228</v>
       </c>
       <c r="W51" t="n">
-        <v>-74.86282</v>
+        <v>-69.26596000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3744</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4522,23 +4522,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U52" t="n">
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>46.36809</v>
+        <v>48.32328</v>
       </c>
       <c r="W52" t="n">
-        <v>-73.97731</v>
+        <v>-79.44637</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Lavallée Sud</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Au 4.50 g/t, Cu 0.398%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>49.95224</v>
+        <v>47.35591</v>
       </c>
       <c r="W53" t="n">
-        <v>-74.8797</v>
+        <v>-78.9842</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2359</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>Lavallée : Zone 39</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Au 14.75 g/t, Cu 0.83%, Ag 10.40 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,1895 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
         <v>55</v>
       </c>
       <c r="V54" t="n">
+        <v>47.37551</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-78.97857</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2360</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sond. Umex 132</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Cu 4%, Zn 6%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>13</v>
+      </c>
+      <c r="T55" t="n">
+        <v>325</v>
+      </c>
+      <c r="U55" t="n">
+        <v>55</v>
+      </c>
+      <c r="V55" t="n">
+        <v>49.79699</v>
+      </c>
+      <c r="W55" t="n">
+        <v>-75.81529</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mistass</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Iron, Copper, Nickel, Cobalt</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>13</v>
+      </c>
+      <c r="T56" t="n">
+        <v>325</v>
+      </c>
+      <c r="U56" t="n">
+        <v>55</v>
+      </c>
+      <c r="V56" t="n">
+        <v>49.24734</v>
+      </c>
+      <c r="W56" t="n">
+        <v>-71.98866</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>13</v>
+      </c>
+      <c r="T57" t="n">
+        <v>325</v>
+      </c>
+      <c r="U57" t="n">
+        <v>55</v>
+      </c>
+      <c r="V57" t="n">
+        <v>45.03676</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-72.77243</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>4930N-1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chromium, Nickel, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>13</v>
+      </c>
+      <c r="T58" t="n">
+        <v>325</v>
+      </c>
+      <c r="U58" t="n">
+        <v>55</v>
+      </c>
+      <c r="V58" t="n">
+        <v>53.38014</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-77.28712</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bonspot</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Silver, Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>13</v>
+      </c>
+      <c r="T59" t="n">
+        <v>325</v>
+      </c>
+      <c r="U59" t="n">
+        <v>55</v>
+      </c>
+      <c r="V59" t="n">
+        <v>53.41679</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-77.27167</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>13</v>
+      </c>
+      <c r="T60" t="n">
+        <v>325</v>
+      </c>
+      <c r="U60" t="n">
+        <v>55</v>
+      </c>
+      <c r="V60" t="n">
+        <v>53.39996</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-77.33163999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Palladium</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Palladium, Egp, Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>13</v>
+      </c>
+      <c r="T61" t="n">
+        <v>325</v>
+      </c>
+      <c r="U61" t="n">
+        <v>55</v>
+      </c>
+      <c r="V61" t="n">
+        <v>53.34013</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-77.32316</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Lac Menarik</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>13</v>
+      </c>
+      <c r="T62" t="n">
+        <v>325</v>
+      </c>
+      <c r="U62" t="n">
+        <v>55</v>
+      </c>
+      <c r="V62" t="n">
+        <v>53.39786</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-77.30625000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Lac Yasinski-NE</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>13</v>
+      </c>
+      <c r="T63" t="n">
+        <v>325</v>
+      </c>
+      <c r="U63" t="n">
+        <v>55</v>
+      </c>
+      <c r="V63" t="n">
+        <v>53.35887</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-77.31016</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Grondin</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>13</v>
+      </c>
+      <c r="T64" t="n">
+        <v>325</v>
+      </c>
+      <c r="U64" t="n">
+        <v>55</v>
+      </c>
+      <c r="V64" t="n">
+        <v>46.26532</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-71.28788</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nutbrown</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>13</v>
+      </c>
+      <c r="T65" t="n">
+        <v>325</v>
+      </c>
+      <c r="U65" t="n">
+        <v>55</v>
+      </c>
+      <c r="V65" t="n">
+        <v>46.26265</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-71.21769</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Coleraine</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="n">
+        <v>325</v>
+      </c>
+      <c r="U66" t="n">
+        <v>55</v>
+      </c>
+      <c r="V66" t="n">
+        <v>46.27176</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-71.28612</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Copper, Uranium, Silver</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>325</v>
+      </c>
+      <c r="U67" t="n">
+        <v>55</v>
+      </c>
+      <c r="V67" t="n">
+        <v>46.265</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-71.21259999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Foy</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>13</v>
+      </c>
+      <c r="T68" t="n">
+        <v>325</v>
+      </c>
+      <c r="U68" t="n">
+        <v>55</v>
+      </c>
+      <c r="V68" t="n">
+        <v>46.26109</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-71.22866</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AC-2010-006</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Au 4.44 g/t</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>13</v>
+      </c>
+      <c r="T69" t="n">
+        <v>325</v>
+      </c>
+      <c r="U69" t="n">
+        <v>55</v>
+      </c>
+      <c r="V69" t="n">
+        <v>52.03235</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-69.13816</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mine Lorraine</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Gold, Nickel, Copper, Iron, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>600 kt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Au 4.43 g/t, Cu 1.08%, Ni 0.47%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>13</v>
+      </c>
+      <c r="T70" t="n">
+        <v>325</v>
+      </c>
+      <c r="U70" t="n">
+        <v>55</v>
+      </c>
+      <c r="V70" t="n">
+        <v>47.35837</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-78.93895000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2347</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CaribGold 99-07</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Bismuth</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bismuth, Gold, Platinum, Palladium, Egp, Nickel, Zinc, Chromium, Silver</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>13</v>
+      </c>
+      <c r="T71" t="n">
+        <v>325</v>
+      </c>
+      <c r="U71" t="n">
+        <v>55</v>
+      </c>
+      <c r="V71" t="n">
+        <v>50.75408</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-76.84898</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lartic Est</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic, Silver</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>6</v>
+      </c>
+      <c r="T72" t="n">
+        <v>150</v>
+      </c>
+      <c r="U72" t="n">
+        <v>55</v>
+      </c>
+      <c r="V72" t="n">
         <v>48.173</v>
       </c>
-      <c r="W54" t="n">
+      <c r="W72" t="n">
         <v>-78.14212999999999</v>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Guettard-Nord</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>12</v>
+      </c>
+      <c r="T73" t="n">
+        <v>300</v>
+      </c>
+      <c r="U73" t="n">
+        <v>55</v>
+      </c>
+      <c r="V73" t="n">
+        <v>50.01478</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-75.39858</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Baleine Rouge Au-Zn-Pb</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lead, Zinc, Gold</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>13</v>
+      </c>
+      <c r="T74" t="n">
+        <v>325</v>
+      </c>
+      <c r="U74" t="n">
+        <v>55</v>
+      </c>
+      <c r="V74" t="n">
+        <v>55.23561</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-67.9516</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hope</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>13</v>
+      </c>
+      <c r="T75" t="n">
+        <v>325</v>
+      </c>
+      <c r="U75" t="n">
+        <v>55</v>
+      </c>
+      <c r="V75" t="n">
+        <v>54.8722</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-69.81637000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tricorne</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>325</v>
+      </c>
+      <c r="U76" t="n">
+        <v>55</v>
+      </c>
+      <c r="V76" t="n">
+        <v>54.85039</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-69.85742</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mauve</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Au 9.13 g/t</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>325</v>
+      </c>
+      <c r="U77" t="n">
+        <v>55</v>
+      </c>
+      <c r="V77" t="n">
+        <v>52.68441</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-76.29656</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Vieux-Camp</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Silver, Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Au 19.29 g/t, Cu 2.74%, Ag 54.00 g/t</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>325</v>
+      </c>
+      <c r="U78" t="n">
+        <v>55</v>
+      </c>
+      <c r="V78" t="n">
+        <v>52.65967</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-76.1383</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Mine Géant Dormant</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>3.2 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Au 32.94 g/t, Ag 11.80 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U2" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="V2" t="n">
-        <v>45.3192</v>
+        <v>49.13127</v>
       </c>
       <c r="W2" t="n">
-        <v>-71.92023</v>
+        <v>-77.97206</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4515</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Mine Madeleine</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Zinc, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>8.1 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Cu 1.9%, Ag 9.00 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -700,23 +700,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V3" t="n">
-        <v>47.99637</v>
+        <v>49.01028</v>
       </c>
       <c r="W3" t="n">
-        <v>-67.11127</v>
+        <v>-66.00369999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,17 +736,17 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold, Copper</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -757,12 +757,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -784,17 +784,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="V4" t="n">
-        <v>47.86378</v>
+        <v>45.3192</v>
       </c>
       <c r="W4" t="n">
-        <v>-67.38485</v>
+        <v>-71.92023</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Cobalt</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 29.25 g/t, W 0.122%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.82919</v>
+        <v>52.64108</v>
       </c>
       <c r="W5" t="n">
-        <v>-70.58076</v>
+        <v>-75.67010999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Sond. DDH-20-2023</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.84595</v>
+        <v>46.36809</v>
       </c>
       <c r="W6" t="n">
-        <v>-70.57626</v>
+        <v>-73.97731</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>Mont Opémiska No 1</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead</t>
+          <t>Gold, Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>50.31401</v>
+        <v>49.95224</v>
       </c>
       <c r="W7" t="n">
-        <v>-62.73908</v>
+        <v>-74.8797</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Claims Paradis</t>
+          <t>Getty</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,17 +1048,17 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
+          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1090,23 +1090,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>48.57696</v>
+        <v>61.39535</v>
       </c>
       <c r="W8" t="n">
-        <v>-78.14164</v>
+        <v>-75.00066</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verreault</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,17 +1126,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 4.78%</t>
+          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>48.71945</v>
+        <v>61.39368</v>
       </c>
       <c r="W9" t="n">
-        <v>-78.33144</v>
+        <v>-75.1713</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>53.39936</v>
+        <v>61.55073</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.29407</v>
+        <v>-72.66555</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St-Nazaire</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>48.70382</v>
+        <v>52.17253</v>
       </c>
       <c r="W11" t="n">
-        <v>-78.25041</v>
+        <v>-76.55762</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Lemoyne-Extension</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Au 6.22 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.40387</v>
+        <v>53.45927</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.30118</v>
+        <v>-75.18433</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=398</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Orfée</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 67.35 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>49.83681</v>
+        <v>53.46154</v>
       </c>
       <c r="W13" t="n">
-        <v>-70.57877999999999</v>
+        <v>-75.21647</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=399</t>
         </is>
       </c>
     </row>
@@ -1506,27 +1506,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sylvie</t>
+          <t>Orfée Est</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
+          <t>Au 10.53 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>61.39737</v>
+        <v>53.46148</v>
       </c>
       <c r="W14" t="n">
-        <v>-74.97753</v>
+        <v>-75.20878999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=402</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timtu</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,17 +1594,17 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
+          <t>Au 12.91 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>61.43006</v>
+        <v>53.51022</v>
       </c>
       <c r="W15" t="n">
-        <v>-74.84983</v>
+        <v>-75.46174000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Getty</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,17 +1672,17 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
+          <t>Au 144.55 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>61.39535</v>
+        <v>53.52019</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.00066</v>
+        <v>-75.40980999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mystery</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,17 +1750,17 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>61.39368</v>
+        <v>53.43724</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.1713</v>
+        <v>-75.04334</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Destorbelle</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 8.20 g/t</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>48.4465</v>
+        <v>53.48752</v>
       </c>
       <c r="W18" t="n">
-        <v>-78.85312999999999</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>50.85296</v>
+        <v>52.17024</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.47398</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mine Aldermac Moulton Hill</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,17 +1984,17 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead, Zinc, Molybdenum, Cadmium, Barium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>871 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 253.86 g/t, Zn 7.7%, Au 2.10 g/t, Pb 5.35%</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2026,23 +2026,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.40941</v>
+        <v>52.1766</v>
       </c>
       <c r="W20" t="n">
-        <v>-71.81791</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4354</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -2052,27 +2052,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lachance #2</t>
+          <t>Sylvie</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Lead, Molybdenum, Zinc, Silver</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
+          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>45.99171</v>
+        <v>61.39737</v>
       </c>
       <c r="W21" t="n">
-        <v>-71.70617</v>
+        <v>-74.97753</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>Timtu</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,17 +2140,17 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>52.17253</v>
+        <v>61.43006</v>
       </c>
       <c r="W22" t="n">
-        <v>-76.55762</v>
+        <v>-74.84983</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PAP Nord (Camp A-1)</t>
+          <t>Sond. LGS09-217</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>60.2779</v>
+        <v>53.528</v>
       </c>
       <c r="W23" t="n">
-        <v>-75.33311</v>
+        <v>-76.54774999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Lac Nasigon</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Cu 4.4%, Ag 96.30 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>61.55073</v>
+        <v>47.53085</v>
       </c>
       <c r="W24" t="n">
-        <v>-72.66555</v>
+        <v>-75.11848000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Nasigon (Lac Lajoue)</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>53.39256</v>
+        <v>47.53875</v>
       </c>
       <c r="W25" t="n">
-        <v>-77.43714</v>
+        <v>-75.10978</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>RA13-02</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Silver, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>45.44828</v>
+        <v>53.17502</v>
       </c>
       <c r="W26" t="n">
-        <v>-72.1057</v>
+        <v>-77.75697</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brompton Copper</t>
+          <t>RA13-03</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Silver, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 3.42%, Ag 3.00 g/t, Ni 0.04%, Zn 0.05%</t>
+          <t>Au 3.71 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>45.48343</v>
+        <v>53.1949</v>
       </c>
       <c r="W27" t="n">
-        <v>-72.10835</v>
+        <v>-77.66768999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2275</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>45.32873</v>
+        <v>52.03235</v>
       </c>
       <c r="W28" t="n">
-        <v>-72.47421</v>
+        <v>-69.13816</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Baleine Rouge Au-Zn-Pb</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Lead, Cadmium, Zinc, Copper, Silver</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>45.29835</v>
+        <v>55.23561</v>
       </c>
       <c r="W29" t="n">
-        <v>-72.31643</v>
+        <v>-67.9516</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Golden Idol</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Lead, Copper</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Au 9.09 g/t, Zn 0.087%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>53.39458</v>
+        <v>53.57002</v>
       </c>
       <c r="W30" t="n">
-        <v>-77.44683999999999</v>
+        <v>-72.41676</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Umex-2</t>
+          <t>Comtois NW</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 2.2%, Zn 6.95%, Au 1.74 g/t, Ag 63.99 g/t</t>
+          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2884,23 +2884,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T31" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U31" t="n">
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.81674</v>
+        <v>49.18766</v>
       </c>
       <c r="W31" t="n">
-        <v>-75.52503</v>
+        <v>-77.31872</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3664</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
         </is>
       </c>
     </row>
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zone 32 (Tonalite-Zone Veine)</t>
+          <t>Jedi</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
+          <t>Au 11.50 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>53.5291</v>
+        <v>54.84385</v>
       </c>
       <c r="W32" t="n">
-        <v>-76.56155</v>
+        <v>-69.86212</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
         </is>
       </c>
     </row>
@@ -2988,22 +2988,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zone 32 (Mico-Milan)</t>
+          <t>Orage</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 72.69 g/t</t>
+          <t>Cu 4.6%, Ag 16.90 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>53.52891</v>
+        <v>53.68741</v>
       </c>
       <c r="W33" t="n">
-        <v>-76.56541</v>
+        <v>-76.22185</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=468</t>
         </is>
       </c>
     </row>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRH-96-07</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 19.59 g/t</t>
+          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.52311</v>
+        <v>54.8722</v>
       </c>
       <c r="W34" t="n">
-        <v>-76.61015</v>
+        <v>-69.81637000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Tricorne</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Manganese</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>46.00535</v>
+        <v>54.85039</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.70357</v>
+        <v>-69.85742</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sond. LF-93-03</t>
+          <t>Jedi Extension</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 56.50 g/t, Ag 70.63 g/t, Cu 0.861%, Zn 1.19%</t>
+          <t>Au 5.89 g/t, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>49.5436</v>
+        <v>54.85448</v>
       </c>
       <c r="W36" t="n">
-        <v>-75.41676</v>
+        <v>-69.83853000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3599</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11102</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>TR-00-126</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Au 20.70 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>53.43724</v>
+        <v>53.53822</v>
       </c>
       <c r="W37" t="n">
-        <v>-75.04334</v>
+        <v>-76.48351</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=491</t>
         </is>
       </c>
     </row>
@@ -3378,22 +3378,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fenton-Ouest</t>
+          <t>TR-00-129, 130 et 131</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 19.17 g/t, Cu 0.72%</t>
+          <t>Au 35.04 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>49.53598</v>
+        <v>53.53948</v>
       </c>
       <c r="W38" t="n">
-        <v>-75.42941</v>
+        <v>-76.47684</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22367</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=492</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Zone no 7</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
+          <t>Copper, Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Au 7.54 g/t, Ag 258.86 g/t, Zn 8.05%, Pb 11.4%, Cu 0.7%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>59.80634</v>
+        <v>53.1821</v>
       </c>
       <c r="W39" t="n">
-        <v>-75.01831</v>
+        <v>-77.71374</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=496</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Galexis</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Beryllium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>53.48752</v>
+        <v>52.03237</v>
       </c>
       <c r="W40" t="n">
-        <v>-75.33392000000001</v>
+        <v>-75.13809999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lac Shallow-Est</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Silver</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 4.4%, Ni 1.02%, Ag 7.89 g/t</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>49.72004</v>
+        <v>49.24734</v>
       </c>
       <c r="W41" t="n">
-        <v>-77.44344</v>
+        <v>-71.98866</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1470</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Nitakwin</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 6.06 g/t</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>52.1766</v>
+        <v>53.39996</v>
       </c>
       <c r="W42" t="n">
-        <v>-76.71138999999999</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mustang</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Palladium, Egp, Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>52.17024</v>
+        <v>53.34013</v>
       </c>
       <c r="W43" t="n">
-        <v>-76.57532999999999</v>
+        <v>-77.32316</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lidge</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Arsenic</t>
+          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>52.21818</v>
+        <v>53.39786</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.45902</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>53.40779</v>
+        <v>53.35887</v>
       </c>
       <c r="W45" t="n">
-        <v>-77.28636</v>
+        <v>-77.31016</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lac Rond</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper</t>
+          <t>Chromium, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 9.00 g/t, Cu 0.48%, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>55.28891</v>
+        <v>53.38014</v>
       </c>
       <c r="W46" t="n">
-        <v>-65.74114</v>
+        <v>-77.28712</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3636</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lac Phooey</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.24%, Zn 0.24%</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>49.32384</v>
+        <v>53.40387</v>
       </c>
       <c r="W47" t="n">
-        <v>-75.02628</v>
+        <v>-77.30118</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3638</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 11.00 g/t, Cu 3.3%</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>49.49222</v>
+        <v>53.39936</v>
       </c>
       <c r="W48" t="n">
-        <v>-75.32478999999999</v>
+        <v>-77.29407</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3643</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -4236,22 +4236,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>48.37403</v>
+        <v>53.40779</v>
       </c>
       <c r="W49" t="n">
-        <v>-65.44089</v>
+        <v>-77.28636</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mine Capelton (Albert)</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,17 +4324,17 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I50" t="b">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>300 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Cu 8.05%, Zn 2.68%, Au 0.63 g/t, Ag 30.40 g/t, Pb 0.285%</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>45.32298</v>
+        <v>53.41679</v>
       </c>
       <c r="W50" t="n">
-        <v>-71.90649999999999</v>
+        <v>-77.27167</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4364</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ferricrete</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vanadium</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Vanadium, Gold, Zinc</t>
+          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 280.30 g/t, V 0.158%, Zn 0.3%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>57.51228</v>
+        <v>53.39256</v>
       </c>
       <c r="W51" t="n">
-        <v>-69.26596000000001</v>
+        <v>-77.43714</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3744</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Silver, Gold, Tungsten, Lead, Copper</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4522,23 +4522,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>48.32328</v>
+        <v>53.39458</v>
       </c>
       <c r="W52" t="n">
-        <v>-79.44637</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lavallée Sud</t>
+          <t>Coconut Club</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Etr, Thorium, Uranium, Zr, Gold, Silver</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Au 4.50 g/t, Cu 0.398%</t>
+          <t>Au 7.94 g/t, U 0.0864%, Ag 33.10 g/t, ETR 1.05%, Th 0.621%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>47.35591</v>
+        <v>46.99057</v>
       </c>
       <c r="W53" t="n">
-        <v>-78.9842</v>
+        <v>-78.59457999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2359</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=535</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lavallée : Zone 39</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 14.75 g/t, Cu 0.83%, Ag 10.40 g/t</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U54" t="n">
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>47.37551</v>
+        <v>48.32328</v>
       </c>
       <c r="W54" t="n">
-        <v>-78.97857</v>
+        <v>-79.44637</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2360</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Isabelle</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,12 +4714,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Au 316.18 g/t, Ag 7.50 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>49.79699</v>
+        <v>52.09336</v>
       </c>
       <c r="W55" t="n">
-        <v>-75.81529</v>
+        <v>-76.75954</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=578</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Lac Delta NW-Cuivre</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 13.33 g/t, Cu 7.3%, Ag 20.30 g/t</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>49.24734</v>
+        <v>52.23158</v>
       </c>
       <c r="W56" t="n">
-        <v>-71.98866</v>
+        <v>-76.4002</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=593</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Wab-88-0406</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum, Bismuth, Tellurium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 5.74 g/t, Cu 2.4%, Mo 0.0901%, Ag 13.50 g/t, Te 0.004%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,14 +4921,14 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>45.03676</v>
+        <v>52.23706</v>
       </c>
       <c r="W57" t="n">
-        <v>-72.77243</v>
+        <v>-76.60512</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=562</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Miltin</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4948,12 +4948,12 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Copper, Silver</t>
+          <t>Silver, Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Au 36.48 g/t, Cu 10.5%, Ag 52.00 g/t</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>53.38014</v>
+        <v>52.2473</v>
       </c>
       <c r="W58" t="n">
-        <v>-77.28712</v>
+        <v>-76.50475</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=565</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Zone Cyr</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Silver, Gold, Arsenic</t>
+          <t>Silver, Gold, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Cu 5.81%, Au 2.12 g/t, Ag 70.00 g/t, Zn 0.46%, Pb 0.19%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>53.41679</v>
+        <v>52.2425</v>
       </c>
       <c r="W59" t="n">
-        <v>-77.27167</v>
+        <v>-76.59574000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=566</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Zone Chino</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Au 24.69 g/t, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>53.39996</v>
+        <v>52.17342</v>
       </c>
       <c r="W60" t="n">
-        <v>-77.33163999999999</v>
+        <v>-76.44268</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=600</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Zone QET</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Au 14.50 g/t, Cu 0.96%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>53.34013</v>
+        <v>52.24811</v>
       </c>
       <c r="W61" t="n">
-        <v>-77.32316</v>
+        <v>-76.49615</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=606</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Viau (ou Bordulac)</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Au 31.00 g/t</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>53.39786</v>
+        <v>48.26547</v>
       </c>
       <c r="W62" t="n">
-        <v>-77.30625000000001</v>
+        <v>-79.41453</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Au 278.00 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5389,14 +5389,14 @@
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>53.35887</v>
+        <v>52.1821</v>
       </c>
       <c r="W63" t="n">
-        <v>-77.31016</v>
+        <v>-76.70099999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5467,14 +5467,14 @@
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>46.26532</v>
+        <v>50.64946</v>
       </c>
       <c r="W64" t="n">
-        <v>-71.28788</v>
+        <v>-75.04613999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Lac Delta Nord (Grid C.22)</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Au 4.71 g/t, Cu 1.81%, Ag 14.00 g/t, Zn 0.54%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5545,14 +5545,14 @@
         <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>46.26265</v>
+        <v>52.24319</v>
       </c>
       <c r="W65" t="n">
-        <v>-71.21769</v>
+        <v>-76.36844000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=598</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lac Tarsac : Veine I et III</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Gold, Lead, Copper, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Au 11.66 g/t</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U66" t="n">
         <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>46.27176</v>
+        <v>48.3561</v>
       </c>
       <c r="W66" t="n">
-        <v>-71.28612</v>
+        <v>-79.43788000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
         </is>
       </c>
     </row>
@@ -5640,22 +5640,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Nisto</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Zinc, Copper, Lead, Uranium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Cu 5.6%, Zn 5.4%, U 0.03%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5701,14 +5701,14 @@
         <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>46.265</v>
+        <v>50.3605</v>
       </c>
       <c r="W67" t="n">
-        <v>-71.21259999999999</v>
+        <v>-63.13619</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=665</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Soucy No 1 - Zones A et D</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Zinc, Gold, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 1.72%, Au 1.61 g/t, Zn 2.77%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5779,14 +5779,14 @@
         <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>46.26109</v>
+        <v>58.32867</v>
       </c>
       <c r="W68" t="n">
-        <v>-71.22866</v>
+        <v>-69.86747</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=677</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Prud'Homme No 1 : Zone Sud</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Cu 4.65%, Zn 12%, Au 1.25 g/t, Ag 29.77 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5857,14 +5857,14 @@
         <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>52.03235</v>
+        <v>58.25921</v>
       </c>
       <c r="W69" t="n">
-        <v>-69.13816</v>
+        <v>-69.91007999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=679</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mine Lorraine</t>
+          <t>Petit-Pas</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold, Nickel, Copper, Iron, Lead, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>600 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Au 4.43 g/t, Cu 1.08%, Ni 0.47%</t>
+          <t>Au 52.87 g/t, Ag 5.10 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5935,14 +5935,14 @@
         <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>47.35837</v>
+        <v>53.48965</v>
       </c>
       <c r="W70" t="n">
-        <v>-78.93895000000001</v>
+        <v>-72.12729</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2347</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=686</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CaribGold 99-07</t>
+          <t>Destorbelle</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -5962,12 +5962,12 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bismuth, Gold, Platinum, Palladium, Egp, Nickel, Zinc, Chromium, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
+          <t>Au 8.20 g/t</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6004,23 +6004,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U71" t="n">
         <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>50.75408</v>
+        <v>48.4465</v>
       </c>
       <c r="W71" t="n">
-        <v>-76.84898</v>
+        <v>-78.85312999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>Huckleberry</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6040,12 +6040,12 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Ag 26.60 g/t</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>48.173</v>
+        <v>55.78035</v>
       </c>
       <c r="W72" t="n">
-        <v>-78.14212999999999</v>
+        <v>-66.95337000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Guettard-Nord</t>
+          <t>Été Indien</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Au 34.17 g/t, Ag 21.60 g/t</t>
+          <t>Au 23.43 g/t, Ag 12.30 g/t</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>50.01478</v>
+        <v>54.07321</v>
       </c>
       <c r="W73" t="n">
-        <v>-75.39858</v>
+        <v>-72.52986</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5234</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=696</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Baleine Rouge Au-Zn-Pb</t>
+          <t>Lingo 3 Ouest</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6196,12 +6196,12 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Gold, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+          <t>Au 3230.89 g/t, Ag 17.30 g/t, Pb 0.000128%, Zn 0.107%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6247,14 +6247,14 @@
         <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>55.23561</v>
+        <v>54.07075</v>
       </c>
       <c r="W74" t="n">
-        <v>-67.9516</v>
+        <v>-72.53373000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=698</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Grenouille 2</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
+          <t>Au 3527.00 g/t, Ag 18.30 g/t</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6325,14 +6325,14 @@
         <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>54.8722</v>
+        <v>54.07734</v>
       </c>
       <c r="W75" t="n">
-        <v>-69.81637000000001</v>
+        <v>-72.51860000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=702</t>
         </is>
       </c>
     </row>
@@ -6342,11 +6342,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tricorne</t>
+          <t>Moman</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
+          <t>Au 3527.40 g/t</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6403,14 +6403,14 @@
         <v>55</v>
       </c>
       <c r="V76" t="n">
-        <v>54.85039</v>
+        <v>54.07892</v>
       </c>
       <c r="W76" t="n">
-        <v>-69.85742</v>
+        <v>-72.51427</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=704</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mauve</t>
+          <t>Slowdance</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 9.13 g/t</t>
+          <t>Au 4.63 g/t, Cu 0.104%, Ag 4.50 g/t, Zn 0.221%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6481,14 +6481,14 @@
         <v>55</v>
       </c>
       <c r="V77" t="n">
-        <v>52.68441</v>
+        <v>54.0731</v>
       </c>
       <c r="W77" t="n">
-        <v>-76.29656</v>
+        <v>-72.54952</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=705</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vieux-Camp</t>
+          <t>Zone 32</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6508,12 +6508,12 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 19.29 g/t, Cu 2.74%, Ag 54.00 g/t</t>
+          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,14 +6559,1730 @@
         <v>55</v>
       </c>
       <c r="V78" t="n">
-        <v>52.65967</v>
+        <v>53.52649</v>
       </c>
       <c r="W78" t="n">
-        <v>-76.1383</v>
+        <v>-76.56404999999999</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>As-3</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Au 6.38 g/t</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>325</v>
+      </c>
+      <c r="U79" t="n">
+        <v>55</v>
+      </c>
+      <c r="V79" t="n">
+        <v>53.52425</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-76.57341</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Au 36.38 g/t</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="n">
+        <v>325</v>
+      </c>
+      <c r="U80" t="n">
+        <v>55</v>
+      </c>
+      <c r="V80" t="n">
+        <v>53.52499</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-76.58275</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Zone 35-L11W</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Au 35.31 g/t</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" t="n">
+        <v>325</v>
+      </c>
+      <c r="U81" t="n">
+        <v>55</v>
+      </c>
+      <c r="V81" t="n">
+        <v>53.52296</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-76.59889</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Au 32.73 g/t</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>13</v>
+      </c>
+      <c r="T82" t="n">
+        <v>325</v>
+      </c>
+      <c r="U82" t="n">
+        <v>55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>53.51886</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-76.60854</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Zone 32 (Tonalite-Zone Veine)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>13</v>
+      </c>
+      <c r="T83" t="n">
+        <v>325</v>
+      </c>
+      <c r="U83" t="n">
+        <v>55</v>
+      </c>
+      <c r="V83" t="n">
+        <v>53.5291</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-76.56155</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Zone 32 (Mico-Milan)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Au 72.69 g/t</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>325</v>
+      </c>
+      <c r="U84" t="n">
+        <v>55</v>
+      </c>
+      <c r="V84" t="n">
+        <v>53.52891</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-76.56541</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TRH-96-07</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Au 19.59 g/t</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>13</v>
+      </c>
+      <c r="T85" t="n">
+        <v>325</v>
+      </c>
+      <c r="U85" t="n">
+        <v>55</v>
+      </c>
+      <c r="V85" t="n">
+        <v>53.52311</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-76.61015</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pari (Zone 30)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Au 13.50 g/t, Cu 0.57%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
+        <v>325</v>
+      </c>
+      <c r="U86" t="n">
+        <v>55</v>
+      </c>
+      <c r="V86" t="n">
+        <v>53.5301</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-76.55025999999999</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Filion</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Cobalt</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>13</v>
+      </c>
+      <c r="T87" t="n">
+        <v>325</v>
+      </c>
+      <c r="U87" t="n">
+        <v>55</v>
+      </c>
+      <c r="V87" t="n">
+        <v>46.61092</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-75.97769</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Red Toad</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Au 153.00 g/t</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>13</v>
+      </c>
+      <c r="T88" t="n">
+        <v>325</v>
+      </c>
+      <c r="U88" t="n">
+        <v>55</v>
+      </c>
+      <c r="V88" t="n">
+        <v>54.08287</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-72.50529</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=712</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sortilèges Dorés Ouest</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Au 3.65 g/t, Cu 0.223%, Ag 3.50 g/t, Zn 0.229%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>13</v>
+      </c>
+      <c r="T89" t="n">
+        <v>325</v>
+      </c>
+      <c r="U89" t="n">
+        <v>55</v>
+      </c>
+      <c r="V89" t="n">
+        <v>54.06291</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-72.57297</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=717</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Jackson (Minerais Lac)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>13</v>
+      </c>
+      <c r="T90" t="n">
+        <v>325</v>
+      </c>
+      <c r="U90" t="n">
+        <v>55</v>
+      </c>
+      <c r="V90" t="n">
+        <v>45.52972</v>
+      </c>
+      <c r="W90" t="n">
+        <v>-71.65783999999999</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Projet 70-Landome</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Zinc, Gold</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>13</v>
+      </c>
+      <c r="T91" t="n">
+        <v>325</v>
+      </c>
+      <c r="U91" t="n">
+        <v>55</v>
+      </c>
+      <c r="V91" t="n">
+        <v>48.46123</v>
+      </c>
+      <c r="W91" t="n">
+        <v>-77.95265999999999</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>de l'Ours</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Au 27.00 g/t</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>13</v>
+      </c>
+      <c r="T92" t="n">
+        <v>325</v>
+      </c>
+      <c r="U92" t="n">
+        <v>55</v>
+      </c>
+      <c r="V92" t="n">
+        <v>53.61441</v>
+      </c>
+      <c r="W92" t="n">
+        <v>-71.97407</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Dead Mouse extension</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Au 18.36 g/t</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>13</v>
+      </c>
+      <c r="T93" t="n">
+        <v>325</v>
+      </c>
+      <c r="U93" t="n">
+        <v>55</v>
+      </c>
+      <c r="V93" t="n">
+        <v>53.61747</v>
+      </c>
+      <c r="W93" t="n">
+        <v>-71.97382</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Bourdon</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Au 21.80 g/t</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>13</v>
+      </c>
+      <c r="T94" t="n">
+        <v>325</v>
+      </c>
+      <c r="U94" t="n">
+        <v>55</v>
+      </c>
+      <c r="V94" t="n">
+        <v>53.62313</v>
+      </c>
+      <c r="W94" t="n">
+        <v>-71.96111999999999</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ugo</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Au 251.66 g/t</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>13</v>
+      </c>
+      <c r="T95" t="n">
+        <v>325</v>
+      </c>
+      <c r="U95" t="n">
+        <v>55</v>
+      </c>
+      <c r="V95" t="n">
+        <v>53.53343</v>
+      </c>
+      <c r="W95" t="n">
+        <v>-76.53331</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Brèche</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Au 8.56 g/t</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>13</v>
+      </c>
+      <c r="T96" t="n">
+        <v>325</v>
+      </c>
+      <c r="U96" t="n">
+        <v>55</v>
+      </c>
+      <c r="V96" t="n">
+        <v>53.53187</v>
+      </c>
+      <c r="W96" t="n">
+        <v>-76.54353</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pari</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Au 730.77 g/t</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>13</v>
+      </c>
+      <c r="T97" t="n">
+        <v>325</v>
+      </c>
+      <c r="U97" t="n">
+        <v>55</v>
+      </c>
+      <c r="V97" t="n">
+        <v>53.53306</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-76.55201</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>St-Benoit</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Lead, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>13</v>
+      </c>
+      <c r="T98" t="n">
+        <v>325</v>
+      </c>
+      <c r="U98" t="n">
+        <v>55</v>
+      </c>
+      <c r="V98" t="n">
+        <v>47.99637</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-67.11127</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Mid-Patapédia</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lead, Silver, Zinc, Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>13</v>
+      </c>
+      <c r="T99" t="n">
+        <v>325</v>
+      </c>
+      <c r="U99" t="n">
+        <v>55</v>
+      </c>
+      <c r="V99" t="n">
+        <v>47.86378</v>
+      </c>
+      <c r="W99" t="n">
+        <v>-67.38485</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BJB - Rustcliff (Boudrias)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Silver, Gold, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>13</v>
+      </c>
+      <c r="T100" t="n">
+        <v>325</v>
+      </c>
+      <c r="U100" t="n">
+        <v>55</v>
+      </c>
+      <c r="V100" t="n">
+        <v>50.31401</v>
+      </c>
+      <c r="W100" t="n">
+        <v>-62.73908</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X100"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -622,10 +622,10 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U2" t="n">
         <v>80</v>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Madeleine</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8.1 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 1.9%, Ag 9.00 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -700,23 +700,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V3" t="n">
-        <v>49.01028</v>
+        <v>45.3192</v>
       </c>
       <c r="W3" t="n">
-        <v>-66.00369999999999</v>
+        <v>-71.92023</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2916</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,17 +736,17 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Palladium, Copper, Gold, Egp, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -757,12 +757,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -784,17 +784,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>45.3192</v>
+        <v>53.34013</v>
       </c>
       <c r="W4" t="n">
-        <v>-71.92023</v>
+        <v>-77.32316</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Copper, Gold, Silver, Lead, Zinc, Arsenic</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>52.64108</v>
+        <v>53.39936</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.67010999999999</v>
+        <v>-77.29407</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>46.36809</v>
+        <v>53.40387</v>
       </c>
       <c r="W6" t="n">
-        <v>-73.97731</v>
+        <v>-77.30118</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver</t>
+          <t>Nickel, Chromium, Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>49.95224</v>
+        <v>53.38014</v>
       </c>
       <c r="W7" t="n">
-        <v>-74.8797</v>
+        <v>-77.28712</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Getty</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,17 +1048,17 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
+          <t>Lead, Silver, Gold, Zinc, Arsenic, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>61.39535</v>
+        <v>53.40779</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.00066</v>
+        <v>-77.28636</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mystery</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,17 +1126,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
+          <t>Nickel, Palladium, Gold, Zinc, Silver, Copper, Lead, Cobalt, Egp</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>61.39368</v>
+        <v>53.39996</v>
       </c>
       <c r="W9" t="n">
-        <v>-75.1713</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>61.55073</v>
+        <v>53.39256</v>
       </c>
       <c r="W10" t="n">
-        <v>-72.66555</v>
+        <v>-77.43714</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Tungsten, Gold, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>52.17253</v>
+        <v>53.39458</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.55762</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lemoyne-Extension</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 6.22 g/t</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.45927</v>
+        <v>45.32873</v>
       </c>
       <c r="W12" t="n">
-        <v>-75.18433</v>
+        <v>-72.47421</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=398</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Orfée</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Gold, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 67.35 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.46154</v>
+        <v>45.44828</v>
       </c>
       <c r="W13" t="n">
-        <v>-75.21647</v>
+        <v>-72.1057</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=399</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Orfée Est</t>
+          <t>de l'Ours</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.53 g/t</t>
+          <t>Au 27.00 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.46148</v>
+        <v>53.61441</v>
       </c>
       <c r="W14" t="n">
-        <v>-75.20878999999999</v>
+        <v>-71.97407</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=402</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
         </is>
       </c>
     </row>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Dead Mouse extension</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 12.91 g/t</t>
+          <t>Au 18.36 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.51022</v>
+        <v>53.61747</v>
       </c>
       <c r="W15" t="n">
-        <v>-75.46174000000001</v>
+        <v>-71.97382</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Bourdon</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 144.55 g/t</t>
+          <t>Au 21.80 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>53.52019</v>
+        <v>53.62313</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.40980999999999</v>
+        <v>-71.96111999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>53.43724</v>
+        <v>49.82919</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.04334</v>
+        <v>-70.58076</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Galexis</t>
+          <t>Bolt</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
+          <t>Cu 2.9%, Ni 0.261%, Ag 17.40 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>53.48752</v>
+        <v>61.57527</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.33392000000001</v>
+        <v>-74.46583</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26280</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mustang</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>52.17024</v>
+        <v>45.29835</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.57532999999999</v>
+        <v>-72.31643</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lac Nitakwin</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 6.06 g/t</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>52.1766</v>
+        <v>53.39786</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.71138999999999</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sylvie</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,17 +2062,17 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
+          <t>Nickel, Copper, Iron, Cobalt</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>61.39737</v>
+        <v>49.24734</v>
       </c>
       <c r="W21" t="n">
-        <v>-74.97753</v>
+        <v>-71.98866</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timtu</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,17 +2140,17 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>61.43006</v>
+        <v>53.35887</v>
       </c>
       <c r="W22" t="n">
-        <v>-74.84983</v>
+        <v>-77.31016</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sond. LGS09-217</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>53.528</v>
+        <v>53.41679</v>
       </c>
       <c r="W23" t="n">
-        <v>-76.54774999999999</v>
+        <v>-77.27167</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lac Nasigon</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 4.4%, Ag 96.30 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>47.53085</v>
+        <v>46.26265</v>
       </c>
       <c r="W24" t="n">
-        <v>-75.11848000000001</v>
+        <v>-71.21769</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nasigon (Lac Lajoue)</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>47.53875</v>
+        <v>46.265</v>
       </c>
       <c r="W25" t="n">
-        <v>-75.10978</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RA13-02</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>53.17502</v>
+        <v>46.27176</v>
       </c>
       <c r="W26" t="n">
-        <v>-77.75697</v>
+        <v>-71.28612</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RA13-03</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 3.71 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>53.1949</v>
+        <v>46.26532</v>
       </c>
       <c r="W27" t="n">
-        <v>-77.66768999999999</v>
+        <v>-71.28788</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Eli SE</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Vanadium, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 25.00 g/t, Cu 1.02%, V 0.228%, Ag 16.70 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>52.03235</v>
+        <v>53.10465</v>
       </c>
       <c r="W28" t="n">
-        <v>-69.13816</v>
+        <v>-77.28514</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=32103</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Baleine Rouge Au-Zn-Pb</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,17 +2686,17 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>55.23561</v>
+        <v>45.42731</v>
       </c>
       <c r="W29" t="n">
-        <v>-67.9516</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Golden Idol</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 9.09 g/t, Zn 0.087%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>53.57002</v>
+        <v>45.43447</v>
       </c>
       <c r="W30" t="n">
-        <v>-72.41676</v>
+        <v>-70.9088</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Comtois NW</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>49.18766</v>
+        <v>45.43568</v>
       </c>
       <c r="W31" t="n">
-        <v>-77.31872</v>
+        <v>-70.91788</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jedi</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
+          <t>Lead, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 11.50 g/t</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>54.84385</v>
+        <v>45.40513</v>
       </c>
       <c r="W32" t="n">
-        <v>-69.86212</v>
+        <v>-70.9376</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Orage</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Ag 16.90 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>53.68741</v>
+        <v>49.84595</v>
       </c>
       <c r="W33" t="n">
-        <v>-76.22185</v>
+        <v>-70.57626</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=468</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>54.8722</v>
+        <v>52.03235</v>
       </c>
       <c r="W34" t="n">
-        <v>-69.81637000000001</v>
+        <v>-69.13816</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tricorne</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Silver, Copper, Manganese, Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>54.85039</v>
+        <v>46.00535</v>
       </c>
       <c r="W35" t="n">
-        <v>-69.85742</v>
+        <v>-71.70357</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jedi Extension</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 5.89 g/t, Ag 6.50 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>54.85448</v>
+        <v>45.03676</v>
       </c>
       <c r="W36" t="n">
-        <v>-69.83853000000001</v>
+        <v>-72.77243</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11102</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TR-00-126</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 20.70 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>53.53822</v>
+        <v>49.83681</v>
       </c>
       <c r="W37" t="n">
-        <v>-76.48351</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -3378,22 +3378,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TR-00-129, 130 et 131</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Egp, Palladium, Platinum, Nickel</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 35.04 g/t</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>53.53948</v>
+        <v>61.55073</v>
       </c>
       <c r="W38" t="n">
-        <v>-76.47684</v>
+        <v>-72.66555</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=492</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zone no 7</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Ag 258.86 g/t, Zn 8.05%, Pb 11.4%, Cu 0.7%</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>53.1821</v>
+        <v>48.32328</v>
       </c>
       <c r="W39" t="n">
-        <v>-77.71374</v>
+        <v>-79.44637</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=496</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -3534,22 +3534,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Beryllium</t>
+          <t>Copper, Silver, Zinc, Gold, Lead</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>52.03237</v>
+        <v>48.37403</v>
       </c>
       <c r="W40" t="n">
-        <v>-75.13809999999999</v>
+        <v>-65.44089</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>49.24734</v>
+        <v>46.26109</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.98866</v>
+        <v>-71.22866</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
+          <t>Copper, Gold, Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>53.39996</v>
+        <v>47.99637</v>
       </c>
       <c r="W42" t="n">
-        <v>-77.33163999999999</v>
+        <v>-67.11127</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper, Silver</t>
+          <t>Copper, Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>53.34013</v>
+        <v>50.31401</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.32316</v>
+        <v>-62.73908</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>53.39786</v>
+        <v>48.09296</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.30625000000001</v>
+        <v>-66.78681</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Lartic Est</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T45" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>53.35887</v>
+        <v>48.173</v>
       </c>
       <c r="W45" t="n">
-        <v>-77.31016</v>
+        <v>-78.14212999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Copper, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>53.38014</v>
+        <v>55.15269</v>
       </c>
       <c r="W46" t="n">
-        <v>-77.28712</v>
+        <v>-66.35399</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>53.40387</v>
+        <v>55.23261</v>
       </c>
       <c r="W47" t="n">
-        <v>-77.30118</v>
+        <v>-66.16073</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Lac Rocher</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,17 +4168,17 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
+          <t>Platinum, Palladium, Nickel, Copper, Egp, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>53.39936</v>
+        <v>50.58471</v>
       </c>
       <c r="W48" t="n">
-        <v>-77.29407</v>
+        <v>-76.34242</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
+          <t>Gold, Silver, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>53.40779</v>
+        <v>49.78784</v>
       </c>
       <c r="W49" t="n">
-        <v>-77.28636</v>
+        <v>-77.08529</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Golden Idol</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Silver, Gold, Arsenic</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Au 9.09 g/t, Zn 0.087%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>53.41679</v>
+        <v>53.57002</v>
       </c>
       <c r="W50" t="n">
-        <v>-77.27167</v>
+        <v>-72.41676</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Amaruk</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,23 +4444,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U51" t="n">
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>53.39256</v>
+        <v>59.60263</v>
       </c>
       <c r="W51" t="n">
-        <v>-77.43714</v>
+        <v>-74.86282</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lac Barlow</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Lead, Copper</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>53.39458</v>
+        <v>49.94431</v>
       </c>
       <c r="W52" t="n">
-        <v>-77.44683999999999</v>
+        <v>-74.71456000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Coconut Club</t>
+          <t>Mont Opémiska No 1</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Etr, Thorium, Uranium, Zr, Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Au 7.94 g/t, U 0.0864%, Ag 33.10 g/t, ETR 1.05%, Th 0.621%</t>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>46.99057</v>
+        <v>49.95224</v>
       </c>
       <c r="W53" t="n">
-        <v>-78.59457999999999</v>
+        <v>-74.8797</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Sond. SER-21-040</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4636,12 +4636,12 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Au 8.71 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4678,23 +4678,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>48.32328</v>
+        <v>53.08409</v>
       </c>
       <c r="W54" t="n">
-        <v>-79.44637</v>
+        <v>-77.20562</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Isabelle</t>
+          <t>Boulder Shear (Cuvier-Est)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Zinc, Arsenic, Copper</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 316.18 g/t, Ag 7.50 g/t</t>
+          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U55" t="n">
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>52.09336</v>
+        <v>49.9399</v>
       </c>
       <c r="W55" t="n">
-        <v>-76.75954</v>
+        <v>-74.70344</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=578</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lac Delta NW-Cuivre</t>
+          <t>CaribGold 99-07</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Bismuth, Chromium, Zinc, Nickel, Egp, Palladium, Platinum, Silver</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Au 13.33 g/t, Cu 7.3%, Ag 20.30 g/t</t>
+          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>52.23158</v>
+        <v>50.75408</v>
       </c>
       <c r="W56" t="n">
-        <v>-76.4002</v>
+        <v>-76.84898</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=593</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wab-88-0406</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Bismuth, Tellurium</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Au 5.74 g/t, Cu 2.4%, Mo 0.0901%, Ag 13.50 g/t, Te 0.004%</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,3368 +4921,14 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>52.23706</v>
+        <v>47.86378</v>
       </c>
       <c r="W57" t="n">
-        <v>-76.60512</v>
+        <v>-67.38485</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=562</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Miltin</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Au 36.48 g/t, Cu 10.5%, Ag 52.00 g/t</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>325</v>
-      </c>
-      <c r="U58" t="n">
-        <v>55</v>
-      </c>
-      <c r="V58" t="n">
-        <v>52.2473</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-76.50475</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=565</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Zone Cyr</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Copper, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Cu 5.81%, Au 2.12 g/t, Ag 70.00 g/t, Zn 0.46%, Pb 0.19%</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>13</v>
-      </c>
-      <c r="T59" t="n">
-        <v>325</v>
-      </c>
-      <c r="U59" t="n">
-        <v>55</v>
-      </c>
-      <c r="V59" t="n">
-        <v>52.2425</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-76.59574000000001</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=566</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Zone Chino</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Au 24.69 g/t, Ag 2.80 g/t</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>13</v>
-      </c>
-      <c r="T60" t="n">
-        <v>325</v>
-      </c>
-      <c r="U60" t="n">
-        <v>55</v>
-      </c>
-      <c r="V60" t="n">
-        <v>52.17342</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-76.44268</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=600</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Zone QET</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Au 14.50 g/t, Cu 0.96%, Ag 11.20 g/t</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>13</v>
-      </c>
-      <c r="T61" t="n">
-        <v>325</v>
-      </c>
-      <c r="U61" t="n">
-        <v>55</v>
-      </c>
-      <c r="V61" t="n">
-        <v>52.24811</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-76.49615</v>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=606</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Viau (ou Bordulac)</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Au 31.00 g/t</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>325</v>
-      </c>
-      <c r="U62" t="n">
-        <v>55</v>
-      </c>
-      <c r="V62" t="n">
-        <v>48.26547</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-79.41453</v>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Challenger</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Au 278.00 g/t</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>13</v>
-      </c>
-      <c r="T63" t="n">
-        <v>325</v>
-      </c>
-      <c r="U63" t="n">
-        <v>55</v>
-      </c>
-      <c r="V63" t="n">
-        <v>52.1821</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-76.70099999999999</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Au 7.60 g/t</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>13</v>
-      </c>
-      <c r="T64" t="n">
-        <v>325</v>
-      </c>
-      <c r="U64" t="n">
-        <v>55</v>
-      </c>
-      <c r="V64" t="n">
-        <v>50.64946</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-75.04613999999999</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Lac Delta Nord (Grid C.22)</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Au 4.71 g/t, Cu 1.81%, Ag 14.00 g/t, Zn 0.54%</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>13</v>
-      </c>
-      <c r="T65" t="n">
-        <v>325</v>
-      </c>
-      <c r="U65" t="n">
-        <v>55</v>
-      </c>
-      <c r="V65" t="n">
-        <v>52.24319</v>
-      </c>
-      <c r="W65" t="n">
-        <v>-76.36844000000001</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=598</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Lac Tarsac : Veine I et III</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Au 11.66 g/t</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>7</v>
-      </c>
-      <c r="T66" t="n">
-        <v>175</v>
-      </c>
-      <c r="U66" t="n">
-        <v>55</v>
-      </c>
-      <c r="V66" t="n">
-        <v>48.3561</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-79.43788000000001</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Nisto</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Lead, Uranium</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Cu 5.6%, Zn 5.4%, U 0.03%</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>13</v>
-      </c>
-      <c r="T67" t="n">
-        <v>325</v>
-      </c>
-      <c r="U67" t="n">
-        <v>55</v>
-      </c>
-      <c r="V67" t="n">
-        <v>50.3605</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-63.13619</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=665</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Soucy No 1 - Zones A et D</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Zinc, Gold, Copper, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Cu 1.72%, Au 1.61 g/t, Zn 2.77%</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="n">
-        <v>13</v>
-      </c>
-      <c r="T68" t="n">
-        <v>325</v>
-      </c>
-      <c r="U68" t="n">
-        <v>55</v>
-      </c>
-      <c r="V68" t="n">
-        <v>58.32867</v>
-      </c>
-      <c r="W68" t="n">
-        <v>-69.86747</v>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=677</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Prud'Homme No 1 : Zone Sud</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Gold, Zinc, Copper, Nickel, Silver</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Cu 4.65%, Zn 12%, Au 1.25 g/t, Ag 29.77 g/t</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="n">
-        <v>13</v>
-      </c>
-      <c r="T69" t="n">
-        <v>325</v>
-      </c>
-      <c r="U69" t="n">
-        <v>55</v>
-      </c>
-      <c r="V69" t="n">
-        <v>58.25921</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-69.91007999999999</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=679</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Petit-Pas</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Au 52.87 g/t, Ag 5.10 g/t</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>13</v>
-      </c>
-      <c r="T70" t="n">
-        <v>325</v>
-      </c>
-      <c r="U70" t="n">
-        <v>55</v>
-      </c>
-      <c r="V70" t="n">
-        <v>53.48965</v>
-      </c>
-      <c r="W70" t="n">
-        <v>-72.12729</v>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=686</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Destorbelle</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Au 8.20 g/t</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>12</v>
-      </c>
-      <c r="T71" t="n">
-        <v>300</v>
-      </c>
-      <c r="U71" t="n">
-        <v>55</v>
-      </c>
-      <c r="V71" t="n">
-        <v>48.4465</v>
-      </c>
-      <c r="W71" t="n">
-        <v>-78.85312999999999</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Huckleberry</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Ag 26.60 g/t</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="n">
-        <v>13</v>
-      </c>
-      <c r="T72" t="n">
-        <v>325</v>
-      </c>
-      <c r="U72" t="n">
-        <v>55</v>
-      </c>
-      <c r="V72" t="n">
-        <v>55.78035</v>
-      </c>
-      <c r="W72" t="n">
-        <v>-66.95337000000001</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Été Indien</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Au 23.43 g/t, Ag 12.30 g/t</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>13</v>
-      </c>
-      <c r="T73" t="n">
-        <v>325</v>
-      </c>
-      <c r="U73" t="n">
-        <v>55</v>
-      </c>
-      <c r="V73" t="n">
-        <v>54.07321</v>
-      </c>
-      <c r="W73" t="n">
-        <v>-72.52986</v>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=696</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Lingo 3 Ouest</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Au 3230.89 g/t, Ag 17.30 g/t, Pb 0.000128%, Zn 0.107%</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>13</v>
-      </c>
-      <c r="T74" t="n">
-        <v>325</v>
-      </c>
-      <c r="U74" t="n">
-        <v>55</v>
-      </c>
-      <c r="V74" t="n">
-        <v>54.07075</v>
-      </c>
-      <c r="W74" t="n">
-        <v>-72.53373000000001</v>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=698</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Grenouille 2</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Au 3527.00 g/t, Ag 18.30 g/t</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>13</v>
-      </c>
-      <c r="T75" t="n">
-        <v>325</v>
-      </c>
-      <c r="U75" t="n">
-        <v>55</v>
-      </c>
-      <c r="V75" t="n">
-        <v>54.07734</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-72.51860000000001</v>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=702</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Moman</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>3</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Au 3527.40 g/t</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>13</v>
-      </c>
-      <c r="T76" t="n">
-        <v>325</v>
-      </c>
-      <c r="U76" t="n">
-        <v>55</v>
-      </c>
-      <c r="V76" t="n">
-        <v>54.07892</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-72.51427</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=704</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Slowdance</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Gold, Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Au 4.63 g/t, Cu 0.104%, Ag 4.50 g/t, Zn 0.221%</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>13</v>
-      </c>
-      <c r="T77" t="n">
-        <v>325</v>
-      </c>
-      <c r="U77" t="n">
-        <v>55</v>
-      </c>
-      <c r="V77" t="n">
-        <v>54.0731</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-72.54952</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=705</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Zone 32</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>13</v>
-      </c>
-      <c r="T78" t="n">
-        <v>325</v>
-      </c>
-      <c r="U78" t="n">
-        <v>55</v>
-      </c>
-      <c r="V78" t="n">
-        <v>53.52649</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-76.56404999999999</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>As-3</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Au 6.38 g/t</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>325</v>
-      </c>
-      <c r="U79" t="n">
-        <v>55</v>
-      </c>
-      <c r="V79" t="n">
-        <v>53.52425</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-76.57341</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Au 36.38 g/t</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>13</v>
-      </c>
-      <c r="T80" t="n">
-        <v>325</v>
-      </c>
-      <c r="U80" t="n">
-        <v>55</v>
-      </c>
-      <c r="V80" t="n">
-        <v>53.52499</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-76.58275</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Zone 35-L11W</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Au 35.31 g/t</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>13</v>
-      </c>
-      <c r="T81" t="n">
-        <v>325</v>
-      </c>
-      <c r="U81" t="n">
-        <v>55</v>
-      </c>
-      <c r="V81" t="n">
-        <v>53.52296</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-76.59889</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Au 32.73 g/t</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>13</v>
-      </c>
-      <c r="T82" t="n">
-        <v>325</v>
-      </c>
-      <c r="U82" t="n">
-        <v>55</v>
-      </c>
-      <c r="V82" t="n">
-        <v>53.51886</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-76.60854</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Zone 32 (Tonalite-Zone Veine)</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>13</v>
-      </c>
-      <c r="T83" t="n">
-        <v>325</v>
-      </c>
-      <c r="U83" t="n">
-        <v>55</v>
-      </c>
-      <c r="V83" t="n">
-        <v>53.5291</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-76.56155</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Zone 32 (Mico-Milan)</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>3</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Au 72.69 g/t</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>325</v>
-      </c>
-      <c r="U84" t="n">
-        <v>55</v>
-      </c>
-      <c r="V84" t="n">
-        <v>53.52891</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-76.56541</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>TRH-96-07</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>3</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Au 19.59 g/t</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>13</v>
-      </c>
-      <c r="T85" t="n">
-        <v>325</v>
-      </c>
-      <c r="U85" t="n">
-        <v>55</v>
-      </c>
-      <c r="V85" t="n">
-        <v>53.52311</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-76.61015</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Pari (Zone 30)</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Copper, Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Au 13.50 g/t, Cu 0.57%</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>13</v>
-      </c>
-      <c r="T86" t="n">
-        <v>325</v>
-      </c>
-      <c r="U86" t="n">
-        <v>55</v>
-      </c>
-      <c r="V86" t="n">
-        <v>53.5301</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-76.55025999999999</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Filion</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Cobalt</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>13</v>
-      </c>
-      <c r="T87" t="n">
-        <v>325</v>
-      </c>
-      <c r="U87" t="n">
-        <v>55</v>
-      </c>
-      <c r="V87" t="n">
-        <v>46.61092</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-75.97769</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Red Toad</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Au 153.00 g/t</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="n">
-        <v>13</v>
-      </c>
-      <c r="T88" t="n">
-        <v>325</v>
-      </c>
-      <c r="U88" t="n">
-        <v>55</v>
-      </c>
-      <c r="V88" t="n">
-        <v>54.08287</v>
-      </c>
-      <c r="W88" t="n">
-        <v>-72.50529</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=712</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Sortilèges Dorés Ouest</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I89" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Au 3.65 g/t, Cu 0.223%, Ag 3.50 g/t, Zn 0.229%</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>13</v>
-      </c>
-      <c r="T89" t="n">
-        <v>325</v>
-      </c>
-      <c r="U89" t="n">
-        <v>55</v>
-      </c>
-      <c r="V89" t="n">
-        <v>54.06291</v>
-      </c>
-      <c r="W89" t="n">
-        <v>-72.57297</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=717</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Jackson (Minerais Lac)</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I90" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="n">
-        <v>13</v>
-      </c>
-      <c r="T90" t="n">
-        <v>325</v>
-      </c>
-      <c r="U90" t="n">
-        <v>55</v>
-      </c>
-      <c r="V90" t="n">
-        <v>45.52972</v>
-      </c>
-      <c r="W90" t="n">
-        <v>-71.65783999999999</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Projet 70-Landome</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Zinc, Gold</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I91" t="b">
-        <v>1</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="n">
-        <v>13</v>
-      </c>
-      <c r="T91" t="n">
-        <v>325</v>
-      </c>
-      <c r="U91" t="n">
-        <v>55</v>
-      </c>
-      <c r="V91" t="n">
-        <v>48.46123</v>
-      </c>
-      <c r="W91" t="n">
-        <v>-77.95265999999999</v>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>de l'Ours</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I92" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Au 27.00 g/t</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="n">
-        <v>13</v>
-      </c>
-      <c r="T92" t="n">
-        <v>325</v>
-      </c>
-      <c r="U92" t="n">
-        <v>55</v>
-      </c>
-      <c r="V92" t="n">
-        <v>53.61441</v>
-      </c>
-      <c r="W92" t="n">
-        <v>-71.97407</v>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Dead Mouse extension</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>2</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I93" t="b">
-        <v>1</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Au 18.36 g/t</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="n">
-        <v>13</v>
-      </c>
-      <c r="T93" t="n">
-        <v>325</v>
-      </c>
-      <c r="U93" t="n">
-        <v>55</v>
-      </c>
-      <c r="V93" t="n">
-        <v>53.61747</v>
-      </c>
-      <c r="W93" t="n">
-        <v>-71.97382</v>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Bourdon</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I94" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Au 21.80 g/t</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="n">
-        <v>13</v>
-      </c>
-      <c r="T94" t="n">
-        <v>325</v>
-      </c>
-      <c r="U94" t="n">
-        <v>55</v>
-      </c>
-      <c r="V94" t="n">
-        <v>53.62313</v>
-      </c>
-      <c r="W94" t="n">
-        <v>-71.96111999999999</v>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Ugo</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I95" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Au 251.66 g/t</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="n">
-        <v>13</v>
-      </c>
-      <c r="T95" t="n">
-        <v>325</v>
-      </c>
-      <c r="U95" t="n">
-        <v>55</v>
-      </c>
-      <c r="V95" t="n">
-        <v>53.53343</v>
-      </c>
-      <c r="W95" t="n">
-        <v>-76.53331</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Brèche</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I96" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Au 8.56 g/t</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="n">
-        <v>13</v>
-      </c>
-      <c r="T96" t="n">
-        <v>325</v>
-      </c>
-      <c r="U96" t="n">
-        <v>55</v>
-      </c>
-      <c r="V96" t="n">
-        <v>53.53187</v>
-      </c>
-      <c r="W96" t="n">
-        <v>-76.54353</v>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Pari</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I97" t="b">
-        <v>1</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Au 730.77 g/t</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="n">
-        <v>13</v>
-      </c>
-      <c r="T97" t="n">
-        <v>325</v>
-      </c>
-      <c r="U97" t="n">
-        <v>55</v>
-      </c>
-      <c r="V97" t="n">
-        <v>53.53306</v>
-      </c>
-      <c r="W97" t="n">
-        <v>-76.55201</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>St-Benoit</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Lead, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I98" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="n">
-        <v>13</v>
-      </c>
-      <c r="T98" t="n">
-        <v>325</v>
-      </c>
-      <c r="U98" t="n">
-        <v>55</v>
-      </c>
-      <c r="V98" t="n">
-        <v>47.99637</v>
-      </c>
-      <c r="W98" t="n">
-        <v>-67.11127</v>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Mid-Patapédia</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Lead, Silver, Zinc, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I99" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="n">
-        <v>13</v>
-      </c>
-      <c r="T99" t="n">
-        <v>325</v>
-      </c>
-      <c r="U99" t="n">
-        <v>55</v>
-      </c>
-      <c r="V99" t="n">
-        <v>47.86378</v>
-      </c>
-      <c r="W99" t="n">
-        <v>-67.38485</v>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Copper, Lead</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I100" t="b">
-        <v>1</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="n">
-        <v>13</v>
-      </c>
-      <c r="T100" t="n">
-        <v>325</v>
-      </c>
-      <c r="U100" t="n">
-        <v>55</v>
-      </c>
-      <c r="V100" t="n">
-        <v>50.31401</v>
-      </c>
-      <c r="W100" t="n">
-        <v>-62.73908</v>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Géant Dormant</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.2 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Au 32.94 g/t, Ag 11.80 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="V2" t="n">
-        <v>49.13127</v>
+        <v>45.3192</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.97206</v>
+        <v>-71.92023</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4515</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Au 29.25 g/t, W 0.122%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>45.3192</v>
+        <v>52.64108</v>
       </c>
       <c r="W3" t="n">
-        <v>-71.92023</v>
+        <v>-75.67010999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Mont Opémiska No 1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Palladium, Copper, Gold, Egp, Silver</t>
+          <t>Gold, Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>53.34013</v>
+        <v>49.95224</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.32316</v>
+        <v>-74.8797</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
         </is>
       </c>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Orfée Est</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Au 10.53 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>53.39936</v>
+        <v>53.46148</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.29407</v>
+        <v>-75.20878999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=402</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Sylvie</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,17 +892,17 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>53.40387</v>
+        <v>61.39737</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.30118</v>
+        <v>-74.97753</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Timtu</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,12 +975,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nickel, Chromium, Copper, Silver</t>
+          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>53.38014</v>
+        <v>61.43006</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.28712</v>
+        <v>-74.84983</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Getty</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,17 +1048,17 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc, Arsenic, Copper</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>53.40779</v>
+        <v>61.39535</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.28636</v>
+        <v>-75.00066</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,17 +1126,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nickel, Palladium, Gold, Zinc, Silver, Copper, Lead, Cobalt, Egp</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>53.39996</v>
+        <v>61.39368</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.33163999999999</v>
+        <v>-75.1713</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten, Copper, Zinc, Lead</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>53.39256</v>
+        <v>61.55073</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.43714</v>
+        <v>-72.66555</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tungsten, Gold, Silver, Copper, Lead</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>53.39458</v>
+        <v>52.17253</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.44683999999999</v>
+        <v>-76.55762</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Glencoe</t>
+          <t>Lemoyne-Extension</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
+          <t>Au 6.22 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>45.32873</v>
+        <v>53.45927</v>
       </c>
       <c r="W12" t="n">
-        <v>-72.47421</v>
+        <v>-75.18433</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=398</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Petit Lac Brompton</t>
+          <t>Orfée</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
+          <t>Au 67.35 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>45.44828</v>
+        <v>53.46154</v>
       </c>
       <c r="W13" t="n">
-        <v>-72.1057</v>
+        <v>-75.21647</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=399</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>de l'Ours</t>
+          <t>RA13-03</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 27.00 g/t</t>
+          <t>Au 3.71 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.61441</v>
+        <v>53.1949</v>
       </c>
       <c r="W14" t="n">
-        <v>-71.97407</v>
+        <v>-77.66768999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
         </is>
       </c>
     </row>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dead Mouse extension</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 18.36 g/t</t>
+          <t>Au 12.91 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.61747</v>
+        <v>53.51022</v>
       </c>
       <c r="W15" t="n">
-        <v>-71.97382</v>
+        <v>-75.46174000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bourdon</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 21.80 g/t</t>
+          <t>Au 144.55 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>53.62313</v>
+        <v>53.52019</v>
       </c>
       <c r="W16" t="n">
-        <v>-71.96111999999999</v>
+        <v>-75.40980999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>49.82919</v>
+        <v>53.43724</v>
       </c>
       <c r="W17" t="n">
-        <v>-70.58076</v>
+        <v>-75.04334</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bolt</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 2.9%, Ni 0.261%, Ag 17.40 g/t</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1870,23 +1870,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>61.57527</v>
+        <v>53.48752</v>
       </c>
       <c r="W18" t="n">
-        <v>-74.46583</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26280</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Cadmium, Lead, Silver, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>45.29835</v>
+        <v>52.17024</v>
       </c>
       <c r="W19" t="n">
-        <v>-72.31643</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>53.39786</v>
+        <v>52.1766</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.30625000000001</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Nasigon (Lac Lajoue)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Iron, Cobalt</t>
+          <t>Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.24734</v>
+        <v>47.53875</v>
       </c>
       <c r="W21" t="n">
-        <v>-71.98866</v>
+        <v>-75.10978</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>53.35887</v>
+        <v>52.03235</v>
       </c>
       <c r="W22" t="n">
-        <v>-77.31016</v>
+        <v>-69.13816</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>RA13-02</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>53.41679</v>
+        <v>53.17502</v>
       </c>
       <c r="W23" t="n">
-        <v>-77.27167</v>
+        <v>-77.75697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Orage</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 4.6%, Ag 16.90 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>46.26265</v>
+        <v>53.68741</v>
       </c>
       <c r="W24" t="n">
-        <v>-71.21769</v>
+        <v>-76.22185</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=468</t>
         </is>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Baleine Rouge Au-Zn-Pb</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>46.265</v>
+        <v>55.23561</v>
       </c>
       <c r="W25" t="n">
-        <v>-71.21259999999999</v>
+        <v>-67.9516</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Sond. LGS09-217</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>46.27176</v>
+        <v>53.528</v>
       </c>
       <c r="W26" t="n">
-        <v>-71.28612</v>
+        <v>-76.54774999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Lac Nasigon</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 4.4%, Ag 96.30 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>46.26532</v>
+        <v>47.53085</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.28788</v>
+        <v>-75.11848000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eli SE</t>
+          <t>Comtois NW</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Copper, Vanadium, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 25.00 g/t, Cu 1.02%, V 0.228%, Ag 16.70 g/t</t>
+          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>53.10465</v>
+        <v>49.18766</v>
       </c>
       <c r="W28" t="n">
-        <v>-77.28514</v>
+        <v>-77.31872</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=32103</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Jedi</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,17 +2686,17 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 11.50 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>45.42731</v>
+        <v>54.84385</v>
       </c>
       <c r="W29" t="n">
-        <v>-70.92610999999999</v>
+        <v>-69.86212</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead, Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>45.43447</v>
+        <v>54.8722</v>
       </c>
       <c r="W30" t="n">
-        <v>-70.9088</v>
+        <v>-69.81637000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Tricorne</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>45.43568</v>
+        <v>54.85039</v>
       </c>
       <c r="W31" t="n">
-        <v>-70.91788</v>
+        <v>-69.85742</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Jedi Extension</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Au 5.89 g/t, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>45.40513</v>
+        <v>54.85448</v>
       </c>
       <c r="W32" t="n">
-        <v>-70.9376</v>
+        <v>-69.83853000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11102</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Golden Idol</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 9.09 g/t, Zn 0.087%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>49.84595</v>
+        <v>53.57002</v>
       </c>
       <c r="W33" t="n">
-        <v>-70.57626</v>
+        <v>-72.41676</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>52.03235</v>
+        <v>53.41679</v>
       </c>
       <c r="W34" t="n">
-        <v>-69.13816</v>
+        <v>-77.27167</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Silver, Copper, Manganese, Zinc</t>
+          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3196,23 +3196,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>46.00535</v>
+        <v>53.39256</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.70357</v>
+        <v>-77.43714</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Gold, Tungsten, Lead, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>45.03676</v>
+        <v>53.39458</v>
       </c>
       <c r="W36" t="n">
-        <v>-72.77243</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>TR-00-126</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 20.70 g/t</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>49.83681</v>
+        <v>53.53822</v>
       </c>
       <c r="W37" t="n">
-        <v>-70.57877999999999</v>
+        <v>-76.48351</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=491</t>
         </is>
       </c>
     </row>
@@ -3378,22 +3378,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>TR-00-129, 130 et 131</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Egp, Palladium, Platinum, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Au 35.04 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>61.55073</v>
+        <v>53.53948</v>
       </c>
       <c r="W38" t="n">
-        <v>-72.66555</v>
+        <v>-76.47684</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=492</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Zone no 7</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Au 7.54 g/t, Ag 258.86 g/t, Zn 8.05%, Pb 11.4%, Cu 0.7%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3508,23 +3508,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>48.32328</v>
+        <v>53.1821</v>
       </c>
       <c r="W39" t="n">
-        <v>-79.44637</v>
+        <v>-77.71374</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=496</t>
         </is>
       </c>
     </row>
@@ -3534,22 +3534,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold, Lead</t>
+          <t>Gold, Beryllium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>48.37403</v>
+        <v>52.03237</v>
       </c>
       <c r="W40" t="n">
-        <v>-65.44089</v>
+        <v>-75.13809999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>46.26109</v>
+        <v>49.24734</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.22866</v>
+        <v>-71.98866</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Zinc, Lead</t>
+          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>47.99637</v>
+        <v>53.39996</v>
       </c>
       <c r="W42" t="n">
-        <v>-67.11127</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead</t>
+          <t>Palladium, Egp, Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>50.31401</v>
+        <v>53.34013</v>
       </c>
       <c r="W43" t="n">
-        <v>-62.73908</v>
+        <v>-77.32316</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>48.09296</v>
+        <v>53.39786</v>
       </c>
       <c r="W44" t="n">
-        <v>-66.78681</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>48.173</v>
+        <v>53.35887</v>
       </c>
       <c r="W45" t="n">
-        <v>-78.14212999999999</v>
+        <v>-77.31016</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lac Walsh-Ouest</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Chromium, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>55.15269</v>
+        <v>53.38014</v>
       </c>
       <c r="W46" t="n">
-        <v>-66.35399</v>
+        <v>-77.28712</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Pogo</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold, Silver</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>55.23261</v>
+        <v>53.40387</v>
       </c>
       <c r="W47" t="n">
-        <v>-66.16073</v>
+        <v>-77.30118</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lac Rocher</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,17 +4168,17 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Nickel, Copper, Egp, Gold, Cobalt</t>
+          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ni 13.2%, Cu 11.4%, Pt 2.49 g/t, Co 0.23%, Au 0.50 g/t</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>50.58471</v>
+        <v>53.39936</v>
       </c>
       <c r="W48" t="n">
-        <v>-76.34242</v>
+        <v>-77.29407</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4260</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Arsenic</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>49.78784</v>
+        <v>53.40779</v>
       </c>
       <c r="W49" t="n">
-        <v>-77.08529</v>
+        <v>-77.28636</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Golden Idol</t>
+          <t>Coconut Club</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Etr, Thorium, Uranium, Zr, Gold, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Au 9.09 g/t, Zn 0.087%</t>
+          <t>Au 7.94 g/t, U 0.0864%, Ag 33.10 g/t, ETR 1.05%, Th 0.621%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>53.57002</v>
+        <v>46.99057</v>
       </c>
       <c r="W50" t="n">
-        <v>-72.41676</v>
+        <v>-78.59457999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=535</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Amaruk</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 84.26 g/t, Ag 18.20 g/t</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,23 +4444,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T51" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U51" t="n">
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>59.60263</v>
+        <v>48.32328</v>
       </c>
       <c r="W51" t="n">
-        <v>-74.86282</v>
+        <v>-79.44637</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lac Barlow</t>
+          <t>Zone Cyr</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Silver, Gold, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+          <t>Cu 5.81%, Au 2.12 g/t, Ag 70.00 g/t, Zn 0.46%, Pb 0.19%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4531,14 +4531,14 @@
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>49.94431</v>
+        <v>52.2425</v>
       </c>
       <c r="W52" t="n">
-        <v>-74.71456000000001</v>
+        <v>-76.59574000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=566</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Au 278.00 g/t</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>49.95224</v>
+        <v>52.1821</v>
       </c>
       <c r="W53" t="n">
-        <v>-74.8797</v>
+        <v>-76.70099999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sond. SER-21-040</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 8.71 g/t</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>53.08409</v>
+        <v>50.64946</v>
       </c>
       <c r="W54" t="n">
-        <v>-77.20562</v>
+        <v>-75.04613999999999</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Boulder Shear (Cuvier-Est)</t>
+          <t>Wab-88-0406</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,12 +4714,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Arsenic, Copper</t>
+          <t>Copper, Gold, Silver, Molybdenum, Bismuth, Tellurium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
+          <t>Au 5.74 g/t, Cu 2.4%, Mo 0.0901%, Ag 13.50 g/t, Te 0.004%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T55" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U55" t="n">
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>49.9399</v>
+        <v>52.23706</v>
       </c>
       <c r="W55" t="n">
-        <v>-74.70344</v>
+        <v>-76.60512</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=562</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CaribGold 99-07</t>
+          <t>Miltin</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold, Bismuth, Chromium, Zinc, Nickel, Egp, Palladium, Platinum, Silver</t>
+          <t>Silver, Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Au 16.94 g/t, Bi 0.158%, Pt 0.10 g/t, Ag 4.90 g/t, Cr 0.1%</t>
+          <t>Au 36.48 g/t, Cu 10.5%, Ag 52.00 g/t</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>50.75408</v>
+        <v>52.2473</v>
       </c>
       <c r="W56" t="n">
-        <v>-76.84898</v>
+        <v>-76.50475</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4248</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=565</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>Isabelle</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,12 +4870,12 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Au 316.18 g/t, Ag 7.50 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,14 +4921,3212 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
+        <v>52.09336</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-76.75954</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=578</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Lac Delta NW-Cuivre</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Au 13.33 g/t, Cu 7.3%, Ag 20.30 g/t</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>13</v>
+      </c>
+      <c r="T58" t="n">
+        <v>325</v>
+      </c>
+      <c r="U58" t="n">
+        <v>55</v>
+      </c>
+      <c r="V58" t="n">
+        <v>52.23158</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-76.4002</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=593</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Viau (ou Bordulac)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Au 31.00 g/t</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>13</v>
+      </c>
+      <c r="T59" t="n">
+        <v>325</v>
+      </c>
+      <c r="U59" t="n">
+        <v>55</v>
+      </c>
+      <c r="V59" t="n">
+        <v>48.26547</v>
+      </c>
+      <c r="W59" t="n">
+        <v>-79.41453</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lac Delta Nord (Grid C.22)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Au 4.71 g/t, Cu 1.81%, Ag 14.00 g/t, Zn 0.54%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>13</v>
+      </c>
+      <c r="T60" t="n">
+        <v>325</v>
+      </c>
+      <c r="U60" t="n">
+        <v>55</v>
+      </c>
+      <c r="V60" t="n">
+        <v>52.24319</v>
+      </c>
+      <c r="W60" t="n">
+        <v>-76.36844000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=598</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Zone Chino</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Au 24.69 g/t, Ag 2.80 g/t</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>13</v>
+      </c>
+      <c r="T61" t="n">
+        <v>325</v>
+      </c>
+      <c r="U61" t="n">
+        <v>55</v>
+      </c>
+      <c r="V61" t="n">
+        <v>52.17342</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-76.44268</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=600</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Zone QET</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Au 14.50 g/t, Cu 0.96%, Ag 11.20 g/t</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>13</v>
+      </c>
+      <c r="T62" t="n">
+        <v>325</v>
+      </c>
+      <c r="U62" t="n">
+        <v>55</v>
+      </c>
+      <c r="V62" t="n">
+        <v>52.24811</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-76.49615</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=606</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Lac Tarsac : Veine I et III</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gold, Lead, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Au 11.66 g/t</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="n">
+        <v>150</v>
+      </c>
+      <c r="U63" t="n">
+        <v>55</v>
+      </c>
+      <c r="V63" t="n">
+        <v>48.3561</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-79.43788000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Huckleberry</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Au 0.40 g/t</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>13</v>
+      </c>
+      <c r="T64" t="n">
+        <v>325</v>
+      </c>
+      <c r="U64" t="n">
+        <v>55</v>
+      </c>
+      <c r="V64" t="n">
+        <v>55.78035</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-66.95337000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Nisto</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Zinc, Copper, Lead, Uranium</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Cu 5.6%, Zn 5.4%, U 0.03%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>13</v>
+      </c>
+      <c r="T65" t="n">
+        <v>325</v>
+      </c>
+      <c r="U65" t="n">
+        <v>55</v>
+      </c>
+      <c r="V65" t="n">
+        <v>50.3605</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-63.13619</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=665</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Destorbelle</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Au 8.20 g/t</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>11</v>
+      </c>
+      <c r="T66" t="n">
+        <v>275</v>
+      </c>
+      <c r="U66" t="n">
+        <v>55</v>
+      </c>
+      <c r="V66" t="n">
+        <v>48.4465</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-78.85312999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Soucy No 1 - Zones A et D</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Zinc, Gold, Copper, Lead, Silver</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Cu 1.72%, Au 1.61 g/t, Zn 2.77%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>325</v>
+      </c>
+      <c r="U67" t="n">
+        <v>55</v>
+      </c>
+      <c r="V67" t="n">
+        <v>58.32867</v>
+      </c>
+      <c r="W67" t="n">
+        <v>-69.86747</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=677</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Prud'Homme No 1 : Zone Sud</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gold, Zinc, Copper, Nickel, Silver</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cu 4.65%, Zn 12%, Au 1.25 g/t, Ag 29.77 g/t</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>13</v>
+      </c>
+      <c r="T68" t="n">
+        <v>325</v>
+      </c>
+      <c r="U68" t="n">
+        <v>55</v>
+      </c>
+      <c r="V68" t="n">
+        <v>58.25921</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-69.91007999999999</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=679</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Petit-Pas</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Au 52.87 g/t, Ag 5.10 g/t</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>13</v>
+      </c>
+      <c r="T69" t="n">
+        <v>325</v>
+      </c>
+      <c r="U69" t="n">
+        <v>55</v>
+      </c>
+      <c r="V69" t="n">
+        <v>53.48965</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-72.12729</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=686</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Red Toad</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Au 153.00 g/t</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>13</v>
+      </c>
+      <c r="T70" t="n">
+        <v>325</v>
+      </c>
+      <c r="U70" t="n">
+        <v>55</v>
+      </c>
+      <c r="V70" t="n">
+        <v>54.08287</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-72.50529</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=712</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sortilèges Dorés Ouest</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Au 3.65 g/t, Cu 0.223%, Ag 3.50 g/t, Zn 0.229%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>13</v>
+      </c>
+      <c r="T71" t="n">
+        <v>325</v>
+      </c>
+      <c r="U71" t="n">
+        <v>55</v>
+      </c>
+      <c r="V71" t="n">
+        <v>54.06291</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-72.57297</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=717</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Jackson (Minerais Lac)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>12</v>
+      </c>
+      <c r="T72" t="n">
+        <v>300</v>
+      </c>
+      <c r="U72" t="n">
+        <v>55</v>
+      </c>
+      <c r="V72" t="n">
+        <v>45.52972</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-71.65783999999999</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Été Indien</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Au 23.43 g/t, Ag 12.30 g/t</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>13</v>
+      </c>
+      <c r="T73" t="n">
+        <v>325</v>
+      </c>
+      <c r="U73" t="n">
+        <v>55</v>
+      </c>
+      <c r="V73" t="n">
+        <v>54.07321</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-72.52986</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=696</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lingo 3 Ouest</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gold, Lead, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Au 3230.89 g/t, Ag 17.30 g/t, Pb 0.000128%, Zn 0.107%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>13</v>
+      </c>
+      <c r="T74" t="n">
+        <v>325</v>
+      </c>
+      <c r="U74" t="n">
+        <v>55</v>
+      </c>
+      <c r="V74" t="n">
+        <v>54.07075</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-72.53373000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=698</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Grenouille 2</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Au 3527.00 g/t, Ag 18.30 g/t</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>13</v>
+      </c>
+      <c r="T75" t="n">
+        <v>325</v>
+      </c>
+      <c r="U75" t="n">
+        <v>55</v>
+      </c>
+      <c r="V75" t="n">
+        <v>54.07734</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-72.51860000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=702</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Moman</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Au 3527.40 g/t</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>325</v>
+      </c>
+      <c r="U76" t="n">
+        <v>55</v>
+      </c>
+      <c r="V76" t="n">
+        <v>54.07892</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-72.51427</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=704</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Slowdance</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Gold, Zinc, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Au 4.63 g/t, Cu 0.104%, Ag 4.50 g/t, Zn 0.221%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
+        <v>325</v>
+      </c>
+      <c r="U77" t="n">
+        <v>55</v>
+      </c>
+      <c r="V77" t="n">
+        <v>54.0731</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-72.54952</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=705</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bourdon</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Au 21.80 g/t</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>325</v>
+      </c>
+      <c r="U78" t="n">
+        <v>55</v>
+      </c>
+      <c r="V78" t="n">
+        <v>53.62313</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-71.96111999999999</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ugo</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Au 251.66 g/t</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>325</v>
+      </c>
+      <c r="U79" t="n">
+        <v>55</v>
+      </c>
+      <c r="V79" t="n">
+        <v>53.53343</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-76.53331</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Brèche</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Au 8.56 g/t</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>13</v>
+      </c>
+      <c r="T80" t="n">
+        <v>325</v>
+      </c>
+      <c r="U80" t="n">
+        <v>55</v>
+      </c>
+      <c r="V80" t="n">
+        <v>53.53187</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-76.54353</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pari</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Au 730.77 g/t</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>13</v>
+      </c>
+      <c r="T81" t="n">
+        <v>325</v>
+      </c>
+      <c r="U81" t="n">
+        <v>55</v>
+      </c>
+      <c r="V81" t="n">
+        <v>53.53306</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-76.55201</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Zone 32</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>13</v>
+      </c>
+      <c r="T82" t="n">
+        <v>325</v>
+      </c>
+      <c r="U82" t="n">
+        <v>55</v>
+      </c>
+      <c r="V82" t="n">
+        <v>53.52649</v>
+      </c>
+      <c r="W82" t="n">
+        <v>-76.56404999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>As-3</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Au 6.38 g/t</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>13</v>
+      </c>
+      <c r="T83" t="n">
+        <v>325</v>
+      </c>
+      <c r="U83" t="n">
+        <v>55</v>
+      </c>
+      <c r="V83" t="n">
+        <v>53.52425</v>
+      </c>
+      <c r="W83" t="n">
+        <v>-76.57341</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Au 36.38 g/t</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>13</v>
+      </c>
+      <c r="T84" t="n">
+        <v>325</v>
+      </c>
+      <c r="U84" t="n">
+        <v>55</v>
+      </c>
+      <c r="V84" t="n">
+        <v>53.52499</v>
+      </c>
+      <c r="W84" t="n">
+        <v>-76.58275</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Zone 35-L11W</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Au 35.31 g/t</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>13</v>
+      </c>
+      <c r="T85" t="n">
+        <v>325</v>
+      </c>
+      <c r="U85" t="n">
+        <v>55</v>
+      </c>
+      <c r="V85" t="n">
+        <v>53.52296</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-76.59889</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Wedding</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Au 32.73 g/t</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>13</v>
+      </c>
+      <c r="T86" t="n">
+        <v>325</v>
+      </c>
+      <c r="U86" t="n">
+        <v>55</v>
+      </c>
+      <c r="V86" t="n">
+        <v>53.51886</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-76.60854</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Zone 32 (Tonalite-Zone Veine)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>13</v>
+      </c>
+      <c r="T87" t="n">
+        <v>325</v>
+      </c>
+      <c r="U87" t="n">
+        <v>55</v>
+      </c>
+      <c r="V87" t="n">
+        <v>53.5291</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-76.56155</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Zone 32 (Mico-Milan)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Au 72.69 g/t</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>13</v>
+      </c>
+      <c r="T88" t="n">
+        <v>325</v>
+      </c>
+      <c r="U88" t="n">
+        <v>55</v>
+      </c>
+      <c r="V88" t="n">
+        <v>53.52891</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-76.56541</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TRH-96-07</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Au 19.59 g/t</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>13</v>
+      </c>
+      <c r="T89" t="n">
+        <v>325</v>
+      </c>
+      <c r="U89" t="n">
+        <v>55</v>
+      </c>
+      <c r="V89" t="n">
+        <v>53.52311</v>
+      </c>
+      <c r="W89" t="n">
+        <v>-76.61015</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pari (Zone 30)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Copper, Gold</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Au 13.50 g/t, Cu 0.57%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>13</v>
+      </c>
+      <c r="T90" t="n">
+        <v>325</v>
+      </c>
+      <c r="U90" t="n">
+        <v>55</v>
+      </c>
+      <c r="V90" t="n">
+        <v>53.5301</v>
+      </c>
+      <c r="W90" t="n">
+        <v>-76.55025999999999</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Filion</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Cobalt</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>13</v>
+      </c>
+      <c r="T91" t="n">
+        <v>325</v>
+      </c>
+      <c r="U91" t="n">
+        <v>55</v>
+      </c>
+      <c r="V91" t="n">
+        <v>46.61092</v>
+      </c>
+      <c r="W91" t="n">
+        <v>-75.97769</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>St-Benoit</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Lead, Zinc, Silver</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>13</v>
+      </c>
+      <c r="T92" t="n">
+        <v>325</v>
+      </c>
+      <c r="U92" t="n">
+        <v>55</v>
+      </c>
+      <c r="V92" t="n">
+        <v>47.99637</v>
+      </c>
+      <c r="W92" t="n">
+        <v>-67.11127</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mid-Patapédia</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lead, Silver, Zinc, Gold, Copper</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>13</v>
+      </c>
+      <c r="T93" t="n">
+        <v>325</v>
+      </c>
+      <c r="U93" t="n">
+        <v>55</v>
+      </c>
+      <c r="V93" t="n">
         <v>47.86378</v>
       </c>
-      <c r="W57" t="n">
+      <c r="W93" t="n">
         <v>-67.38485</v>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BJB - Rustcliff (Boudrias)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Silver, Gold, Copper, Lead</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>13</v>
+      </c>
+      <c r="T94" t="n">
+        <v>325</v>
+      </c>
+      <c r="U94" t="n">
+        <v>55</v>
+      </c>
+      <c r="V94" t="n">
+        <v>50.31401</v>
+      </c>
+      <c r="W94" t="n">
+        <v>-62.73908</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Projet 70-Landome</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Copper, Silver, Zinc, Gold</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>13</v>
+      </c>
+      <c r="T95" t="n">
+        <v>325</v>
+      </c>
+      <c r="U95" t="n">
+        <v>55</v>
+      </c>
+      <c r="V95" t="n">
+        <v>48.46123</v>
+      </c>
+      <c r="W95" t="n">
+        <v>-77.95265999999999</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>de l'Ours</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Au 27.00 g/t</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>13</v>
+      </c>
+      <c r="T96" t="n">
+        <v>325</v>
+      </c>
+      <c r="U96" t="n">
+        <v>55</v>
+      </c>
+      <c r="V96" t="n">
+        <v>53.61441</v>
+      </c>
+      <c r="W96" t="n">
+        <v>-71.97407</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Dead Mouse extension</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Au 18.36 g/t</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>13</v>
+      </c>
+      <c r="T97" t="n">
+        <v>325</v>
+      </c>
+      <c r="U97" t="n">
+        <v>55</v>
+      </c>
+      <c r="V97" t="n">
+        <v>53.61747</v>
+      </c>
+      <c r="W97" t="n">
+        <v>-71.97382</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ELR-16-002</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Au 9.13 g/t</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>13</v>
+      </c>
+      <c r="T98" t="n">
+        <v>325</v>
+      </c>
+      <c r="U98" t="n">
+        <v>55</v>
+      </c>
+      <c r="V98" t="n">
+        <v>52.67859</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-76.30803</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X98"/>
+  <dimension ref="A1:X99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Mine Géant Dormant</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>3.2 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Au 32.94 g/t, Ag 11.80 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U2" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="V2" t="n">
-        <v>45.3192</v>
+        <v>49.13127</v>
       </c>
       <c r="W2" t="n">
-        <v>-71.92023</v>
+        <v>-77.97206</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4515</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="V3" t="n">
-        <v>52.64108</v>
+        <v>45.3192</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.67010999999999</v>
+        <v>-71.92023</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver</t>
+          <t>Tungsten, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Au 29.25 g/t, W 0.122%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>49.95224</v>
+        <v>52.64108</v>
       </c>
       <c r="W4" t="n">
-        <v>-74.8797</v>
+        <v>-75.67010999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
         </is>
       </c>
     </row>
@@ -804,11 +804,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orfée Est</t>
+          <t>Mont Opémiska No 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 10.53 g/t</t>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>53.46148</v>
+        <v>49.95224</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.20878999999999</v>
+        <v>-74.8797</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=402</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
         </is>
       </c>
     </row>
@@ -882,27 +882,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sylvie</t>
+          <t>Orfée Est</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
+          <t>Au 10.53 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>61.39737</v>
+        <v>53.46148</v>
       </c>
       <c r="W6" t="n">
-        <v>-74.97753</v>
+        <v>-75.20878999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=402</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timtu</t>
+          <t>Sylvie</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
+          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>61.43006</v>
+        <v>61.39737</v>
       </c>
       <c r="W7" t="n">
-        <v>-74.84983</v>
+        <v>-74.97753</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Getty</t>
+          <t>Timtu</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
+          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
+          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>61.39535</v>
+        <v>61.43006</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.00066</v>
+        <v>-74.84983</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mystery</t>
+          <t>Getty</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
+          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>61.39368</v>
+        <v>61.39535</v>
       </c>
       <c r="W9" t="n">
-        <v>-75.1713</v>
+        <v>-75.00066</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>61.55073</v>
+        <v>61.39368</v>
       </c>
       <c r="W10" t="n">
-        <v>-72.66555</v>
+        <v>-75.1713</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>52.17253</v>
+        <v>61.55073</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.55762</v>
+        <v>-72.66555</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lemoyne-Extension</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 6.22 g/t</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>53.45927</v>
+        <v>52.17253</v>
       </c>
       <c r="W12" t="n">
-        <v>-75.18433</v>
+        <v>-76.55762</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=398</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Orfée</t>
+          <t>Lemoyne-Extension</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 67.35 g/t</t>
+          <t>Au 6.22 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.46154</v>
+        <v>53.45927</v>
       </c>
       <c r="W13" t="n">
-        <v>-75.21647</v>
+        <v>-75.18433</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=399</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=398</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RA13-03</t>
+          <t>Orfée</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 3.71 g/t</t>
+          <t>Au 67.35 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.1949</v>
+        <v>53.46154</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.66768999999999</v>
+        <v>-75.21647</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=399</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>RA13-03</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 12.91 g/t</t>
+          <t>Au 3.71 g/t</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.51022</v>
+        <v>53.1949</v>
       </c>
       <c r="W15" t="n">
-        <v>-75.46174000000001</v>
+        <v>-77.66768999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 144.55 g/t</t>
+          <t>Au 12.91 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>53.52019</v>
+        <v>53.51022</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.40980999999999</v>
+        <v>-75.46174000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Au 144.55 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>53.43724</v>
+        <v>53.52019</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.04334</v>
+        <v>-75.40980999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Galexis</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>53.48752</v>
+        <v>53.43724</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.33392000000001</v>
+        <v>-75.04334</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mustang</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>52.17024</v>
+        <v>53.48752</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.57532999999999</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lac Nitakwin</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 6.06 g/t</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>52.1766</v>
+        <v>52.17024</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.71138999999999</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nasigon (Lac Lajoue)</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>47.53875</v>
+        <v>52.1766</v>
       </c>
       <c r="W21" t="n">
-        <v>-75.10978</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Nasigon (Lac Lajoue)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Copper, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>52.03235</v>
+        <v>47.53875</v>
       </c>
       <c r="W22" t="n">
-        <v>-69.13816</v>
+        <v>-75.10978</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RA13-02</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>53.17502</v>
+        <v>52.03235</v>
       </c>
       <c r="W23" t="n">
-        <v>-77.75697</v>
+        <v>-69.13816</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Orage</t>
+          <t>RA13-02</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Ag 16.90 g/t</t>
+          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>53.68741</v>
+        <v>53.17502</v>
       </c>
       <c r="W24" t="n">
-        <v>-76.22185</v>
+        <v>-77.75697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=468</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Baleine Rouge Au-Zn-Pb</t>
+          <t>Orage</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2374,12 +2374,12 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+          <t>Cu 4.6%, Ag 16.90 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>55.23561</v>
+        <v>53.68741</v>
       </c>
       <c r="W25" t="n">
-        <v>-67.9516</v>
+        <v>-76.22185</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=468</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sond. LGS09-217</t>
+          <t>Baleine Rouge Au-Zn-Pb</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>53.528</v>
+        <v>55.23561</v>
       </c>
       <c r="W26" t="n">
-        <v>-76.54774999999999</v>
+        <v>-67.9516</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lac Nasigon</t>
+          <t>Sond. LGS09-217</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 4.4%, Ag 96.30 g/t</t>
+          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>47.53085</v>
+        <v>53.528</v>
       </c>
       <c r="W27" t="n">
-        <v>-75.11848000000001</v>
+        <v>-76.54774999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Comtois NW</t>
+          <t>Lac Nasigon</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
+          <t>Cu 4.4%, Ag 96.30 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>49.18766</v>
+        <v>47.53085</v>
       </c>
       <c r="W28" t="n">
-        <v>-77.31872</v>
+        <v>-75.11848000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jedi</t>
+          <t>Comtois NW</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 11.50 g/t</t>
+          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>54.84385</v>
+        <v>49.18766</v>
       </c>
       <c r="W29" t="n">
-        <v>-69.86212</v>
+        <v>-77.31872</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Jedi</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
+          <t>Au 11.50 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>54.8722</v>
+        <v>54.84385</v>
       </c>
       <c r="W30" t="n">
-        <v>-69.81637000000001</v>
+        <v>-69.86212</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tricorne</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
+          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>54.85039</v>
+        <v>54.8722</v>
       </c>
       <c r="W31" t="n">
-        <v>-69.85742</v>
+        <v>-69.81637000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jedi Extension</t>
+          <t>Tricorne</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 5.89 g/t, Ag 6.50 g/t</t>
+          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>54.85448</v>
+        <v>54.85039</v>
       </c>
       <c r="W32" t="n">
-        <v>-69.83853000000001</v>
+        <v>-69.85742</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11102</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Golden Idol</t>
+          <t>Jedi Extension</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 9.09 g/t, Zn 0.087%</t>
+          <t>Au 5.89 g/t, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>53.57002</v>
+        <v>54.85448</v>
       </c>
       <c r="W33" t="n">
-        <v>-72.41676</v>
+        <v>-69.83853000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11102</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Golden Idol</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Silver, Gold, Arsenic</t>
+          <t>Gold, Zinc</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Au 9.09 g/t, Zn 0.087%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.41679</v>
+        <v>53.57002</v>
       </c>
       <c r="W34" t="n">
-        <v>-77.27167</v>
+        <v>-72.41676</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Bonspot</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>53.39256</v>
+        <v>53.41679</v>
       </c>
       <c r="W35" t="n">
-        <v>-77.43714</v>
+        <v>-77.27167</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Lead, Copper</t>
+          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>53.39458</v>
+        <v>53.39256</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.44683999999999</v>
+        <v>-77.43714</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TR-00-126</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Tungsten, Lead, Copper</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 20.70 g/t</t>
+          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>53.53822</v>
+        <v>53.39458</v>
       </c>
       <c r="W37" t="n">
-        <v>-76.48351</v>
+        <v>-77.44683999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
         </is>
       </c>
     </row>
@@ -3378,11 +3378,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TR-00-129, 130 et 131</t>
+          <t>TR-00-126</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 35.04 g/t</t>
+          <t>Au 20.70 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>53.53948</v>
+        <v>53.53822</v>
       </c>
       <c r="W38" t="n">
-        <v>-76.47684</v>
+        <v>-76.48351</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=492</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=491</t>
         </is>
       </c>
     </row>
@@ -3456,22 +3456,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zone no 7</t>
+          <t>TR-00-129, 130 et 131</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Ag 258.86 g/t, Zn 8.05%, Pb 11.4%, Cu 0.7%</t>
+          <t>Au 35.04 g/t</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>53.1821</v>
+        <v>53.53948</v>
       </c>
       <c r="W39" t="n">
-        <v>-77.71374</v>
+        <v>-76.47684</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=496</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=492</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Zone no 7</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Beryllium</t>
+          <t>Copper, Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 7.54 g/t, Ag 258.86 g/t, Zn 8.05%, Pb 11.4%, Cu 0.7%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>52.03237</v>
+        <v>53.1821</v>
       </c>
       <c r="W40" t="n">
-        <v>-75.13809999999999</v>
+        <v>-77.71374</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=496</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Gold, Beryllium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>49.24734</v>
+        <v>52.03237</v>
       </c>
       <c r="W41" t="n">
-        <v>-71.98866</v>
+        <v>-75.13809999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Mistass</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>53.39996</v>
+        <v>49.24734</v>
       </c>
       <c r="W42" t="n">
-        <v>-77.33163999999999</v>
+        <v>-71.98866</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper, Silver</t>
+          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>53.34013</v>
+        <v>53.39996</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.32316</v>
+        <v>-77.33163999999999</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
+          <t>Palladium, Egp, Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>53.39786</v>
+        <v>53.34013</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.30625000000001</v>
+        <v>-77.32316</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3985,14 +3985,14 @@
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>53.35887</v>
+        <v>53.39786</v>
       </c>
       <c r="W45" t="n">
-        <v>-77.31016</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Lac Yasinski-NE</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>53.38014</v>
+        <v>53.35887</v>
       </c>
       <c r="W46" t="n">
-        <v>-77.28712</v>
+        <v>-77.31016</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>4930N-1</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Chromium</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Chromium, Nickel, Copper, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>53.40387</v>
+        <v>53.38014</v>
       </c>
       <c r="W47" t="n">
-        <v>-77.30118</v>
+        <v>-77.28712</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Au-1</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>53.39936</v>
+        <v>53.40387</v>
       </c>
       <c r="W48" t="n">
-        <v>-77.29407</v>
+        <v>-77.30118</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Au-26</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
+          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>53.40779</v>
+        <v>53.39936</v>
       </c>
       <c r="W49" t="n">
-        <v>-77.28636</v>
+        <v>-77.29407</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Coconut Club</t>
+          <t>PG-221094</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Etr, Thorium, Uranium, Zr, Gold, Silver</t>
+          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Au 7.94 g/t, U 0.0864%, Ag 33.10 g/t, ETR 1.05%, Th 0.621%</t>
+          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>46.99057</v>
+        <v>53.40779</v>
       </c>
       <c r="W50" t="n">
-        <v>-78.59457999999999</v>
+        <v>-77.28636</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Coconut Club</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Etr, Thorium, Uranium, Zr, Gold, Silver</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Au 7.94 g/t, U 0.0864%, Ag 33.10 g/t, ETR 1.05%, Th 0.621%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4444,23 +4444,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>48.32328</v>
+        <v>46.99057</v>
       </c>
       <c r="W51" t="n">
-        <v>-79.44637</v>
+        <v>-78.59457999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=535</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Zone Cyr</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead, Zinc</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Cu 5.81%, Au 2.12 g/t, Ag 70.00 g/t, Zn 0.46%, Pb 0.19%</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4522,23 +4522,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U52" t="n">
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>52.2425</v>
+        <v>48.32328</v>
       </c>
       <c r="W52" t="n">
-        <v>-76.59574000000001</v>
+        <v>-79.44637</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=566</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Zone Cyr</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Copper, Lead, Zinc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Au 278.00 g/t</t>
+          <t>Cu 5.81%, Au 2.12 g/t, Ag 70.00 g/t, Zn 0.46%, Pb 0.19%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>52.1821</v>
+        <v>52.2425</v>
       </c>
       <c r="W53" t="n">
-        <v>-76.70099999999999</v>
+        <v>-76.59574000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=566</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 7.60 g/t</t>
+          <t>Au 278.00 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>50.64946</v>
+        <v>52.1821</v>
       </c>
       <c r="W54" t="n">
-        <v>-75.04613999999999</v>
+        <v>-76.70099999999999</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wab-88-0406</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4714,12 +4714,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Bismuth, Tellurium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 5.74 g/t, Cu 2.4%, Mo 0.0901%, Ag 13.50 g/t, Te 0.004%</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4765,14 +4765,14 @@
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>52.23706</v>
+        <v>50.64946</v>
       </c>
       <c r="W55" t="n">
-        <v>-76.60512</v>
+        <v>-75.04613999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=562</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Miltin</t>
+          <t>Wab-88-0406</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Zinc</t>
+          <t>Copper, Gold, Silver, Molybdenum, Bismuth, Tellurium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Au 36.48 g/t, Cu 10.5%, Ag 52.00 g/t</t>
+          <t>Au 5.74 g/t, Cu 2.4%, Mo 0.0901%, Ag 13.50 g/t, Te 0.004%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,14 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>52.2473</v>
+        <v>52.23706</v>
       </c>
       <c r="W56" t="n">
-        <v>-76.50475</v>
+        <v>-76.60512</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=565</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=562</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Isabelle</t>
+          <t>Miltin</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4870,12 +4870,12 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Silver, Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Au 316.18 g/t, Ag 7.50 g/t</t>
+          <t>Au 36.48 g/t, Cu 10.5%, Ag 52.00 g/t</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4921,14 +4921,14 @@
         <v>55</v>
       </c>
       <c r="V57" t="n">
-        <v>52.09336</v>
+        <v>52.2473</v>
       </c>
       <c r="W57" t="n">
-        <v>-76.75954</v>
+        <v>-76.50475</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=578</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=565</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lac Delta NW-Cuivre</t>
+          <t>Isabelle</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Au 13.33 g/t, Cu 7.3%, Ag 20.30 g/t</t>
+          <t>Au 316.18 g/t, Ag 7.50 g/t</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4999,14 +4999,14 @@
         <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>52.23158</v>
+        <v>52.09336</v>
       </c>
       <c r="W58" t="n">
-        <v>-76.4002</v>
+        <v>-76.75954</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=593</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=578</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Viau (ou Bordulac)</t>
+          <t>Lac Delta NW-Cuivre</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Au 31.00 g/t</t>
+          <t>Au 13.33 g/t, Cu 7.3%, Ag 20.30 g/t</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5077,14 +5077,14 @@
         <v>55</v>
       </c>
       <c r="V59" t="n">
-        <v>48.26547</v>
+        <v>52.23158</v>
       </c>
       <c r="W59" t="n">
-        <v>-79.41453</v>
+        <v>-76.4002</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=593</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lac Delta Nord (Grid C.22)</t>
+          <t>Viau (ou Bordulac)</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5104,12 +5104,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Au 4.71 g/t, Cu 1.81%, Ag 14.00 g/t, Zn 0.54%</t>
+          <t>Au 31.00 g/t</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5155,14 +5155,14 @@
         <v>55</v>
       </c>
       <c r="V60" t="n">
-        <v>52.24319</v>
+        <v>48.26547</v>
       </c>
       <c r="W60" t="n">
-        <v>-76.36844000000001</v>
+        <v>-79.41453</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=598</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Zone Chino</t>
+          <t>Lac Delta Nord (Grid C.22)</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5182,12 +5182,12 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Au 24.69 g/t, Ag 2.80 g/t</t>
+          <t>Au 4.71 g/t, Cu 1.81%, Ag 14.00 g/t, Zn 0.54%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>55</v>
       </c>
       <c r="V61" t="n">
-        <v>52.17342</v>
+        <v>52.24319</v>
       </c>
       <c r="W61" t="n">
-        <v>-76.44268</v>
+        <v>-76.36844000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=600</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=598</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zone QET</t>
+          <t>Zone Chino</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5260,12 +5260,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Au 14.50 g/t, Cu 0.96%, Ag 11.20 g/t</t>
+          <t>Au 24.69 g/t, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5311,14 +5311,14 @@
         <v>55</v>
       </c>
       <c r="V62" t="n">
-        <v>52.24811</v>
+        <v>52.17342</v>
       </c>
       <c r="W62" t="n">
-        <v>-76.49615</v>
+        <v>-76.44268</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=606</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=600</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lac Tarsac : Veine I et III</t>
+          <t>Zone QET</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -5338,12 +5338,12 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Lead, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Au 11.66 g/t</t>
+          <t>Au 14.50 g/t, Cu 0.96%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5380,23 +5380,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T63" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U63" t="n">
         <v>55</v>
       </c>
       <c r="V63" t="n">
-        <v>48.3561</v>
+        <v>52.24811</v>
       </c>
       <c r="W63" t="n">
-        <v>-79.43788000000001</v>
+        <v>-76.49615</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=606</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Huckleberry</t>
+          <t>Lac Tarsac : Veine I et III</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5416,12 +5416,12 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
+          <t>Gold, Lead, Copper, Silver</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Au 0.40 g/t</t>
+          <t>Au 11.66 g/t</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5458,23 +5458,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T64" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U64" t="n">
         <v>55</v>
       </c>
       <c r="V64" t="n">
-        <v>55.78035</v>
+        <v>48.3561</v>
       </c>
       <c r="W64" t="n">
-        <v>-66.95337000000001</v>
+        <v>-79.43788000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nisto</t>
+          <t>Huckleberry</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -5494,12 +5494,12 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Uranium</t>
+          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Zn 5.4%, U 0.03%</t>
+          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Au 0.40 g/t</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5545,14 +5545,14 @@
         <v>55</v>
       </c>
       <c r="V65" t="n">
-        <v>50.3605</v>
+        <v>55.78035</v>
       </c>
       <c r="W65" t="n">
-        <v>-63.13619</v>
+        <v>-66.95337000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=665</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Destorbelle</t>
+          <t>Nisto</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5572,12 +5572,12 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Lead, Uranium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Au 8.20 g/t</t>
+          <t>Cu 5.6%, Zn 5.4%, U 0.03%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5614,23 +5614,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>55</v>
       </c>
       <c r="V66" t="n">
-        <v>48.4465</v>
+        <v>50.3605</v>
       </c>
       <c r="W66" t="n">
-        <v>-78.85312999999999</v>
+        <v>-63.13619</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=665</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Soucy No 1 - Zones A et D</t>
+          <t>Destorbelle</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -5650,12 +5650,12 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Zinc, Gold, Copper, Lead, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Cu 1.72%, Au 1.61 g/t, Zn 2.77%</t>
+          <t>Au 8.20 g/t</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5692,23 +5692,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U67" t="n">
         <v>55</v>
       </c>
       <c r="V67" t="n">
-        <v>58.32867</v>
+        <v>48.4465</v>
       </c>
       <c r="W67" t="n">
-        <v>-69.86747</v>
+        <v>-78.85312999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=677</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Prud'Homme No 1 : Zone Sud</t>
+          <t>Soucy No 1 - Zones A et D</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5728,12 +5728,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Nickel, Silver</t>
+          <t>Zinc, Gold, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Cu 4.65%, Zn 12%, Au 1.25 g/t, Ag 29.77 g/t</t>
+          <t>Cu 1.72%, Au 1.61 g/t, Zn 2.77%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5779,14 +5779,14 @@
         <v>55</v>
       </c>
       <c r="V68" t="n">
-        <v>58.25921</v>
+        <v>58.32867</v>
       </c>
       <c r="W68" t="n">
-        <v>-69.91007999999999</v>
+        <v>-69.86747</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=679</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=677</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Petit-Pas</t>
+          <t>Prud'Homme No 1 : Zone Sud</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Zinc, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Au 52.87 g/t, Ag 5.10 g/t</t>
+          <t>Cu 4.65%, Zn 12%, Au 1.25 g/t, Ag 29.77 g/t</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5857,14 +5857,14 @@
         <v>55</v>
       </c>
       <c r="V69" t="n">
-        <v>53.48965</v>
+        <v>58.25921</v>
       </c>
       <c r="W69" t="n">
-        <v>-72.12729</v>
+        <v>-69.91007999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=686</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=679</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Red Toad</t>
+          <t>Petit-Pas</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Au 153.00 g/t</t>
+          <t>Au 52.87 g/t, Ag 5.10 g/t</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5935,14 +5935,14 @@
         <v>55</v>
       </c>
       <c r="V70" t="n">
-        <v>54.08287</v>
+        <v>53.48965</v>
       </c>
       <c r="W70" t="n">
-        <v>-72.50529</v>
+        <v>-72.12729</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=712</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=686</t>
         </is>
       </c>
     </row>
@@ -5952,11 +5952,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sortilèges Dorés Ouest</t>
+          <t>Red Toad</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Au 3.65 g/t, Cu 0.223%, Ag 3.50 g/t, Zn 0.229%</t>
+          <t>Au 153.00 g/t</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>55</v>
       </c>
       <c r="V71" t="n">
-        <v>54.06291</v>
+        <v>54.08287</v>
       </c>
       <c r="W71" t="n">
-        <v>-72.57297</v>
+        <v>-72.50529</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=717</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=712</t>
         </is>
       </c>
     </row>
@@ -6030,11 +6030,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jackson (Minerais Lac)</t>
+          <t>Sortilèges Dorés Ouest</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
+          <t>Au 3.65 g/t, Cu 0.223%, Ag 3.50 g/t, Zn 0.229%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6082,23 +6082,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>55</v>
       </c>
       <c r="V72" t="n">
-        <v>45.52972</v>
+        <v>54.06291</v>
       </c>
       <c r="W72" t="n">
-        <v>-71.65783999999999</v>
+        <v>-72.57297</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=717</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Été Indien</t>
+          <t>Jackson (Minerais Lac)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Au 23.43 g/t, Ag 12.30 g/t</t>
+          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6160,23 +6160,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T73" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U73" t="n">
         <v>55</v>
       </c>
       <c r="V73" t="n">
-        <v>54.07321</v>
+        <v>45.52972</v>
       </c>
       <c r="W73" t="n">
-        <v>-72.52986</v>
+        <v>-71.65783999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=696</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lingo 3 Ouest</t>
+          <t>Été Indien</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 3230.89 g/t, Ag 17.30 g/t, Pb 0.000128%, Zn 0.107%</t>
+          <t>Au 23.43 g/t, Ag 12.30 g/t</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6247,14 +6247,14 @@
         <v>55</v>
       </c>
       <c r="V74" t="n">
-        <v>54.07075</v>
+        <v>54.07321</v>
       </c>
       <c r="W74" t="n">
-        <v>-72.53373000000001</v>
+        <v>-72.52986</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=696</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Grenouille 2</t>
+          <t>Lingo 3 Ouest</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Au 3527.00 g/t, Ag 18.30 g/t</t>
+          <t>Au 3230.89 g/t, Ag 17.30 g/t, Pb 0.000128%, Zn 0.107%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6325,14 +6325,14 @@
         <v>55</v>
       </c>
       <c r="V75" t="n">
-        <v>54.07734</v>
+        <v>54.07075</v>
       </c>
       <c r="W75" t="n">
-        <v>-72.51860000000001</v>
+        <v>-72.53373000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=702</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=698</t>
         </is>
       </c>
     </row>
@@ -6342,11 +6342,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Moman</t>
+          <t>Grenouille 2</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 3527.40 g/t</t>
+          <t>Au 3527.00 g/t, Ag 18.30 g/t</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6403,14 +6403,14 @@
         <v>55</v>
       </c>
       <c r="V76" t="n">
-        <v>54.07892</v>
+        <v>54.07734</v>
       </c>
       <c r="W76" t="n">
-        <v>-72.51427</v>
+        <v>-72.51860000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=702</t>
         </is>
       </c>
     </row>
@@ -6420,11 +6420,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Slowdance</t>
+          <t>Moman</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 4.63 g/t, Cu 0.104%, Ag 4.50 g/t, Zn 0.221%</t>
+          <t>Au 3527.40 g/t</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6481,14 +6481,14 @@
         <v>55</v>
       </c>
       <c r="V77" t="n">
-        <v>54.0731</v>
+        <v>54.07892</v>
       </c>
       <c r="W77" t="n">
-        <v>-72.54952</v>
+        <v>-72.51427</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=705</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=704</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bourdon</t>
+          <t>Slowdance</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 21.80 g/t</t>
+          <t>Au 4.63 g/t, Cu 0.104%, Ag 4.50 g/t, Zn 0.221%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6559,14 +6559,14 @@
         <v>55</v>
       </c>
       <c r="V78" t="n">
-        <v>53.62313</v>
+        <v>54.0731</v>
       </c>
       <c r="W78" t="n">
-        <v>-71.96111999999999</v>
+        <v>-72.54952</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=705</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Bourdon</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 251.66 g/t</t>
+          <t>Au 21.80 g/t</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6637,14 +6637,14 @@
         <v>55</v>
       </c>
       <c r="V79" t="n">
-        <v>53.53343</v>
+        <v>53.62313</v>
       </c>
       <c r="W79" t="n">
-        <v>-76.53331</v>
+        <v>-71.96111999999999</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Brèche</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 8.56 g/t</t>
+          <t>Au 251.66 g/t</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6715,14 +6715,14 @@
         <v>55</v>
       </c>
       <c r="V80" t="n">
-        <v>53.53187</v>
+        <v>53.53343</v>
       </c>
       <c r="W80" t="n">
-        <v>-76.54353</v>
+        <v>-76.53331</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pari</t>
+          <t>Brèche</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 730.77 g/t</t>
+          <t>Au 8.56 g/t</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6793,14 +6793,14 @@
         <v>55</v>
       </c>
       <c r="V81" t="n">
-        <v>53.53306</v>
+        <v>53.53187</v>
       </c>
       <c r="W81" t="n">
-        <v>-76.55201</v>
+        <v>-76.54353</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zone 32</t>
+          <t>Pari</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -6820,12 +6820,12 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
+          <t>Au 730.77 g/t</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6871,14 +6871,14 @@
         <v>55</v>
       </c>
       <c r="V82" t="n">
-        <v>53.52649</v>
+        <v>53.53306</v>
       </c>
       <c r="W82" t="n">
-        <v>-76.56404999999999</v>
+        <v>-76.55201</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>As-3</t>
+          <t>Zone 32</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6898,12 +6898,12 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 6.38 g/t</t>
+          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6949,14 +6949,14 @@
         <v>55</v>
       </c>
       <c r="V83" t="n">
-        <v>53.52425</v>
+        <v>53.52649</v>
       </c>
       <c r="W83" t="n">
-        <v>-76.57341</v>
+        <v>-76.56404999999999</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As-3</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Au 36.38 g/t</t>
+          <t>Au 6.38 g/t</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7027,14 +7027,14 @@
         <v>55</v>
       </c>
       <c r="V84" t="n">
-        <v>53.52499</v>
+        <v>53.52425</v>
       </c>
       <c r="W84" t="n">
-        <v>-76.58275</v>
+        <v>-76.57341</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Zone 35-L11W</t>
+          <t>As</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Au 35.31 g/t</t>
+          <t>Au 36.38 g/t</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>55</v>
       </c>
       <c r="V85" t="n">
-        <v>53.52296</v>
+        <v>53.52499</v>
       </c>
       <c r="W85" t="n">
-        <v>-76.59889</v>
+        <v>-76.58275</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>Zone 35-L11W</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Au 32.73 g/t</t>
+          <t>Au 35.31 g/t</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7183,14 +7183,14 @@
         <v>55</v>
       </c>
       <c r="V86" t="n">
-        <v>53.51886</v>
+        <v>53.52296</v>
       </c>
       <c r="W86" t="n">
-        <v>-76.60854</v>
+        <v>-76.59889</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
         </is>
       </c>
     </row>
@@ -7200,22 +7200,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Zone 32 (Tonalite-Zone Veine)</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
+          <t>Au 32.73 g/t</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7261,14 +7261,14 @@
         <v>55</v>
       </c>
       <c r="V87" t="n">
-        <v>53.5291</v>
+        <v>53.51886</v>
       </c>
       <c r="W87" t="n">
-        <v>-76.56155</v>
+        <v>-76.60854</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
         </is>
       </c>
     </row>
@@ -7278,22 +7278,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Zone 32 (Mico-Milan)</t>
+          <t>Zone 32 (Tonalite-Zone Veine)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Au 72.69 g/t</t>
+          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7339,14 +7339,14 @@
         <v>55</v>
       </c>
       <c r="V88" t="n">
-        <v>53.52891</v>
+        <v>53.5291</v>
       </c>
       <c r="W88" t="n">
-        <v>-76.56541</v>
+        <v>-76.56155</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRH-96-07</t>
+          <t>Zone 32 (Mico-Milan)</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Au 19.59 g/t</t>
+          <t>Au 72.69 g/t</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7417,14 +7417,14 @@
         <v>55</v>
       </c>
       <c r="V89" t="n">
-        <v>53.52311</v>
+        <v>53.52891</v>
       </c>
       <c r="W89" t="n">
-        <v>-76.61015</v>
+        <v>-76.56541</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
         </is>
       </c>
     </row>
@@ -7434,22 +7434,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pari (Zone 30)</t>
+          <t>TRH-96-07</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 13.50 g/t, Cu 0.57%</t>
+          <t>Au 19.59 g/t</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7495,14 +7495,14 @@
         <v>55</v>
       </c>
       <c r="V90" t="n">
-        <v>53.5301</v>
+        <v>53.52311</v>
       </c>
       <c r="W90" t="n">
-        <v>-76.55025999999999</v>
+        <v>-76.61015</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
         </is>
       </c>
     </row>
@@ -7512,22 +7512,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Filion</t>
+          <t>Pari (Zone 30)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
+          <t>Au 13.50 g/t, Cu 0.57%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7573,14 +7573,14 @@
         <v>55</v>
       </c>
       <c r="V91" t="n">
-        <v>46.61092</v>
+        <v>53.5301</v>
       </c>
       <c r="W91" t="n">
-        <v>-75.97769</v>
+        <v>-76.55025999999999</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>St-Benoit</t>
+          <t>Filion</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -7600,12 +7600,12 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead, Zinc, Silver</t>
+          <t>Nickel, Copper, Cobalt</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
+          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7651,14 +7651,14 @@
         <v>55</v>
       </c>
       <c r="V92" t="n">
-        <v>47.99637</v>
+        <v>46.61092</v>
       </c>
       <c r="W92" t="n">
-        <v>-67.11127</v>
+        <v>-75.97769</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mid-Patapédia</t>
+          <t>St-Benoit</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -7678,12 +7678,12 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold, Copper</t>
+          <t>Gold, Copper, Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
+          <t>Au 7.54 g/t, Cu 1.26%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7729,14 +7729,14 @@
         <v>55</v>
       </c>
       <c r="V93" t="n">
-        <v>47.86378</v>
+        <v>47.99637</v>
       </c>
       <c r="W93" t="n">
-        <v>-67.38485</v>
+        <v>-67.11127</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
+          <t>Mid-Patapédia</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -7756,12 +7756,12 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead</t>
+          <t>Lead, Silver, Zinc, Gold, Copper</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
+          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7807,14 +7807,14 @@
         <v>55</v>
       </c>
       <c r="V94" t="n">
-        <v>50.31401</v>
+        <v>47.86378</v>
       </c>
       <c r="W94" t="n">
-        <v>-62.73908</v>
+        <v>-67.38485</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Projet 70-Landome</t>
+          <t>BJB - Rustcliff (Boudrias)</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -7834,12 +7834,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Silver, Gold, Copper, Lead</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
+          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7885,14 +7885,14 @@
         <v>55</v>
       </c>
       <c r="V95" t="n">
-        <v>48.46123</v>
+        <v>50.31401</v>
       </c>
       <c r="W95" t="n">
-        <v>-77.95265999999999</v>
+        <v>-62.73908</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>de l'Ours</t>
+          <t>Projet 70-Landome</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -7912,12 +7912,12 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 27.00 g/t</t>
+          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7963,14 +7963,14 @@
         <v>55</v>
       </c>
       <c r="V96" t="n">
-        <v>53.61441</v>
+        <v>48.46123</v>
       </c>
       <c r="W96" t="n">
-        <v>-71.97407</v>
+        <v>-77.95265999999999</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
         </is>
       </c>
     </row>
@@ -7980,11 +7980,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dead Mouse extension</t>
+          <t>de l'Ours</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Au 18.36 g/t</t>
+          <t>Au 27.00 g/t</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>55</v>
       </c>
       <c r="V97" t="n">
-        <v>53.61747</v>
+        <v>53.61441</v>
       </c>
       <c r="W97" t="n">
-        <v>-71.97382</v>
+        <v>-71.97407</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
         </is>
       </c>
     </row>
@@ -8058,11 +8058,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ELR-16-002</t>
+          <t>Dead Mouse extension</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Au 9.13 g/t</t>
+          <t>Au 18.36 g/t</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8119,12 +8119,90 @@
         <v>55</v>
       </c>
       <c r="V98" t="n">
+        <v>53.61747</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-71.97382</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ELR-16-002</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Au 9.13 g/t</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>13</v>
+      </c>
+      <c r="T99" t="n">
+        <v>325</v>
+      </c>
+      <c r="U99" t="n">
+        <v>55</v>
+      </c>
+      <c r="V99" t="n">
         <v>52.67859</v>
       </c>
-      <c r="W98" t="n">
+      <c r="W99" t="n">
         <v>-76.30803</v>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
         </is>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X99"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Géant Dormant</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Copper, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.2 Mt</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Au 32.94 g/t, Ag 11.80 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="V2" t="n">
-        <v>49.13127</v>
+        <v>45.3192</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.97206</v>
+        <v>-71.92023</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4515</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Zullo</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Nickel, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Cu 3.35%, Ni 2.7%, Au 1.35 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>45.3192</v>
+        <v>47.43373</v>
       </c>
       <c r="W3" t="n">
-        <v>-71.92023</v>
+        <v>-79.24794</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4696</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Patry-Duchesne (Laverlochère)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tungsten, Gold</t>
+          <t>Molybdenum, Silver, Gold, Bismuth, Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>52.64108</v>
+        <v>47.43121</v>
       </c>
       <c r="W4" t="n">
-        <v>-75.67010999999999</v>
+        <v>-79.32868999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Guimond</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>49.95224</v>
+        <v>47.37388</v>
       </c>
       <c r="W5" t="n">
-        <v>-74.8797</v>
+        <v>-79.13840999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
         </is>
       </c>
     </row>
@@ -882,11 +882,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Orfée Est</t>
+          <t>Rambo</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 10.53 g/t</t>
+          <t>Au 7.60 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>53.46148</v>
+        <v>49.93645</v>
       </c>
       <c r="W6" t="n">
-        <v>-75.20878999999999</v>
+        <v>-79.32689999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=402</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3919</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sylvie</t>
+          <t>Zone Lynx</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,17 +970,17 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
+          <t>Au 7.78 g/t</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>61.39737</v>
+        <v>49.93762</v>
       </c>
       <c r="W7" t="n">
-        <v>-74.97753</v>
+        <v>-79.3579</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3915</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timtu</t>
+          <t>Brisebois</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,17 +1048,17 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
+          <t>Au 27.97 g/t, Ag 5.90 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>61.43006</v>
+        <v>47.35141</v>
       </c>
       <c r="W8" t="n">
-        <v>-74.84983</v>
+        <v>-79.04821</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4705</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Getty</t>
+          <t>Midrim</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,17 +1126,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
+          <t>Copper, Nickel, Egp, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
+          <t>Cu 3.54%, Ni 2.94%, EGP 0.000422%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>61.39535</v>
+        <v>47.47178</v>
       </c>
       <c r="W9" t="n">
-        <v>-75.00066</v>
+        <v>-79.23383</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4692</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mystery</t>
+          <t>Fabre Nord</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,17 +1204,17 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
+          <t>Au 6.48 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>61.39368</v>
+        <v>47.26406</v>
       </c>
       <c r="W10" t="n">
-        <v>-75.1713</v>
+        <v>-79.40157000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gamache A</t>
+          <t>Pike</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
+          <t>Copper, Nickel, Gold, Silver, Mg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
+          <t>Cu 12.3%, Au 2.54 g/t, Ni 0.28%, Ag 9.60 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>61.55073</v>
+        <v>47.32819</v>
       </c>
       <c r="W11" t="n">
-        <v>-72.66555</v>
+        <v>-79.07715</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4703</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandpit</t>
+          <t>Train No 4 (Lac Crabe)</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Uranium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 18.05 g/t, As 0.158%</t>
+          <t>Cu 3.71%, U 0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>52.17253</v>
+        <v>56.39584</v>
       </c>
       <c r="W12" t="n">
-        <v>-76.55762</v>
+        <v>-68.39176999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lemoyne-Extension</t>
+          <t>Lac Janjandashi</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 6.22 g/t</t>
+          <t>Cu 13.9%, Ag 133.70 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.45927</v>
+        <v>53.56991</v>
       </c>
       <c r="W13" t="n">
-        <v>-75.18433</v>
+        <v>-77.31073000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=398</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Orfée</t>
+          <t>Meilleur (Chess Uranium)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 67.35 g/t</t>
+          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>53.46154</v>
+        <v>45.6921</v>
       </c>
       <c r="W14" t="n">
-        <v>-75.21647</v>
+        <v>-76.64127999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=399</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RA13-03</t>
+          <t>SGR-09</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Uranium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.71 g/t</t>
+          <t>Au 3.31 g/t, U 0.11%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>53.1949</v>
+        <v>56.43951</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.66768999999999</v>
+        <v>-68.10245999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20539</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lac Harris</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 12.91 g/t</t>
+          <t>Cu 5.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>53.51022</v>
+        <v>47.68996</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.46174000000001</v>
+        <v>-76.66074999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Lac Foubert</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 144.55 g/t</t>
+          <t>Cu 6.1%, Au 5.52 g/t, Mo 0.448%, Ag 38.10 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>53.52019</v>
+        <v>49.80466</v>
       </c>
       <c r="W17" t="n">
-        <v>-75.40980999999999</v>
+        <v>-79.28044</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3927</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>53.43724</v>
+        <v>49.84595</v>
       </c>
       <c r="W18" t="n">
-        <v>-75.04334</v>
+        <v>-70.57626</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Galexis</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>53.48752</v>
+        <v>49.83681</v>
       </c>
       <c r="W19" t="n">
-        <v>-75.33392000000001</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mustang</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>52.17024</v>
+        <v>53.43724</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.57532999999999</v>
+        <v>-75.04334</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lac Nitakwin</t>
+          <t>Lac Shallow-Est</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 6.06 g/t</t>
+          <t>Cu 4.4%, Ni 1.02%, Ag 7.89 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>52.1766</v>
+        <v>49.72004</v>
       </c>
       <c r="W21" t="n">
-        <v>-76.71138999999999</v>
+        <v>-77.44344</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1470</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nasigon (Lac Lajoue)</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 9.21%, Ag 100.00 g/t, Au 0.88 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>47.53875</v>
+        <v>49.82919</v>
       </c>
       <c r="W22" t="n">
-        <v>-75.10978</v>
+        <v>-70.58076</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20138</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Tungsten, Tellurium, Arsenic, Copper, Silver, Cobalt</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>52.03235</v>
+        <v>59.80634</v>
       </c>
       <c r="W23" t="n">
-        <v>-69.13816</v>
+        <v>-75.01831</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RA13-02</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 4.67 g/t, Ag 9.80 g/t</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>53.17502</v>
+        <v>49.59836</v>
       </c>
       <c r="W24" t="n">
-        <v>-77.75697</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20536</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Orage</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Iron</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Ag 16.90 g/t</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>53.68741</v>
+        <v>49.63941</v>
       </c>
       <c r="W25" t="n">
-        <v>-76.22185</v>
+        <v>-76.90893</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=468</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Baleine Rouge Au-Zn-Pb</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2452,12 +2452,12 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Gold</t>
+          <t>Uranium, Gold, Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>55.23561</v>
+        <v>56.43038</v>
       </c>
       <c r="W26" t="n">
-        <v>-67.9516</v>
+        <v>-68.09914000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sond. LGS09-217</t>
+          <t>Zone Meridian SW</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 2.76%, Au 2.19 g/t, Ag 14.70 g/t</t>
+          <t>Au 18.20 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>53.528</v>
+        <v>53.02374</v>
       </c>
       <c r="W27" t="n">
-        <v>-76.54774999999999</v>
+        <v>-69.6341</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20066</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66997</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lac Nasigon</t>
+          <t>Kogaluc 1</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Silver, Copper</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 4.4%, Ag 96.30 g/t</t>
+          <t>Au 9.26 g/t, Cu 0.4%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>47.53085</v>
+        <v>58.81627</v>
       </c>
       <c r="W28" t="n">
-        <v>-75.11848000000001</v>
+        <v>-74.70458000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=20134</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Comtois NW</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 71.70 g/t, Ag 10.60 g/t</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.18766</v>
+        <v>46.26109</v>
       </c>
       <c r="W29" t="n">
-        <v>-77.31872</v>
+        <v>-71.22866</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14615</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jedi</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
+          <t>Copper, Silver, Zinc, Gold, Lead</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 11.50 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>54.84385</v>
+        <v>48.37403</v>
       </c>
       <c r="W30" t="n">
-        <v>-69.86212</v>
+        <v>-65.44089</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=14912</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2842,12 +2842,12 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>54.8722</v>
+        <v>46.26265</v>
       </c>
       <c r="W31" t="n">
-        <v>-69.81637000000001</v>
+        <v>-71.21769</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tricorne</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Au 8750.00 g/t, Cu 0.317%, Ag 7.70 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>54.85039</v>
+        <v>46.26532</v>
       </c>
       <c r="W32" t="n">
-        <v>-69.85742</v>
+        <v>-71.28788</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jedi Extension</t>
+          <t>Lac du Crapet</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 5.89 g/t, Ag 6.50 g/t</t>
+          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>54.85448</v>
+        <v>52.20175</v>
       </c>
       <c r="W33" t="n">
-        <v>-69.83853000000001</v>
+        <v>-70.89798</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11102</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Golden Idol</t>
+          <t>Ouf</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Zinc</t>
+          <t>Copper, Zinc, Lead, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 9.09 g/t, Zn 0.087%</t>
+          <t>Cu 11.8%, Ag 204.00 g/t, Zn 8.7%, Pb 1.6%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.57002</v>
+        <v>53.90478</v>
       </c>
       <c r="W34" t="n">
-        <v>-72.41676</v>
+        <v>-74.69878</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=13390</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3841</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bonspot</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Silver, Gold, Arsenic</t>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Au 33.04 g/t, Ag 79.30 g/t, As 22.1%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>53.41679</v>
+        <v>45.43447</v>
       </c>
       <c r="W35" t="n">
-        <v>-77.27167</v>
+        <v>-70.9088</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6015</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gordie/Benoit/Will/Pierre/Giaro</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tungsten, Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Copper, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Au 119.53 g/t, W 0.147%, Ag 124.60 g/t, Cu 0.599%, Pb 0.301%</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>53.39256</v>
+        <v>45.43568</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.43714</v>
+        <v>-70.91788</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6018</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Lead, Copper</t>
+          <t>Lead, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 87.43 g/t, W 0.324%, Ag 354.00 g/t, Cu 1.81%, Pb 2.51%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>53.39458</v>
+        <v>45.40513</v>
       </c>
       <c r="W37" t="n">
-        <v>-77.44683999999999</v>
+        <v>-70.9376</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6019</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TR-00-126</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 20.70 g/t</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>53.53822</v>
+        <v>45.44349</v>
       </c>
       <c r="W38" t="n">
-        <v>-76.48351</v>
+        <v>-70.91244</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=491</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -3456,22 +3456,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TR-00-129, 130 et 131</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 35.04 g/t</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>53.53948</v>
+        <v>45.45582</v>
       </c>
       <c r="W39" t="n">
-        <v>-76.47684</v>
+        <v>-70.90786</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=492</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zone no 7</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Zinc, Copper, Tungsten</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 7.54 g/t, Ag 258.86 g/t, Zn 8.05%, Pb 11.4%, Cu 0.7%</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>53.1821</v>
+        <v>60.2779</v>
       </c>
       <c r="W40" t="n">
-        <v>-77.71374</v>
+        <v>-75.33311</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=496</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Beryllium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>52.03237</v>
+        <v>45.03676</v>
       </c>
       <c r="W41" t="n">
-        <v>-75.13809999999999</v>
+        <v>-72.77243</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -3690,22 +3690,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>49.24734</v>
+        <v>46.265</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.98866</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Nickel, Silver, Zinc, Copper, Cobalt, Lead, Egp</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>53.39996</v>
+        <v>46.27176</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.33163999999999</v>
+        <v>-71.28612</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3856,12 +3856,12 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Palladium, Egp, Gold, Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>53.34013</v>
+        <v>52.03235</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.32316</v>
+        <v>-69.13816</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Lartic Est</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rh, Platinum, Palladium, Gold, Nickel, Egp, Chromium, Copper</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>53.39786</v>
+        <v>48.173</v>
       </c>
       <c r="W45" t="n">
-        <v>-77.30625000000001</v>
+        <v>-78.14212999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Delhi Pacific</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Cu 7.36%, Ag 24.90 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4063,14 +4063,14 @@
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>53.35887</v>
+        <v>56.40258</v>
       </c>
       <c r="W46" t="n">
-        <v>-77.31016</v>
+        <v>-67.9023</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4930N-1</t>
+          <t>Lac Dunphy</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4090,12 +4090,12 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chromium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chromium, Nickel, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Cu 4.06%, Ni 0.35%, Ag 15.50 g/t, Cr 15.2%</t>
+          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4141,14 +4141,14 @@
         <v>55</v>
       </c>
       <c r="V47" t="n">
-        <v>53.38014</v>
+        <v>56.05097</v>
       </c>
       <c r="W47" t="n">
-        <v>-77.28712</v>
+        <v>-67.71257</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6000</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Au-1</t>
+          <t>Baleine Rouge Au-Zn-Pb</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4168,12 +4168,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Lead, Gold, Zinc</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Au 20.60 g/t, Ag 3.20 g/t, As 9.7%</t>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4219,14 +4219,14 @@
         <v>55</v>
       </c>
       <c r="V48" t="n">
-        <v>53.40387</v>
+        <v>55.23561</v>
       </c>
       <c r="W48" t="n">
-        <v>-77.30118</v>
+        <v>-67.9516</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6001</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Au-26</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4246,12 +4246,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Copper, Arsenic, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Cu 6.74%, Au 3.19 g/t, Ag 69.26 g/t, Pb 1.79%</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>55</v>
       </c>
       <c r="V49" t="n">
-        <v>53.39936</v>
+        <v>55.15269</v>
       </c>
       <c r="W49" t="n">
-        <v>-77.29407</v>
+        <v>-66.35399</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6002</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PG-221094</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4324,12 +4324,12 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold, Copper, Arsenic</t>
+          <t>Gold, Beryllium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Au 58.08 g/t, Ag 1283.00 g/t, Pb 5.7%, Zn 1.48%, Cu 0.252%</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4375,14 +4375,14 @@
         <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>53.40779</v>
+        <v>52.03237</v>
       </c>
       <c r="W50" t="n">
-        <v>-77.28636</v>
+        <v>-75.13809999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=6003</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Coconut Club</t>
+          <t>Goshawk</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -4402,12 +4402,12 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Etr, Thorium, Uranium, Zr, Gold, Silver</t>
+          <t>Gold, Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Au 7.94 g/t, U 0.0864%, Ag 33.10 g/t, ETR 1.05%, Th 0.621%</t>
+          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4453,14 +4453,14 @@
         <v>55</v>
       </c>
       <c r="V51" t="n">
-        <v>46.99057</v>
+        <v>61.56992</v>
       </c>
       <c r="W51" t="n">
-        <v>-78.59457999999999</v>
+        <v>-75.20258</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=535</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Rochelom</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -4480,12 +4480,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4522,23 +4522,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U52" t="n">
         <v>55</v>
       </c>
       <c r="V52" t="n">
-        <v>48.32328</v>
+        <v>49.77064</v>
       </c>
       <c r="W52" t="n">
-        <v>-79.44637</v>
+        <v>-76.01858</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zone Cyr</t>
+          <t>Lac Rivon-Ouest</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -4558,12 +4558,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper, Lead, Zinc</t>
+          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Cu 5.81%, Au 2.12 g/t, Ag 70.00 g/t, Zn 0.46%, Pb 0.19%</t>
+          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4609,14 +4609,14 @@
         <v>55</v>
       </c>
       <c r="V53" t="n">
-        <v>52.2425</v>
+        <v>51.72313</v>
       </c>
       <c r="W53" t="n">
-        <v>-76.59574000000001</v>
+        <v>-72.79697</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=566</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Challenger</t>
+          <t>Gold Fields</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 278.00 g/t</t>
+          <t>Au 19.04 g/t</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4687,14 +4687,14 @@
         <v>55</v>
       </c>
       <c r="V54" t="n">
-        <v>52.1821</v>
+        <v>49.09287</v>
       </c>
       <c r="W54" t="n">
-        <v>-76.70099999999999</v>
+        <v>-78.42254</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35087</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>D-91-01 (Option Dejour)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Au 7.60 g/t</t>
+          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4756,23 +4756,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U55" t="n">
         <v>55</v>
       </c>
       <c r="V55" t="n">
-        <v>50.64946</v>
+        <v>49.02527</v>
       </c>
       <c r="W55" t="n">
-        <v>-75.04613999999999</v>
+        <v>-78.38705</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=35209</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wab-88-0406</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4792,12 +4792,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Bismuth, Tellurium</t>
+          <t>Gold, Copper, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Au 5.74 g/t, Cu 2.4%, Mo 0.0901%, Ag 13.50 g/t, Te 0.004%</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4843,3368 +4843,14 @@
         <v>55</v>
       </c>
       <c r="V56" t="n">
-        <v>52.23706</v>
+        <v>52.21818</v>
       </c>
       <c r="W56" t="n">
-        <v>-76.60512</v>
+        <v>-77.45902</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=562</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Miltin</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Au 36.48 g/t, Cu 10.5%, Ag 52.00 g/t</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>325</v>
-      </c>
-      <c r="U57" t="n">
-        <v>55</v>
-      </c>
-      <c r="V57" t="n">
-        <v>52.2473</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-76.50475</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=565</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Isabelle</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Au 316.18 g/t, Ag 7.50 g/t</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>325</v>
-      </c>
-      <c r="U58" t="n">
-        <v>55</v>
-      </c>
-      <c r="V58" t="n">
-        <v>52.09336</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-76.75954</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=578</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Lac Delta NW-Cuivre</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Au 13.33 g/t, Cu 7.3%, Ag 20.30 g/t</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>13</v>
-      </c>
-      <c r="T59" t="n">
-        <v>325</v>
-      </c>
-      <c r="U59" t="n">
-        <v>55</v>
-      </c>
-      <c r="V59" t="n">
-        <v>52.23158</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-76.4002</v>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=593</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Viau (ou Bordulac)</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Au 31.00 g/t</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>13</v>
-      </c>
-      <c r="T60" t="n">
-        <v>325</v>
-      </c>
-      <c r="U60" t="n">
-        <v>55</v>
-      </c>
-      <c r="V60" t="n">
-        <v>48.26547</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-79.41453</v>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5797</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lac Delta Nord (Grid C.22)</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Au 4.71 g/t, Cu 1.81%, Ag 14.00 g/t, Zn 0.54%</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="n">
-        <v>13</v>
-      </c>
-      <c r="T61" t="n">
-        <v>325</v>
-      </c>
-      <c r="U61" t="n">
-        <v>55</v>
-      </c>
-      <c r="V61" t="n">
-        <v>52.24319</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-76.36844000000001</v>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=598</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Zone Chino</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Au 24.69 g/t, Ag 2.80 g/t</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
-        <v>13</v>
-      </c>
-      <c r="T62" t="n">
-        <v>325</v>
-      </c>
-      <c r="U62" t="n">
-        <v>55</v>
-      </c>
-      <c r="V62" t="n">
-        <v>52.17342</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-76.44268</v>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=600</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Zone QET</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Au 14.50 g/t, Cu 0.96%, Ag 11.20 g/t</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
-        <v>13</v>
-      </c>
-      <c r="T63" t="n">
-        <v>325</v>
-      </c>
-      <c r="U63" t="n">
-        <v>55</v>
-      </c>
-      <c r="V63" t="n">
-        <v>52.24811</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-76.49615</v>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=606</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Lac Tarsac : Veine I et III</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Au 11.66 g/t</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>6</v>
-      </c>
-      <c r="T64" t="n">
-        <v>150</v>
-      </c>
-      <c r="U64" t="n">
-        <v>55</v>
-      </c>
-      <c r="V64" t="n">
-        <v>48.3561</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-79.43788000000001</v>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5777</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Huckleberry</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Platinum, Palladium, Egp, Nickel, Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Cu 10.6%, Pd 10.70 g/t, Pt 5.11 g/t, Ni 0.424%, Au 0.40 g/t</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>13</v>
-      </c>
-      <c r="T65" t="n">
-        <v>325</v>
-      </c>
-      <c r="U65" t="n">
-        <v>55</v>
-      </c>
-      <c r="V65" t="n">
-        <v>55.78035</v>
-      </c>
-      <c r="W65" t="n">
-        <v>-66.95337000000001</v>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39556</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Nisto</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Lead, Uranium</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Cu 5.6%, Zn 5.4%, U 0.03%</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>13</v>
-      </c>
-      <c r="T66" t="n">
-        <v>325</v>
-      </c>
-      <c r="U66" t="n">
-        <v>55</v>
-      </c>
-      <c r="V66" t="n">
-        <v>50.3605</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-63.13619</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=665</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Destorbelle</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Au 8.20 g/t</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>11</v>
-      </c>
-      <c r="T67" t="n">
-        <v>275</v>
-      </c>
-      <c r="U67" t="n">
-        <v>55</v>
-      </c>
-      <c r="V67" t="n">
-        <v>48.4465</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-78.85312999999999</v>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5661</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Soucy No 1 - Zones A et D</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Zinc, Gold, Copper, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Cu 1.72%, Au 1.61 g/t, Zn 2.77%</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="n">
-        <v>13</v>
-      </c>
-      <c r="T68" t="n">
-        <v>325</v>
-      </c>
-      <c r="U68" t="n">
-        <v>55</v>
-      </c>
-      <c r="V68" t="n">
-        <v>58.32867</v>
-      </c>
-      <c r="W68" t="n">
-        <v>-69.86747</v>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=677</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Prud'Homme No 1 : Zone Sud</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Gold, Zinc, Copper, Nickel, Silver</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Cu 4.65%, Zn 12%, Au 1.25 g/t, Ag 29.77 g/t</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="n">
-        <v>13</v>
-      </c>
-      <c r="T69" t="n">
-        <v>325</v>
-      </c>
-      <c r="U69" t="n">
-        <v>55</v>
-      </c>
-      <c r="V69" t="n">
-        <v>58.25921</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-69.91007999999999</v>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=679</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Petit-Pas</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Au 52.87 g/t, Ag 5.10 g/t</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>13</v>
-      </c>
-      <c r="T70" t="n">
-        <v>325</v>
-      </c>
-      <c r="U70" t="n">
-        <v>55</v>
-      </c>
-      <c r="V70" t="n">
-        <v>53.48965</v>
-      </c>
-      <c r="W70" t="n">
-        <v>-72.12729</v>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=686</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Red Toad</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Au 153.00 g/t</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>13</v>
-      </c>
-      <c r="T71" t="n">
-        <v>325</v>
-      </c>
-      <c r="U71" t="n">
-        <v>55</v>
-      </c>
-      <c r="V71" t="n">
-        <v>54.08287</v>
-      </c>
-      <c r="W71" t="n">
-        <v>-72.50529</v>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=712</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Sortilèges Dorés Ouest</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Au 3.65 g/t, Cu 0.223%, Ag 3.50 g/t, Zn 0.229%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="n">
-        <v>13</v>
-      </c>
-      <c r="T72" t="n">
-        <v>325</v>
-      </c>
-      <c r="U72" t="n">
-        <v>55</v>
-      </c>
-      <c r="V72" t="n">
-        <v>54.06291</v>
-      </c>
-      <c r="W72" t="n">
-        <v>-72.57297</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=717</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Jackson (Minerais Lac)</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Au 7.30 g/t, Ag 11.00 g/t</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>12</v>
-      </c>
-      <c r="T73" t="n">
-        <v>300</v>
-      </c>
-      <c r="U73" t="n">
-        <v>55</v>
-      </c>
-      <c r="V73" t="n">
-        <v>45.52972</v>
-      </c>
-      <c r="W73" t="n">
-        <v>-71.65783999999999</v>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5585</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Été Indien</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Au 23.43 g/t, Ag 12.30 g/t</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>13</v>
-      </c>
-      <c r="T74" t="n">
-        <v>325</v>
-      </c>
-      <c r="U74" t="n">
-        <v>55</v>
-      </c>
-      <c r="V74" t="n">
-        <v>54.07321</v>
-      </c>
-      <c r="W74" t="n">
-        <v>-72.52986</v>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=696</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Lingo 3 Ouest</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Au 3230.89 g/t, Ag 17.30 g/t, Pb 0.000128%, Zn 0.107%</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>13</v>
-      </c>
-      <c r="T75" t="n">
-        <v>325</v>
-      </c>
-      <c r="U75" t="n">
-        <v>55</v>
-      </c>
-      <c r="V75" t="n">
-        <v>54.07075</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-72.53373000000001</v>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=698</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Grenouille 2</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Au 3527.00 g/t, Ag 18.30 g/t</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>13</v>
-      </c>
-      <c r="T76" t="n">
-        <v>325</v>
-      </c>
-      <c r="U76" t="n">
-        <v>55</v>
-      </c>
-      <c r="V76" t="n">
-        <v>54.07734</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-72.51860000000001</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=702</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Moman</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>3</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Au 3527.40 g/t</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>13</v>
-      </c>
-      <c r="T77" t="n">
-        <v>325</v>
-      </c>
-      <c r="U77" t="n">
-        <v>55</v>
-      </c>
-      <c r="V77" t="n">
-        <v>54.07892</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-72.51427</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=704</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Slowdance</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Gold, Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Au 4.63 g/t, Cu 0.104%, Ag 4.50 g/t, Zn 0.221%</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>13</v>
-      </c>
-      <c r="T78" t="n">
-        <v>325</v>
-      </c>
-      <c r="U78" t="n">
-        <v>55</v>
-      </c>
-      <c r="V78" t="n">
-        <v>54.0731</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-72.54952</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=705</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Bourdon</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Au 21.80 g/t</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>325</v>
-      </c>
-      <c r="U79" t="n">
-        <v>55</v>
-      </c>
-      <c r="V79" t="n">
-        <v>53.62313</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-71.96111999999999</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5491</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Ugo</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Au 251.66 g/t</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="n">
-        <v>13</v>
-      </c>
-      <c r="T80" t="n">
-        <v>325</v>
-      </c>
-      <c r="U80" t="n">
-        <v>55</v>
-      </c>
-      <c r="V80" t="n">
-        <v>53.53343</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-76.53331</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5503</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Brèche</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Au 8.56 g/t</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>13</v>
-      </c>
-      <c r="T81" t="n">
-        <v>325</v>
-      </c>
-      <c r="U81" t="n">
-        <v>55</v>
-      </c>
-      <c r="V81" t="n">
-        <v>53.53187</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-76.54353</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5504</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Pari</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I82" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Au 730.77 g/t</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="n">
-        <v>13</v>
-      </c>
-      <c r="T82" t="n">
-        <v>325</v>
-      </c>
-      <c r="U82" t="n">
-        <v>55</v>
-      </c>
-      <c r="V82" t="n">
-        <v>53.53306</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-76.55201</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5505</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Zone 32</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I83" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Au 42.64 g/t, Cu 10.2%, Ag 14.40 g/t</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="n">
-        <v>13</v>
-      </c>
-      <c r="T83" t="n">
-        <v>325</v>
-      </c>
-      <c r="U83" t="n">
-        <v>55</v>
-      </c>
-      <c r="V83" t="n">
-        <v>53.52649</v>
-      </c>
-      <c r="W83" t="n">
-        <v>-76.56404999999999</v>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5506</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>As-3</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Au 6.38 g/t</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="n">
-        <v>13</v>
-      </c>
-      <c r="T84" t="n">
-        <v>325</v>
-      </c>
-      <c r="U84" t="n">
-        <v>55</v>
-      </c>
-      <c r="V84" t="n">
-        <v>53.52425</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-76.57341</v>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5507</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="b">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Au 36.38 g/t</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="n">
-        <v>13</v>
-      </c>
-      <c r="T85" t="n">
-        <v>325</v>
-      </c>
-      <c r="U85" t="n">
-        <v>55</v>
-      </c>
-      <c r="V85" t="n">
-        <v>53.52499</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-76.58275</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5508</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Zone 35-L11W</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I86" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" t="b">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Au 35.31 g/t</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="n">
-        <v>13</v>
-      </c>
-      <c r="T86" t="n">
-        <v>325</v>
-      </c>
-      <c r="U86" t="n">
-        <v>55</v>
-      </c>
-      <c r="V86" t="n">
-        <v>53.52296</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-76.59889</v>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5511</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I87" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" t="b">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Au 32.73 g/t</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="n">
-        <v>13</v>
-      </c>
-      <c r="T87" t="n">
-        <v>325</v>
-      </c>
-      <c r="U87" t="n">
-        <v>55</v>
-      </c>
-      <c r="V87" t="n">
-        <v>53.51886</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-76.60854</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5512</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Zone 32 (Tonalite-Zone Veine)</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I88" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" t="b">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Au 101.50 g/t, Ag 68.20 g/t, Cu 0.6%</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="n">
-        <v>13</v>
-      </c>
-      <c r="T88" t="n">
-        <v>325</v>
-      </c>
-      <c r="U88" t="n">
-        <v>55</v>
-      </c>
-      <c r="V88" t="n">
-        <v>53.5291</v>
-      </c>
-      <c r="W88" t="n">
-        <v>-76.56155</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5521</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Zone 32 (Mico-Milan)</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I89" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" t="b">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Au 72.69 g/t</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="n">
-        <v>13</v>
-      </c>
-      <c r="T89" t="n">
-        <v>325</v>
-      </c>
-      <c r="U89" t="n">
-        <v>55</v>
-      </c>
-      <c r="V89" t="n">
-        <v>53.52891</v>
-      </c>
-      <c r="W89" t="n">
-        <v>-76.56541</v>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5522</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>TRH-96-07</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>3</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I90" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" t="b">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Au 19.59 g/t</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="n">
-        <v>13</v>
-      </c>
-      <c r="T90" t="n">
-        <v>325</v>
-      </c>
-      <c r="U90" t="n">
-        <v>55</v>
-      </c>
-      <c r="V90" t="n">
-        <v>53.52311</v>
-      </c>
-      <c r="W90" t="n">
-        <v>-76.61015</v>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5524</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Pari (Zone 30)</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Copper, Gold</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I91" t="b">
-        <v>1</v>
-      </c>
-      <c r="J91" t="b">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Au 13.50 g/t, Cu 0.57%</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="n">
-        <v>13</v>
-      </c>
-      <c r="T91" t="n">
-        <v>325</v>
-      </c>
-      <c r="U91" t="n">
-        <v>55</v>
-      </c>
-      <c r="V91" t="n">
-        <v>53.5301</v>
-      </c>
-      <c r="W91" t="n">
-        <v>-76.55025999999999</v>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5525</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Filion</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Cobalt</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I92" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" t="b">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Cu 4.22%, Co 0.27%, Ni 0.75%</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="n">
-        <v>13</v>
-      </c>
-      <c r="T92" t="n">
-        <v>325</v>
-      </c>
-      <c r="U92" t="n">
-        <v>55</v>
-      </c>
-      <c r="V92" t="n">
-        <v>46.61092</v>
-      </c>
-      <c r="W92" t="n">
-        <v>-75.97769</v>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5535</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>St-Benoit</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Lead, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I93" t="b">
-        <v>1</v>
-      </c>
-      <c r="J93" t="b">
-        <v>0</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Au 7.54 g/t, Cu 1.26%</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="n">
-        <v>13</v>
-      </c>
-      <c r="T93" t="n">
-        <v>325</v>
-      </c>
-      <c r="U93" t="n">
-        <v>55</v>
-      </c>
-      <c r="V93" t="n">
-        <v>47.99637</v>
-      </c>
-      <c r="W93" t="n">
-        <v>-67.11127</v>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5356</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Mid-Patapédia</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Lead, Silver, Zinc, Gold, Copper</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I94" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" t="b">
-        <v>0</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Au 49.35 g/t, Ag 332.10 g/t, Cu 2.37%, Pb 8.75%, Zn 2.21%</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="n">
-        <v>13</v>
-      </c>
-      <c r="T94" t="n">
-        <v>325</v>
-      </c>
-      <c r="U94" t="n">
-        <v>55</v>
-      </c>
-      <c r="V94" t="n">
-        <v>47.86378</v>
-      </c>
-      <c r="W94" t="n">
-        <v>-67.38485</v>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5357</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>BJB - Rustcliff (Boudrias)</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Silver, Gold, Copper, Lead</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I95" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Cu 2.79%, Au 2.06 g/t, Ag 50.60 g/t, Pb 0.7%</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="n">
-        <v>13</v>
-      </c>
-      <c r="T95" t="n">
-        <v>325</v>
-      </c>
-      <c r="U95" t="n">
-        <v>55</v>
-      </c>
-      <c r="V95" t="n">
-        <v>50.31401</v>
-      </c>
-      <c r="W95" t="n">
-        <v>-62.73908</v>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5406</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Projet 70-Landome</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Copper, Silver, Zinc, Gold</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I96" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Cu 6.93%, Zn 9.19%, Ag 60.20 g/t, Au 0.51 g/t</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="n">
-        <v>13</v>
-      </c>
-      <c r="T96" t="n">
-        <v>325</v>
-      </c>
-      <c r="U96" t="n">
-        <v>55</v>
-      </c>
-      <c r="V96" t="n">
-        <v>48.46123</v>
-      </c>
-      <c r="W96" t="n">
-        <v>-77.95265999999999</v>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5462</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>de l'Ours</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I97" t="b">
-        <v>1</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Au 27.00 g/t</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="n">
-        <v>13</v>
-      </c>
-      <c r="T97" t="n">
-        <v>325</v>
-      </c>
-      <c r="U97" t="n">
-        <v>55</v>
-      </c>
-      <c r="V97" t="n">
-        <v>53.61441</v>
-      </c>
-      <c r="W97" t="n">
-        <v>-71.97407</v>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5489</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Dead Mouse extension</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>2</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I98" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Au 18.36 g/t</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="n">
-        <v>13</v>
-      </c>
-      <c r="T98" t="n">
-        <v>325</v>
-      </c>
-      <c r="U98" t="n">
-        <v>55</v>
-      </c>
-      <c r="V98" t="n">
-        <v>53.61747</v>
-      </c>
-      <c r="W98" t="n">
-        <v>-71.97382</v>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5490</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>ELR-16-002</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I99" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Au 9.13 g/t</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="n">
-        <v>13</v>
-      </c>
-      <c r="T99" t="n">
-        <v>325</v>
-      </c>
-      <c r="U99" t="n">
-        <v>55</v>
-      </c>
-      <c r="V99" t="n">
-        <v>52.67859</v>
-      </c>
-      <c r="W99" t="n">
-        <v>-76.30803</v>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=43078</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zullo</t>
+          <t>Croix-3</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.35%, Ni 2.7%, Au 1.35 g/t</t>
+          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>47.43373</v>
+        <v>49.05483</v>
       </c>
       <c r="W3" t="n">
-        <v>-79.24794</v>
+        <v>-75.39637999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4696</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
         </is>
       </c>
     </row>
@@ -726,22 +726,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Patry-Duchesne (Laverlochère)</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Molybdenum, Silver, Gold, Bismuth, Copper</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 25.3%, Ag 310.23 g/t, Au 1.37 g/t, Mo 0.427%, Bi 0.15%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>47.43121</v>
+        <v>46.265</v>
       </c>
       <c r="W4" t="n">
-        <v>-79.32868999999999</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4695</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Guimond</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 6.55 g/t, Ag 17.48 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>47.37388</v>
+        <v>46.27176</v>
       </c>
       <c r="W5" t="n">
-        <v>-79.13840999999999</v>
+        <v>-71.28612</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4698</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rambo</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 7.60 g/t</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>49.93645</v>
+        <v>46.26109</v>
       </c>
       <c r="W6" t="n">
-        <v>-79.32689999999999</v>
+        <v>-71.22866</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zone Lynx</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 7.78 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>49.93762</v>
+        <v>46.26532</v>
       </c>
       <c r="W7" t="n">
-        <v>-79.3579</v>
+        <v>-71.28788</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3915</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brisebois</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 27.97 g/t, Ag 5.90 g/t</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>47.35141</v>
+        <v>46.26265</v>
       </c>
       <c r="W8" t="n">
-        <v>-79.04821</v>
+        <v>-71.21769</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4705</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Midrim</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 3.54%, Ni 2.94%, EGP 0.000422%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>47.47178</v>
+        <v>45.03676</v>
       </c>
       <c r="W9" t="n">
-        <v>-79.23383</v>
+        <v>-72.77243</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4692</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fabre Nord</t>
+          <t>Lac Fecteau Est</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 6.48 g/t</t>
+          <t>Au 8.80 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>47.26406</v>
+        <v>49.03096</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.40157000000001</v>
+        <v>-75.24721</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4704</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pike</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold, Silver, Mg</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 12.3%, Au 2.54 g/t, Ni 0.28%, Ag 9.60 g/t</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>47.32819</v>
+        <v>48.31932</v>
       </c>
       <c r="W11" t="n">
-        <v>-79.07715</v>
+        <v>-64.9713</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4703</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Train No 4 (Lac Crabe)</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Uranium</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 3.71%, U 0.07%</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>56.39584</v>
+        <v>51.6436</v>
       </c>
       <c r="W12" t="n">
-        <v>-68.39176999999999</v>
+        <v>-67.33749</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4909</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lac Janjandashi</t>
+          <t>Filon Baker (Lac Arseneault)</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Lead, Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 13.9%, Ag 133.70 g/t</t>
+          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>53.56991</v>
+        <v>48.37895</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.31073000000001</v>
+        <v>-65.22886</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4804</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Meilleur (Chess Uranium)</t>
+          <t>Frontier South</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Egp, Palladium, Platinum, Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Iron</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 3.27%, Pd 2.46 g/t, Ni 0.6%, Au 0.50 g/t, Pt 0.73 g/t</t>
+          <t>Cu 10.8%, Ni 5.31%, Pd 5.54 g/t, Pt 1.55 g/t, EGP 0.000709%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>45.6921</v>
+        <v>61.35434</v>
       </c>
       <c r="W14" t="n">
-        <v>-76.64127999999999</v>
+        <v>-76.05906</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4809</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1040</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SGR-09</t>
+          <t>Sond. Umex 132</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Uranium</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 3.31 g/t, U 0.11%</t>
+          <t>Cu 4%, Zn 6%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>56.43951</v>
+        <v>49.79699</v>
       </c>
       <c r="W15" t="n">
-        <v>-68.10245999999999</v>
+        <v>-75.81529</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4914</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lac Harris</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 5.07%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>47.68996</v>
+        <v>45.42257</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.66074999999999</v>
+        <v>-70.92541</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4859</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lac Foubert</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,17 +1750,17 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Lead, Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 6.1%, Au 5.52 g/t, Mo 0.448%, Ag 38.10 g/t</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1792,23 +1792,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>49.80466</v>
+        <v>45.42731</v>
       </c>
       <c r="W17" t="n">
-        <v>-79.28044</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3927</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>49.84595</v>
+        <v>45.40513</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.57626</v>
+        <v>-70.9376</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.83681</v>
+        <v>45.45582</v>
       </c>
       <c r="W19" t="n">
-        <v>-70.57877999999999</v>
+        <v>-70.90786</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,12 +1984,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>53.43724</v>
+        <v>45.44349</v>
       </c>
       <c r="W20" t="n">
-        <v>-75.04334</v>
+        <v>-70.91244</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lac Shallow-Est</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 4.4%, Ni 1.02%, Ag 7.89 g/t</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>49.72004</v>
+        <v>48.33048</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.44344</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1470</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Dussault</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Silver, Copper, Zinc, Manganese</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>49.82919</v>
+        <v>46.00535</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.58076</v>
+        <v>-71.70357</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qalluviartuuq-NW</t>
+          <t>Swarm Hill</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Tungsten, Tellurium, Arsenic, Copper, Silver, Cobalt</t>
+          <t>Copper, Nickel, Gold, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
+          <t>Cu 4.13%, Au 1.05 g/t, Ni 0.32%, Zn 0.42%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>59.80634</v>
+        <v>61.51392</v>
       </c>
       <c r="W23" t="n">
-        <v>-75.01831</v>
+        <v>-76.44999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1032</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lac Beaupré-Est</t>
+          <t>Lac Chassé-Est</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Zinc, Copper, Iron, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
+          <t>Cu 6.82%, Au 0.35 g/t, Zn 0.877%, Ag 12.00 g/t, Fe 48.3%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>49.59836</v>
+        <v>61.62679</v>
       </c>
       <c r="W24" t="n">
-        <v>-76.92194000000001</v>
+        <v>-76.35439</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1031</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Iron</t>
+          <t>Copper, Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>49.63941</v>
+        <v>49.78784</v>
       </c>
       <c r="W25" t="n">
-        <v>-76.90893</v>
+        <v>-77.08529</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -2442,22 +2442,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Uranium, Gold, Copper</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 223.40 g/t, U 0.1%, Cu 0.4%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>56.43038</v>
+        <v>48.37403</v>
       </c>
       <c r="W26" t="n">
-        <v>-68.09914000000001</v>
+        <v>-65.44089</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4919</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zone Meridian SW</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 18.20 g/t</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>53.02374</v>
+        <v>45.43447</v>
       </c>
       <c r="W27" t="n">
-        <v>-69.6341</v>
+        <v>-70.9088</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=66997</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kogaluc 1</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Au 9.26 g/t, Cu 0.4%</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>58.81627</v>
+        <v>45.43568</v>
       </c>
       <c r="W28" t="n">
-        <v>-74.70458000000001</v>
+        <v>-70.91788</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4974</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Cedar Rapids-Zone Village</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Au 302.00 g/t, Cu 5.5%, Ag 21.10 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>46.26109</v>
+        <v>49.01186</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.22866</v>
+        <v>-77.06395000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3520</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>48.37403</v>
+        <v>48.23154</v>
       </c>
       <c r="W30" t="n">
-        <v>-65.44089</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>46.26265</v>
+        <v>48.09296</v>
       </c>
       <c r="W31" t="n">
-        <v>-71.21769</v>
+        <v>-66.78681</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Sond. DDH-20-2023</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Iron, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>46.26532</v>
+        <v>46.36809</v>
       </c>
       <c r="W32" t="n">
-        <v>-71.28788</v>
+        <v>-73.97731</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac du Crapet</t>
+          <t>Lac Retty - Lac Bleu</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 29.00 g/t, Pb 0.212%</t>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>52.20175</v>
+        <v>55.22879</v>
       </c>
       <c r="W33" t="n">
-        <v>-70.89798</v>
+        <v>-66.12246</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4968</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ouf</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Silver</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Cu 11.8%, Ag 204.00 g/t, Zn 8.7%, Pb 1.6%</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.90478</v>
+        <v>55.15269</v>
       </c>
       <c r="W34" t="n">
-        <v>-74.69878</v>
+        <v>-66.35399</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3841</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead, Gold</t>
+          <t>Nickel, Copper, Gold, Platinum, Palladium, Egp, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>45.43447</v>
+        <v>55.23261</v>
       </c>
       <c r="W35" t="n">
-        <v>-70.9088</v>
+        <v>-66.16073</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Lac Beaupré-Est</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 5.3%, Ni 0.88%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>45.43568</v>
+        <v>49.59836</v>
       </c>
       <c r="W36" t="n">
-        <v>-70.91788</v>
+        <v>-76.92194000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,12 +3310,12 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Silver</t>
+          <t>Iron, Nickel, Copper</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>45.40513</v>
+        <v>49.63941</v>
       </c>
       <c r="W37" t="n">
-        <v>-70.9376</v>
+        <v>-76.90893</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Qalluviartuuq-NW</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3439,14 +3439,14 @@
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>45.44349</v>
+        <v>59.80634</v>
       </c>
       <c r="W38" t="n">
-        <v>-70.91244</v>
+        <v>-75.01831</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Zone Nicholson (Puits Racicot)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Gold, Silver</t>
+          <t>Gold, Lead, Cadmium, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>45.45582</v>
+        <v>45.29835</v>
       </c>
       <c r="W39" t="n">
-        <v>-70.90786</v>
+        <v>-72.31643</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAP Nord (Camp A-1)</t>
+          <t>St-Nazaire</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Copper, Tungsten</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
+          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>60.2779</v>
+        <v>48.70382</v>
       </c>
       <c r="W40" t="n">
-        <v>-75.33311</v>
+        <v>-78.25041</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Arsène</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 31.13 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>45.03676</v>
+        <v>55.2524</v>
       </c>
       <c r="W41" t="n">
-        <v>-72.77243</v>
+        <v>-67.95193</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
         </is>
       </c>
     </row>
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Franelle</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Cu 60%, Ag 43.49 g/t</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3751,14 +3751,14 @@
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>46.265</v>
+        <v>55.55824</v>
       </c>
       <c r="W42" t="n">
-        <v>-71.21259999999999</v>
+        <v>-67.34804</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glencoe</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 4.28%, Ag 3.00 g/t</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>46.27176</v>
+        <v>45.32873</v>
       </c>
       <c r="W43" t="n">
-        <v>-71.28612</v>
+        <v>-72.47421</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
         </is>
       </c>
     </row>
@@ -3846,22 +3846,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>Lachance #2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Lead, Molybdenum, Zinc, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3898,23 +3898,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U44" t="n">
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>52.03235</v>
+        <v>45.99171</v>
       </c>
       <c r="W44" t="n">
-        <v>-69.13816</v>
+        <v>-71.70617</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>Petit Lac Brompton</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Nickel, Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T45" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>48.173</v>
+        <v>45.44828</v>
       </c>
       <c r="W45" t="n">
-        <v>-78.14212999999999</v>
+        <v>-72.1057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Delhi Pacific</t>
+          <t>Claims Paradis</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Cu 7.36%, Ag 24.90 g/t</t>
+          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4054,803 +4054,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T46" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U46" t="n">
         <v>55</v>
       </c>
       <c r="V46" t="n">
-        <v>56.40258</v>
+        <v>48.57696</v>
       </c>
       <c r="W46" t="n">
-        <v>-67.9023</v>
+        <v>-78.14164</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4639</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Lac Dunphy</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Cu 18.2%, Ag 40.00 g/t, Au 0.17 g/t</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="n">
-        <v>13</v>
-      </c>
-      <c r="T47" t="n">
-        <v>325</v>
-      </c>
-      <c r="U47" t="n">
-        <v>55</v>
-      </c>
-      <c r="V47" t="n">
-        <v>56.05097</v>
-      </c>
-      <c r="W47" t="n">
-        <v>-67.71257</v>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4634</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Baleine Rouge Au-Zn-Pb</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Lead, Gold, Zinc</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="n">
-        <v>13</v>
-      </c>
-      <c r="T48" t="n">
-        <v>325</v>
-      </c>
-      <c r="U48" t="n">
-        <v>55</v>
-      </c>
-      <c r="V48" t="n">
-        <v>55.23561</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-67.9516</v>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Lac Walsh-Ouest</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="n">
-        <v>13</v>
-      </c>
-      <c r="T49" t="n">
-        <v>325</v>
-      </c>
-      <c r="U49" t="n">
-        <v>55</v>
-      </c>
-      <c r="V49" t="n">
-        <v>55.15269</v>
-      </c>
-      <c r="W49" t="n">
-        <v>-66.35399</v>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Cavalier</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Gold, Beryllium</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Au 4.44 g/t</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="n">
-        <v>13</v>
-      </c>
-      <c r="T50" t="n">
-        <v>325</v>
-      </c>
-      <c r="U50" t="n">
-        <v>55</v>
-      </c>
-      <c r="V50" t="n">
-        <v>52.03237</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-75.13809999999999</v>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=9288</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Goshawk</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Gold, Zinc, Copper, Lead, Silver</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 16.90 g/t, Cu 1.53%, Zn 3.55%, Ag 20.20 g/t, Pb 0.7%</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>13</v>
-      </c>
-      <c r="T51" t="n">
-        <v>325</v>
-      </c>
-      <c r="U51" t="n">
-        <v>55</v>
-      </c>
-      <c r="V51" t="n">
-        <v>61.56992</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-75.20258</v>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4509</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Rochelom</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Gold, Silver, Lead</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Au 782.00 g/t, Ag 145.20 g/t</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="n">
-        <v>250</v>
-      </c>
-      <c r="U52" t="n">
-        <v>55</v>
-      </c>
-      <c r="V52" t="n">
-        <v>49.77064</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-76.01858</v>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4504</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Lac Rivon-Ouest</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Gold, Molybdenum, Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Cu 11.7%, Mo 3%, Au 3.93 g/t, Ag 215.46 g/t, Zn 1.21%</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="n">
-        <v>13</v>
-      </c>
-      <c r="T53" t="n">
-        <v>325</v>
-      </c>
-      <c r="U53" t="n">
-        <v>55</v>
-      </c>
-      <c r="V53" t="n">
-        <v>51.72313</v>
-      </c>
-      <c r="W53" t="n">
-        <v>-72.79697</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4562</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Gold Fields</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Au 19.04 g/t</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>13</v>
-      </c>
-      <c r="T54" t="n">
-        <v>325</v>
-      </c>
-      <c r="U54" t="n">
-        <v>55</v>
-      </c>
-      <c r="V54" t="n">
-        <v>49.09287</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-78.42254</v>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4044</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>D-91-01 (Option Dejour)</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Au 4.35 g/t, Ag 6.90 g/t</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="n">
-        <v>12</v>
-      </c>
-      <c r="T55" t="n">
-        <v>300</v>
-      </c>
-      <c r="U55" t="n">
-        <v>55</v>
-      </c>
-      <c r="V55" t="n">
-        <v>49.02527</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-78.38705</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4045</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Lidge</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver, Arsenic</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>13</v>
-      </c>
-      <c r="T56" t="n">
-        <v>325</v>
-      </c>
-      <c r="U56" t="n">
-        <v>55</v>
-      </c>
-      <c r="V56" t="n">
-        <v>52.21818</v>
-      </c>
-      <c r="W56" t="n">
-        <v>-77.45902</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Croix-3</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>49.05483</v>
+        <v>49.84595</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.39637999999999</v>
+        <v>-70.57626</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -726,22 +726,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Golden Butterfly</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Gold, Silver, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>46.265</v>
+        <v>51.99697</v>
       </c>
       <c r="W4" t="n">
-        <v>-71.21259999999999</v>
+        <v>-75.22655</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Barre de fer</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>46.27176</v>
+        <v>51.6436</v>
       </c>
       <c r="W5" t="n">
-        <v>-71.28612</v>
+        <v>-67.33749</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Hunt (Port Daniel No. 2)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 9.35%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>46.26109</v>
+        <v>48.31932</v>
       </c>
       <c r="W6" t="n">
-        <v>-71.22866</v>
+        <v>-64.9713</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Rivière Pontois</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Copper, Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1012,23 +1012,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U7" t="n">
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>46.26532</v>
+        <v>53.51426</v>
       </c>
       <c r="W7" t="n">
-        <v>-71.28788</v>
+        <v>-74.51608</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>46.26265</v>
+        <v>49.83681</v>
       </c>
       <c r="W8" t="n">
-        <v>-71.21769</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>45.03676</v>
+        <v>49.82919</v>
       </c>
       <c r="W9" t="n">
-        <v>-72.77243</v>
+        <v>-70.58076</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lac Fecteau Est</t>
+          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t</t>
+          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>49.03096</v>
+        <v>58.23464</v>
       </c>
       <c r="W10" t="n">
-        <v>-75.24721</v>
+        <v>-69.92364000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Principal (Zone Olga)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>48.31932</v>
+        <v>49.78784</v>
       </c>
       <c r="W11" t="n">
-        <v>-64.9713</v>
+        <v>-77.08529</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Ruisseau Basket</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>Cu 14.2%, Ag 8.57 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>51.6436</v>
+        <v>48.09296</v>
       </c>
       <c r="W12" t="n">
-        <v>-67.33749</v>
+        <v>-66.78681</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Filon Baker (Lac Arseneault)</t>
+          <t>Big Dragon</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1438,12 +1438,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 48.00 g/t, Ag 197.10 g/t, Zn 3.5%, Pb 6.6%, Cu 0.105%</t>
+          <t>Au 6.57 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>48.37895</v>
+        <v>48.23154</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.22886</v>
+        <v>-66.80576000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1159</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frontier South</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Egp, Copper, Nickel, Platinum, Palladium, Iron</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ni 5.31%, Pd 5.54 g/t, Pt 1.55 g/t, EGP 0.000709%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>61.35434</v>
+        <v>48.37403</v>
       </c>
       <c r="W14" t="n">
-        <v>-76.05906</v>
+        <v>-65.44089</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1040</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sond. Umex 132</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 4%, Zn 6%</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>49.79699</v>
+        <v>45.45582</v>
       </c>
       <c r="W15" t="n">
-        <v>-75.81529</v>
+        <v>-70.90786</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3668</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>45.42257</v>
+        <v>45.40513</v>
       </c>
       <c r="W16" t="n">
-        <v>-70.92541</v>
+        <v>-70.9376</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.40513</v>
+        <v>45.42257</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.9376</v>
+        <v>-70.92541</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Cedar Rapids-Zone Village</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Au 302.00 g/t, Cu 5.5%, Ag 21.10 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U19" t="n">
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>45.45582</v>
+        <v>49.01186</v>
       </c>
       <c r="W19" t="n">
-        <v>-70.90786</v>
+        <v>-77.06395000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3520</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.44349</v>
+        <v>45.43568</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.91244</v>
+        <v>-70.91788</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,12 +2062,12 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2104,23 +2104,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>48.33048</v>
+        <v>45.43447</v>
       </c>
       <c r="W21" t="n">
-        <v>-67.01985999999999</v>
+        <v>-70.9088</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dussault</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Manganese</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 44.6%, Ag 70.80 g/t, Mn 2.96%, Zn 0.0674%</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2182,23 +2182,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>46.00535</v>
+        <v>45.44349</v>
       </c>
       <c r="W22" t="n">
-        <v>-71.70357</v>
+        <v>-70.91244</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3614</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Swarm Hill</t>
+          <t>Croix-3</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Gold, Zinc</t>
+          <t>Gold, Silver, Copper, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 4.13%, Au 1.05 g/t, Ni 0.32%, Zn 0.42%</t>
+          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>61.51392</v>
+        <v>49.05483</v>
       </c>
       <c r="W23" t="n">
-        <v>-76.44999</v>
+        <v>-75.39637999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1032</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lac Chassé-Est</t>
+          <t>Lac Fecteau Est</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Iron, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cu 6.82%, Au 0.35 g/t, Zn 0.877%, Ag 12.00 g/t, Fe 48.3%</t>
+          <t>Au 8.80 g/t</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>61.62679</v>
+        <v>49.03096</v>
       </c>
       <c r="W24" t="n">
-        <v>-76.35439</v>
+        <v>-75.24721</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1031</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>49.78784</v>
+        <v>45.03676</v>
       </c>
       <c r="W25" t="n">
-        <v>-77.08529</v>
+        <v>-72.77243</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -2442,22 +2442,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>OR79</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 3.74 g/t</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>48.37403</v>
+        <v>49.7697</v>
       </c>
       <c r="W26" t="n">
-        <v>-65.44089</v>
+        <v>-76.03744</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=53722</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Lidge</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Silver, Copper, Gold, Arsenic</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>45.43447</v>
+        <v>52.21818</v>
       </c>
       <c r="W27" t="n">
-        <v>-70.9088</v>
+        <v>-77.45902</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>45.43568</v>
+        <v>46.26109</v>
       </c>
       <c r="W28" t="n">
-        <v>-70.91788</v>
+        <v>-71.22866</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cedar Rapids-Zone Village</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 302.00 g/t, Cu 5.5%, Ag 21.10 g/t</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2728,23 +2728,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T29" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U29" t="n">
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>49.01186</v>
+        <v>46.27176</v>
       </c>
       <c r="W29" t="n">
-        <v>-77.06395000000001</v>
+        <v>-71.28612</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3520</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>48.23154</v>
+        <v>46.265</v>
       </c>
       <c r="W30" t="n">
-        <v>-66.80576000000001</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>48.09296</v>
+        <v>46.26532</v>
       </c>
       <c r="W31" t="n">
-        <v>-66.78681</v>
+        <v>-71.28788</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sond. DDH-20-2023</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2920,12 +2920,12 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Iron, Copper, Nickel, Cobalt</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 2.84%, Ni 2.35%, Co 0.268%, Fe 46.7%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>46.36809</v>
+        <v>46.26265</v>
       </c>
       <c r="W32" t="n">
-        <v>-73.97731</v>
+        <v>-71.21769</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67317</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Bleu</t>
+          <t>Lac Retty - Lac Pogo</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Niobium</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
+          <t>Nickel, Copper, Gold, Platinum, Palladium, Egp, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
+          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,1028 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>55.22879</v>
+        <v>55.23261</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.12246</v>
+        <v>-66.16073</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Lac Walsh-Ouest</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Cu 3.05%, Ni 0.67%</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>13</v>
-      </c>
-      <c r="T34" t="n">
-        <v>325</v>
-      </c>
-      <c r="U34" t="n">
-        <v>55</v>
-      </c>
-      <c r="V34" t="n">
-        <v>55.15269</v>
-      </c>
-      <c r="W34" t="n">
-        <v>-66.35399</v>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Lac Retty - Lac Pogo</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Gold, Platinum, Palladium, Egp, Silver</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
-        <v>13</v>
-      </c>
-      <c r="T35" t="n">
-        <v>325</v>
-      </c>
-      <c r="U35" t="n">
-        <v>55</v>
-      </c>
-      <c r="V35" t="n">
-        <v>55.23261</v>
-      </c>
-      <c r="W35" t="n">
-        <v>-66.16073</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
           <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lac Beaupré-Est</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Cu 5.3%, Ni 0.88%</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>13</v>
-      </c>
-      <c r="T36" t="n">
-        <v>325</v>
-      </c>
-      <c r="U36" t="n">
-        <v>55</v>
-      </c>
-      <c r="V36" t="n">
-        <v>49.59836</v>
-      </c>
-      <c r="W36" t="n">
-        <v>-76.92194000000001</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1460</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Harrison</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Iron, Nickel, Copper</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Cu 7.32%, Ni 0.9%, Fe 42%</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>13</v>
-      </c>
-      <c r="T37" t="n">
-        <v>325</v>
-      </c>
-      <c r="U37" t="n">
-        <v>55</v>
-      </c>
-      <c r="V37" t="n">
-        <v>49.63941</v>
-      </c>
-      <c r="W37" t="n">
-        <v>-76.90893</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1458</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Qalluviartuuq-NW</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Gold, Arsenic, Tellurium, Tungsten, Cobalt, Silver, Copper</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Au 6.80 g/t, W 0.0386%, Cu 0.31%, Ag 19.45 g/t, Co 0.0445%</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>13</v>
-      </c>
-      <c r="T38" t="n">
-        <v>325</v>
-      </c>
-      <c r="U38" t="n">
-        <v>55</v>
-      </c>
-      <c r="V38" t="n">
-        <v>59.80634</v>
-      </c>
-      <c r="W38" t="n">
-        <v>-75.01831</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1482</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Zone Nicholson (Puits Racicot)</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Gold, Lead, Cadmium, Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Au 18.17 g/t, Zn 30.4%, Cu 0.47%, Ag 21.10 g/t, Pb 0.6%</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>13</v>
-      </c>
-      <c r="T39" t="n">
-        <v>325</v>
-      </c>
-      <c r="U39" t="n">
-        <v>55</v>
-      </c>
-      <c r="V39" t="n">
-        <v>45.29835</v>
-      </c>
-      <c r="W39" t="n">
-        <v>-72.31643</v>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2288</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>St-Nazaire</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Zinc</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Zinc, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Cu 3.3%, Zn 2.4%, Ag 23.27 g/t</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>13</v>
-      </c>
-      <c r="T40" t="n">
-        <v>325</v>
-      </c>
-      <c r="U40" t="n">
-        <v>55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>48.70382</v>
-      </c>
-      <c r="W40" t="n">
-        <v>-78.25041</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2229</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Arsène</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I41" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Au 31.13 g/t</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>13</v>
-      </c>
-      <c r="T41" t="n">
-        <v>325</v>
-      </c>
-      <c r="U41" t="n">
-        <v>55</v>
-      </c>
-      <c r="V41" t="n">
-        <v>55.2524</v>
-      </c>
-      <c r="W41" t="n">
-        <v>-67.95193</v>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1641</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Franelle</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Cu 60%, Ag 43.49 g/t</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>13</v>
-      </c>
-      <c r="T42" t="n">
-        <v>325</v>
-      </c>
-      <c r="U42" t="n">
-        <v>55</v>
-      </c>
-      <c r="V42" t="n">
-        <v>55.55824</v>
-      </c>
-      <c r="W42" t="n">
-        <v>-67.34804</v>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1628</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Glencoe</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Cu 4.28%, Ag 3.00 g/t</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="n">
-        <v>13</v>
-      </c>
-      <c r="T43" t="n">
-        <v>325</v>
-      </c>
-      <c r="U43" t="n">
-        <v>55</v>
-      </c>
-      <c r="V43" t="n">
-        <v>45.32873</v>
-      </c>
-      <c r="W43" t="n">
-        <v>-72.47421</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2281</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Lachance #2</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Copper, Lead, Molybdenum, Zinc, Silver</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Cu 2.45%, Mo 0.777%, Ag 41.20 g/t, Pb 2.64%, Zn 0.0319%</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="n">
-        <v>250</v>
-      </c>
-      <c r="U44" t="n">
-        <v>55</v>
-      </c>
-      <c r="V44" t="n">
-        <v>45.99171</v>
-      </c>
-      <c r="W44" t="n">
-        <v>-71.70617</v>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2266</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Petit Lac Brompton</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Cu 11.8%, Au 0.60 g/t, Ni 0.39%</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="n">
-        <v>9</v>
-      </c>
-      <c r="T45" t="n">
-        <v>225</v>
-      </c>
-      <c r="U45" t="n">
-        <v>55</v>
-      </c>
-      <c r="V45" t="n">
-        <v>45.44828</v>
-      </c>
-      <c r="W45" t="n">
-        <v>-72.1057</v>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2274</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Claims Paradis</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Gold, Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Au 2.07 g/t, Cu 1.41%, Ag 11.20 g/t</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="n">
-        <v>12</v>
-      </c>
-      <c r="T46" t="n">
-        <v>300</v>
-      </c>
-      <c r="U46" t="n">
-        <v>55</v>
-      </c>
-      <c r="V46" t="n">
-        <v>48.57696</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-78.14164</v>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2214</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Gold, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,12 +658,12 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -709,14 +709,14 @@
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>49.84595</v>
+        <v>53.48752</v>
       </c>
       <c r="W3" t="n">
-        <v>-70.57626</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Golden Butterfly</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,12 +736,12 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Iron</t>
+          <t>Nickel, Copper, Cobalt, Platinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 14.16 g/t, Ag 7.70 g/t, Fe 31.1%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,23 +778,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>51.99697</v>
+        <v>49.82919</v>
       </c>
       <c r="W4" t="n">
-        <v>-75.22655</v>
+        <v>-70.58076</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2866</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Barre de fer</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -814,12 +814,12 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu 3.24%, Ni 2.34%, Co 0.223%</t>
+          <t>Au 144.55 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>51.6436</v>
+        <v>53.52019</v>
       </c>
       <c r="W5" t="n">
-        <v>-67.33749</v>
+        <v>-75.40980999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2874</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hunt (Port Daniel No. 2)</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,12 +892,12 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu 9.35%</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>48.31932</v>
+        <v>53.43724</v>
       </c>
       <c r="W6" t="n">
-        <v>-64.9713</v>
+        <v>-75.04334</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2922</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rivière Pontois</t>
+          <t>Fenton-Ouest</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -970,12 +970,12 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Gold, Arsenic, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 19.34 g/t, Cu 2.25%, Ag 9.30 g/t, As 3.79%</t>
+          <t>Au 19.17 g/t, Cu 0.72%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1012,23 +1012,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>53.51426</v>
+        <v>49.53598</v>
       </c>
       <c r="W7" t="n">
-        <v>-74.51608</v>
+        <v>-75.42941</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=147</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22367</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Grizzly</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Au 5.18 g/t</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>49.83681</v>
+        <v>49.97591</v>
       </c>
       <c r="W8" t="n">
-        <v>-70.57877999999999</v>
+        <v>-75.32237000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22089</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Au 12.91 g/t</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>49.82919</v>
+        <v>53.51022</v>
       </c>
       <c r="W9" t="n">
-        <v>-70.58076</v>
+        <v>-75.46174000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prud'Homme No 2 - Zone B (Leslie No 1)</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,12 +1204,12 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Palladium, Egp, Cobalt</t>
+          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 3.36%, Ni 1.52%, Co 0.07%, Pd 0.26 g/t, EGP 2.6e-05%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>58.23464</v>
+        <v>49.83681</v>
       </c>
       <c r="W10" t="n">
-        <v>-69.92364000000001</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2637</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Principal (Zone Olga)</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Arsenic</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 405.20 g/t, Cu 3.83%, Ag 121.37 g/t</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>49.78784</v>
+        <v>49.84595</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.08529</v>
+        <v>-70.57626</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3435</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ruisseau Basket</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1360,12 +1360,12 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Cu 14.2%, Ag 8.57 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>48.09296</v>
+        <v>52.03235</v>
       </c>
       <c r="W12" t="n">
-        <v>-66.78681</v>
+        <v>-69.13816</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3454</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -1428,22 +1428,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Big Dragon</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver, Zinc, Gold, Lead</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 6.57 g/t</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>48.23154</v>
+        <v>48.37403</v>
       </c>
       <c r="W13" t="n">
-        <v>-66.80576000000001</v>
+        <v>-65.44089</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3458</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1516,12 +1516,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Silver, Copper, Gold, Lead</t>
+          <t>Copper, Silver, Uranium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>48.37403</v>
+        <v>46.265</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.44089</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Frontier South</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Lead, Zinc, Copper, Silver</t>
+          <t>Nickel, Copper, Egp, Palladium, Platinum, Iron</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Cu 10.8%, Ni 5.31%, Pd 5.54 g/t, Pt 1.55 g/t, EGP 0.000709%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>45.45582</v>
+        <v>61.35434</v>
       </c>
       <c r="W15" t="n">
-        <v>-70.90786</v>
+        <v>-76.05906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1040</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1672,12 +1672,12 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Copper, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>45.40513</v>
+        <v>48.33048</v>
       </c>
       <c r="W16" t="n">
-        <v>-70.9376</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Fraser (Zones 3, 4 &amp; 5)</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,17 +1750,17 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc, Copper</t>
+          <t>Gold, Silver, Lead, Zinc, Copper, Arsenic, Antimony, Mercury</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>45.42731</v>
+        <v>48.32289</v>
       </c>
       <c r="W17" t="n">
-        <v>-70.92610999999999</v>
+        <v>-67.05</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>Fort Chimo (Lac Plissé)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1828,12 +1828,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Copper, Zinc, Gold, Nickel, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>45.42257</v>
+        <v>58.12861</v>
       </c>
       <c r="W18" t="n">
-        <v>-70.92541</v>
+        <v>-69.55745</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cedar Rapids-Zone Village</t>
+          <t>Dessureault (Lac Rougemont)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 302.00 g/t, Cu 5.5%, Ag 21.10 g/t</t>
+          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1948,23 +1948,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>49.01186</v>
+        <v>58.02817</v>
       </c>
       <c r="W19" t="n">
-        <v>-77.06395000000001</v>
+        <v>-69.57268000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3520</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,17 +1984,17 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Lead, Silver</t>
+          <t>Copper, Zinc, Silver, Gold, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.43568</v>
+        <v>45.42731</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.91788</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Lead, Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>45.43447</v>
+        <v>45.40513</v>
       </c>
       <c r="W21" t="n">
-        <v>-70.9088</v>
+        <v>-70.9376</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Silver</t>
+          <t>Copper, Zinc, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>45.44349</v>
+        <v>45.43447</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.91244</v>
+        <v>-70.9088</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Croix-3</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc</t>
+          <t>Copper, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Au 4.60 g/t, Zn 0.53%, Cu 0.14%, Ag 5.15 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>49.05483</v>
+        <v>45.43568</v>
       </c>
       <c r="W23" t="n">
-        <v>-75.39637999999999</v>
+        <v>-70.91788</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3029</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lac Fecteau Est</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2296,12 +2296,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 8.80 g/t</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>49.03096</v>
+        <v>45.45582</v>
       </c>
       <c r="W24" t="n">
-        <v>-75.24721</v>
+        <v>-70.90786</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=3034</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>45.03676</v>
+        <v>45.44349</v>
       </c>
       <c r="W25" t="n">
-        <v>-72.77243</v>
+        <v>-70.91244</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OR79</t>
+          <t>46W</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Zinc, Arsenic</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 3.74 g/t</t>
+          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>49.7697</v>
+        <v>48.29961</v>
       </c>
       <c r="W26" t="n">
-        <v>-76.03744</v>
+        <v>-67.12675</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=53722</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lidge</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Silver, Copper, Gold, Arsenic</t>
+          <t>Copper, Zinc, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Au 11.42 g/t, Ag 653.00 g/t, Cu 1.3%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>52.21818</v>
+        <v>45.42257</v>
       </c>
       <c r="W27" t="n">
-        <v>-77.45902</v>
+        <v>-70.92541</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=158</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>46.26109</v>
+        <v>45.03676</v>
       </c>
       <c r="W28" t="n">
-        <v>-71.22866</v>
+        <v>-72.77243</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2686,12 +2686,12 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc</t>
+          <t>Copper, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>46.27176</v>
+        <v>46.26532</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.28612</v>
+        <v>-71.28788</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2754,22 +2754,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper, Uranium, Silver</t>
+          <t>Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>46.265</v>
+        <v>46.27176</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.21259999999999</v>
+        <v>-71.28612</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver</t>
+          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>46.26532</v>
+        <v>46.26109</v>
       </c>
       <c r="W31" t="n">
-        <v>-71.28788</v>
+        <v>-71.22866</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
+          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Retty - Lac Pogo</t>
+          <t>Lac Menarik</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Gold, Platinum, Palladium, Egp, Silver</t>
+          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu 2.62%, Au 1.98 g/t, Pd 5.64 g/t, Ni 0.464%, Pt 1.00 g/t</t>
+          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,1262 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>55.23261</v>
+        <v>53.39786</v>
       </c>
       <c r="W33" t="n">
-        <v>-66.16073</v>
+        <v>-77.30625000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1684</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lac Gasosabeekatch/Lac Ultra</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Palladium</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Palladium, Copper, Gold, Egp, Silver</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="n">
+        <v>325</v>
+      </c>
+      <c r="U34" t="n">
+        <v>55</v>
+      </c>
+      <c r="V34" t="n">
+        <v>53.34013</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-77.32316</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mistass</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nickel, Copper, Iron, Cobalt</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>13</v>
+      </c>
+      <c r="T35" t="n">
+        <v>325</v>
+      </c>
+      <c r="U35" t="n">
+        <v>55</v>
+      </c>
+      <c r="V35" t="n">
+        <v>49.24734</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-71.98866</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nickel, Palladium, Gold, Zinc, Silver, Copper, Lead, Cobalt, Egp</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>13</v>
+      </c>
+      <c r="T36" t="n">
+        <v>325</v>
+      </c>
+      <c r="U36" t="n">
+        <v>55</v>
+      </c>
+      <c r="V36" t="n">
+        <v>53.39996</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-77.33163999999999</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lartic Est</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Arsenic</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" t="n">
+        <v>175</v>
+      </c>
+      <c r="U37" t="n">
+        <v>55</v>
+      </c>
+      <c r="V37" t="n">
+        <v>48.173</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-78.14212999999999</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Twin</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Copper</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>175</v>
+      </c>
+      <c r="U38" t="n">
+        <v>55</v>
+      </c>
+      <c r="V38" t="n">
+        <v>48.32328</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-79.44637</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lac Barlow</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gold, Silver, Arsenic</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>13</v>
+      </c>
+      <c r="T39" t="n">
+        <v>325</v>
+      </c>
+      <c r="U39" t="n">
+        <v>55</v>
+      </c>
+      <c r="V39" t="n">
+        <v>49.94431</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-74.71456000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sond. SER-21-040</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Au 8.71 g/t</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>13</v>
+      </c>
+      <c r="T40" t="n">
+        <v>325</v>
+      </c>
+      <c r="U40" t="n">
+        <v>55</v>
+      </c>
+      <c r="V40" t="n">
+        <v>53.08409</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-77.20562</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Gold, Tungsten</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Au 29.25 g/t, W 0.122%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>13</v>
+      </c>
+      <c r="T41" t="n">
+        <v>325</v>
+      </c>
+      <c r="U41" t="n">
+        <v>55</v>
+      </c>
+      <c r="V41" t="n">
+        <v>52.64108</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-75.67010999999999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lac Yasinski-NE</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Gold, Copper, Silver</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>13</v>
+      </c>
+      <c r="T42" t="n">
+        <v>325</v>
+      </c>
+      <c r="U42" t="n">
+        <v>55</v>
+      </c>
+      <c r="V42" t="n">
+        <v>53.35887</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-77.31016</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mont Opémiska No 1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="n">
+        <v>325</v>
+      </c>
+      <c r="U43" t="n">
+        <v>55</v>
+      </c>
+      <c r="V43" t="n">
+        <v>49.95224</v>
+      </c>
+      <c r="W43" t="n">
+        <v>-74.8797</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sheillan</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Au 90.30 g/t</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>13</v>
+      </c>
+      <c r="T44" t="n">
+        <v>325</v>
+      </c>
+      <c r="U44" t="n">
+        <v>55</v>
+      </c>
+      <c r="V44" t="n">
+        <v>49.10861</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-76.22864</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AT-32-91</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Au 5.09 g/t</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" t="n">
+        <v>225</v>
+      </c>
+      <c r="U45" t="n">
+        <v>55</v>
+      </c>
+      <c r="V45" t="n">
+        <v>48.89509</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-78.79843</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H-1429-046</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Au 5.80 g/t, Cu 1%, Zn 0.25%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>13</v>
+      </c>
+      <c r="T46" t="n">
+        <v>325</v>
+      </c>
+      <c r="U46" t="n">
+        <v>55</v>
+      </c>
+      <c r="V46" t="n">
+        <v>50.85296</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-76.47398</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4226</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Transfiguration: Zone E3</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lead, Copper, Silver, Zinc, Gold</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cu 6.57%, Pb 9.62%, Ag 32.10 g/t, Zn 0.541%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>13</v>
+      </c>
+      <c r="T47" t="n">
+        <v>325</v>
+      </c>
+      <c r="U47" t="n">
+        <v>55</v>
+      </c>
+      <c r="V47" t="n">
+        <v>47.9394</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-68.76391</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4166</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Boulder Shear (Cuvier-Est)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gold, Zinc, Arsenic, Copper</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Au 20.97 g/t, Zn 3.89%, Cu 0.0856%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>12</v>
+      </c>
+      <c r="T48" t="n">
+        <v>300</v>
+      </c>
+      <c r="U48" t="n">
+        <v>55</v>
+      </c>
+      <c r="V48" t="n">
+        <v>49.9399</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-74.70344</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=95</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Baleine Rouge Au-Zn-Pb</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lead, Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Au 35.15 g/t, Pb 6.55%, Zn 1.47%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="n">
+        <v>325</v>
+      </c>
+      <c r="U49" t="n">
+        <v>55</v>
+      </c>
+      <c r="V49" t="n">
+        <v>55.23561</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-67.9516</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=17535</t>
         </is>
       </c>
     </row>

--- a/site/qc_leads.xlsx
+++ b/site/qc_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mine Eustis</t>
+          <t>Mine Géant Dormant</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -580,12 +580,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Gold, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.6 Mt</t>
+          <t>3.2 Mt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
+          <t>Au 32.94 g/t, Ag 11.80 g/t</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,23 +622,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U2" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="V2" t="n">
-        <v>45.3192</v>
+        <v>49.13127</v>
       </c>
       <c r="W2" t="n">
-        <v>-71.92023</v>
+        <v>-77.97206</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4515</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Galexis</t>
+          <t>Mine Eustis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -658,17 +658,17 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Zinc, Copper, Lead, Gold, Silver</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -679,12 +679,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>1.6 Mt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
+          <t>Cu 3%, Zn 2%, Ag 14.10 g/t</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -706,17 +706,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="V3" t="n">
-        <v>53.48752</v>
+        <v>45.3192</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.33392000000001</v>
+        <v>-71.92023</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4362</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MHY Ap (Gravi)</t>
+          <t>Sylvie</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -736,17 +736,17 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Cobalt, Platinum</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -762,7 +762,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
+          <t>Ni 3.88%, Cu 4.19%, Pd 1.54 g/t, Pt 0.52 g/t, EGP 0.000179%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,14 +787,14 @@
         <v>55</v>
       </c>
       <c r="V4" t="n">
-        <v>49.82919</v>
+        <v>61.39737</v>
       </c>
       <c r="W4" t="n">
-        <v>-70.58076</v>
+        <v>-74.97753</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23764</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Lac Nitakwin</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 144.55 g/t</t>
+          <t>Au 6.06 g/t</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -865,14 +865,14 @@
         <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>53.52019</v>
+        <v>52.1766</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.40980999999999</v>
+        <v>-76.71138999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23457</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tommy</t>
+          <t>Timtu</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -892,17 +892,17 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Platinum, Palladium, Egp, Copper, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -918,7 +918,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 14.57 g/t</t>
+          <t>Ni 3.65%, Cu 3.45%, Pd 6.66 g/t, Pt 2.43 g/t, EGP 0.000909%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -943,14 +943,14 @@
         <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>53.43724</v>
+        <v>61.43006</v>
       </c>
       <c r="W6" t="n">
-        <v>-75.04334</v>
+        <v>-74.84983</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23795</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fenton-Ouest</t>
+          <t>36E</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 19.17 g/t, Cu 0.72%</t>
+          <t>Au 17.18 g/t, As 1%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1021,14 +1021,14 @@
         <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>49.53598</v>
+        <v>48.33048</v>
       </c>
       <c r="W7" t="n">
-        <v>-75.42941</v>
+        <v>-67.01985999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22367</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grizzly</t>
+          <t>Frontier South</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1048,12 +1048,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium, Iron</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 5.18 g/t</t>
+          <t>Cu 10.8%, Ni 5.31%, Pd 5.54 g/t, Pt 1.55 g/t, EGP 0.000709%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1099,14 +1099,14 @@
         <v>55</v>
       </c>
       <c r="V8" t="n">
-        <v>49.97591</v>
+        <v>61.35434</v>
       </c>
       <c r="W8" t="n">
-        <v>-75.32237000000001</v>
+        <v>-76.05906</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1040</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Swarm Hill</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1126,12 +1126,12 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel, Gold, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 12.91 g/t</t>
+          <t>Cu 4.13%, Au 1.05 g/t, Ni 0.32%, Zn 0.42%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1177,14 +1177,14 @@
         <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>53.51022</v>
+        <v>61.51392</v>
       </c>
       <c r="W9" t="n">
-        <v>-75.46174000000001</v>
+        <v>-76.44999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21591</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1032</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MHY Nord</t>
+          <t>Mystery</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1204,17 +1204,17 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Cobalt, Platinum, Nickel, Palladium, Egp</t>
+          <t>Platinum, Palladium, Egp, Copper, Nickel, Cobalt, Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
+          <t>Ni 3.01%, Cu 2.28%, Pd 5.00 g/t, Pt 1.75 g/t, EGP 0.000663%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1255,14 +1255,14 @@
         <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>49.83681</v>
+        <v>61.39368</v>
       </c>
       <c r="W10" t="n">
-        <v>-70.57877999999999</v>
+        <v>-75.1713</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24711</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MHY B (97-C340)</t>
+          <t>Lac Chassé-Est</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1282,12 +1282,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt</t>
+          <t>Zinc, Copper, Iron, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
+          <t>Cu 6.82%, Au 0.35 g/t, Zn 0.877%, Ag 12.00 g/t, Fe 48.3%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1333,14 +1333,14 @@
         <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>49.84595</v>
+        <v>61.62679</v>
       </c>
       <c r="W11" t="n">
-        <v>-70.57626</v>
+        <v>-76.35439</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1031</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AC-2010-006</t>
+          <t>46W</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic, Zinc, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Au 4.44 g/t</t>
+          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1411,14 +1411,14 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>52.03235</v>
+        <v>48.29961</v>
       </c>
       <c r="W12" t="n">
-        <v>-69.13816</v>
+        <v>-67.12675</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
         </is>
       </c>
     </row>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reboul : Zone Nord-Est</t>
+          <t>Lavallée : Zone 39</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold, Lead</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
+          <t>Au 14.75 g/t, Cu 0.83%, Ag 10.40 g/t</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>48.37403</v>
+        <v>47.37551</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.44089</v>
+        <v>-78.97857</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2360</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mine Harvey Hill : Tunnel Europa</t>
+          <t>Lavallée Sud</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver, Uranium</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
+          <t>Au 4.50 g/t, Cu 0.398%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1567,14 +1567,14 @@
         <v>55</v>
       </c>
       <c r="V14" t="n">
-        <v>46.265</v>
+        <v>47.35591</v>
       </c>
       <c r="W14" t="n">
-        <v>-71.21259999999999</v>
+        <v>-78.9842</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2359</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frontier South</t>
+          <t>MHY B (97-C340)</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1594,12 +1594,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Egp, Palladium, Platinum, Iron</t>
+          <t>Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ni 5.31%, Pd 5.54 g/t, Pt 1.55 g/t, EGP 0.000709%</t>
+          <t>Cu 2.57%, Ni 1.18%, Co 0.15%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1645,14 +1645,14 @@
         <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>61.35434</v>
+        <v>49.84595</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.05906</v>
+        <v>-70.57626</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1040</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1329</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36E</t>
+          <t>Tommy</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Au 17.18 g/t, As 1%</t>
+          <t>Au 14.57 g/t</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1723,14 +1723,14 @@
         <v>55</v>
       </c>
       <c r="V16" t="n">
-        <v>48.33048</v>
+        <v>53.43724</v>
       </c>
       <c r="W16" t="n">
-        <v>-67.01985999999999</v>
+        <v>-75.04334</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1082</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22226</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fraser (Zones 3, 4 &amp; 5)</t>
+          <t>MHY Nord</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1750,12 +1750,12 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper, Arsenic, Antimony, Mercury</t>
+          <t>Platinum, Cobalt, Copper, Nickel, Palladium, Egp</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
+          <t>Cu 4.34%, Co 0.564%, Ni 1.2%, Pt 0.84 g/t, Pd 0.11 g/t</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1801,14 +1801,14 @@
         <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>48.32289</v>
+        <v>49.83681</v>
       </c>
       <c r="W17" t="n">
-        <v>-67.05</v>
+        <v>-70.57877999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1336</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fort Chimo (Lac Plissé)</t>
+          <t>MHY Ap (Gravi)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Nickel, Silver</t>
+          <t>Copper, Nickel, Platinum, Cobalt</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Au 5.76 g/t, Cu 5.2%, Zn 2.1%, Ag 26.05 g/t, Ni 0.27%</t>
+          <t>Cu 5.57%, Ni 1.15%, Co 0.15%, Pt 0.15 g/t</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1879,14 +1879,14 @@
         <v>55</v>
       </c>
       <c r="V18" t="n">
-        <v>58.12861</v>
+        <v>49.82919</v>
       </c>
       <c r="W18" t="n">
-        <v>-69.55745</v>
+        <v>-70.58076</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2642</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1337</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dessureault (Lac Rougemont)</t>
+          <t>Galexis</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1906,12 +1906,12 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Au 31.80 g/t, Ag 54.00 g/t</t>
+          <t>Au 4.90 g/t, Cu 2.02%, Ag 2.80 g/t</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1957,14 +1957,14 @@
         <v>55</v>
       </c>
       <c r="V19" t="n">
-        <v>58.02817</v>
+        <v>53.48752</v>
       </c>
       <c r="W19" t="n">
-        <v>-69.57268000000001</v>
+        <v>-75.33392000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=2649</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=22466</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mine Clinton O</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1984,17 +1984,17 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Gold, Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>122 kt</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
+          <t>Au 144.55 g/t</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2035,14 +2035,14 @@
         <v>55</v>
       </c>
       <c r="V20" t="n">
-        <v>45.42731</v>
+        <v>53.52019</v>
       </c>
       <c r="W20" t="n">
-        <v>-70.92610999999999</v>
+        <v>-75.40980999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=21885</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Clinton F</t>
+          <t>Getty</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2062,17 +2062,17 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lead, Copper, Zinc, Silver</t>
+          <t>Palladium, Egp, Copper, Nickel, Platinum, Gold, Cobalt</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
+          <t>Ni 3.41%, Cu 1.91%, Pd 1.36 g/t, Pt 0.42 g/t, EGP 0.000169%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2113,14 +2113,14 @@
         <v>55</v>
       </c>
       <c r="V21" t="n">
-        <v>45.40513</v>
+        <v>61.39535</v>
       </c>
       <c r="W21" t="n">
-        <v>-70.9376</v>
+        <v>-75.00066</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=24064</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Clinton V</t>
+          <t>Mustang</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2140,12 +2140,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
+          <t>Au 111.17 g/t, Ag 25.20 g/t</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2191,14 +2191,14 @@
         <v>55</v>
       </c>
       <c r="V22" t="n">
-        <v>45.43447</v>
+        <v>52.17024</v>
       </c>
       <c r="W22" t="n">
-        <v>-70.9088</v>
+        <v>-76.57532999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=23427</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clinton D</t>
+          <t>Foy</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2218,12 +2218,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver, Lead</t>
+          <t>Gold, Copper, Zinc, Chromium, Nickel, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
+          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2269,14 +2269,14 @@
         <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>45.43568</v>
+        <v>46.26109</v>
       </c>
       <c r="W23" t="n">
-        <v>-70.91788</v>
+        <v>-71.22866</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clinton A</t>
+          <t>Nutbrown</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead, Gold, Silver</t>
+          <t>Copper, Molybdenum, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
+          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2347,14 +2347,14 @@
         <v>55</v>
       </c>
       <c r="V24" t="n">
-        <v>45.45582</v>
+        <v>46.26265</v>
       </c>
       <c r="W24" t="n">
-        <v>-70.90786</v>
+        <v>-71.21769</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinton C</t>
+          <t>Grondin</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Copper, Gold, Zinc, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
+          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2425,14 +2425,14 @@
         <v>55</v>
       </c>
       <c r="V25" t="n">
-        <v>45.44349</v>
+        <v>46.26532</v>
       </c>
       <c r="W25" t="n">
-        <v>-70.91244</v>
+        <v>-71.28788</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
         </is>
       </c>
     </row>
@@ -2442,22 +2442,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>46W</t>
+          <t>Reboul : Zone Nord-Est</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver, Zinc, Arsenic</t>
+          <t>Zinc, Silver, Copper, Gold, Lead</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Au 54.90 g/t, Ag 6.40 g/t, As 1%, Zn 0.252%</t>
+          <t>Cu 3.3%, Ag 147.00 g/t, Au 0.70 g/t, Zn 1.08%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2503,14 +2503,14 @@
         <v>55</v>
       </c>
       <c r="V26" t="n">
-        <v>48.29961</v>
+        <v>48.37403</v>
       </c>
       <c r="W26" t="n">
-        <v>-67.12675</v>
+        <v>-65.44089</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1084</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1167</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clinton E</t>
+          <t>AC-2010-006</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2530,12 +2530,12 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
+          <t>Au 4.44 g/t</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2581,14 +2581,14 @@
         <v>55</v>
       </c>
       <c r="V27" t="n">
-        <v>45.42257</v>
+        <v>52.03235</v>
       </c>
       <c r="W27" t="n">
-        <v>-70.92541</v>
+        <v>-69.13816</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=28774</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abbott Corners  (Frelisghburg Copper)</t>
+          <t>Sandpit</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2608,12 +2608,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu 4.1%, Ag 18.00 g/t</t>
+          <t>Au 18.05 g/t, As 0.158%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2659,14 +2659,14 @@
         <v>55</v>
       </c>
       <c r="V28" t="n">
-        <v>45.03676</v>
+        <v>52.17253</v>
       </c>
       <c r="W28" t="n">
-        <v>-72.77243</v>
+        <v>-76.55762</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=26698</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grondin</t>
+          <t>Abbott Corners  (Frelisghburg Copper)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Silver, Zinc, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cu 2.3%, Au 0.75 g/t, Ag 22.00 g/t, Zn 0.5%</t>
+          <t>Cu 4.1%, Ag 18.00 g/t</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2737,14 +2737,14 @@
         <v>55</v>
       </c>
       <c r="V29" t="n">
-        <v>46.26532</v>
+        <v>45.03676</v>
       </c>
       <c r="W29" t="n">
-        <v>-71.28788</v>
+        <v>-72.77243</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1208</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1269</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Gamache A</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2764,12 +2764,12 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zinc, Copper, Gold</t>
+          <t>Egp, Copper, Nickel, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
+          <t>Cu 6.33%, Ni 0.69%, Pd 2.55 g/t, Pt 0.65 g/t, EGP 0.000313%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2815,14 +2815,14 @@
         <v>55</v>
       </c>
       <c r="V30" t="n">
-        <v>46.27176</v>
+        <v>61.55073</v>
       </c>
       <c r="W30" t="n">
-        <v>-71.28612</v>
+        <v>-72.66555</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=25568</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Foy</t>
+          <t>PAP Nord (Camp A-1)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Nickel, Chromium</t>
+          <t>Copper, Zinc, Silver, Gold, Tungsten</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu 10.1%, Au 3.16 g/t, Ni 0.2%, Ag 11.60 g/t, Cr 0.32%</t>
+          <t>Au 31.70 g/t, W 0.87%, Ag 78.90 g/t, Cu 0.748%, Zn 0.908%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2893,14 +2893,14 @@
         <v>55</v>
       </c>
       <c r="V31" t="n">
-        <v>46.26109</v>
+        <v>60.2779</v>
       </c>
       <c r="W31" t="n">
-        <v>-71.22866</v>
+        <v>-75.33311</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1211</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=27048</t>
         </is>
       </c>
     </row>
@@ -2910,11 +2910,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nutbrown</t>
+          <t>Mine Harvey Hill : Tunnel Europa</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Molybdenum, Silver</t>
+          <t>Copper, Uranium, Silver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu 10.8%, Ag 36.20 g/t, Au 0.34 g/t, Mo 0.04%, Zn 0.0846%</t>
+          <t>Cu 12%, Ag 35.30 g/t, U 0.011%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2971,14 +2971,14 @@
         <v>55</v>
       </c>
       <c r="V32" t="n">
-        <v>46.26265</v>
+        <v>46.265</v>
       </c>
       <c r="W32" t="n">
-        <v>-71.21769</v>
+        <v>-71.21259999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1210</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1220</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lac Menarik</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2998,12 +2998,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rh, Chromium, Egp, Nickel, Gold, Palladium, Platinum, Copper</t>
+          <t>Gold, Copper, Zinc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Au 6.00 g/t, Pd 2.90 g/t, Ni 0.292%, Pt 0.68 g/t, Cr 28.9%</t>
+          <t>Au 4.80 g/t, Zn 7.55%, Cu 0.55%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,14 +3049,14 @@
         <v>55</v>
       </c>
       <c r="V33" t="n">
-        <v>53.39786</v>
+        <v>46.27176</v>
       </c>
       <c r="W33" t="n">
-        <v>-77.30625000000001</v>
+        <v>-71.28612</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5993</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1217</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lac Gasosabeekatch/Lac Ultra</t>
+          <t>Clinton C</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3076,12 +3076,12 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Palladium, Copper, Gold, Egp, Silver</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Au 7.33 g/t, Cu 6.5%, Ag 38.00 g/t, Pd 1.00 g/t, EGP 0.0001%</t>
+          <t>Cu 4.6%, Zn 2.1%, Ag 7.20 g/t</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3127,14 +3127,14 @@
         <v>55</v>
       </c>
       <c r="V34" t="n">
-        <v>53.34013</v>
+        <v>45.44349</v>
       </c>
       <c r="W34" t="n">
-        <v>-77.32316</v>
+        <v>-70.91244</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5991</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1089</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mistass</t>
+          <t>Clinton A</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3154,12 +3154,12 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Iron, Cobalt</t>
+          <t>Gold, Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Cu 5.6%, Ni 0.995%, Fe 31.4%</t>
+          <t>Au 8.24 g/t, Cu 6.63%, Zn 17.1%, Ag 44.20 g/t, Pb 0.53%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3205,14 +3205,14 @@
         <v>55</v>
       </c>
       <c r="V35" t="n">
-        <v>49.24734</v>
+        <v>45.45582</v>
       </c>
       <c r="W35" t="n">
-        <v>-71.98866</v>
+        <v>-70.90786</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5965</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1090</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Yasinski (Lac Beaver) : Lac Beaver</t>
+          <t>Clinton F</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3232,12 +3232,12 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nickel, Palladium, Gold, Zinc, Silver, Copper, Lead, Cobalt, Egp</t>
+          <t>Lead, Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 2.27%, Au 1.71 g/t, Ni 1.12%, Zn 3.74%, Ag 53.83 g/t</t>
+          <t>Cu 8.7%, Zn 9.4%, Ag 26.10 g/t, Pb 0.54%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>55</v>
       </c>
       <c r="V36" t="n">
-        <v>53.39996</v>
+        <v>45.40513</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.33163999999999</v>
+        <v>-70.9376</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5990</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1094</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lartic Est</t>
+          <t>Mine Clinton O</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3310,17 +3310,17 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Lead, Gold, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>no tonnage on record</t>
+          <t>122 kt</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Au 13.70 g/t, Ag 4.80 g/t</t>
+          <t>Cu 16.9%, Zn 12.3%, Ag 113.90 g/t, Au 1.22 g/t, Pb 4.53%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3352,23 +3352,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>55</v>
       </c>
       <c r="V37" t="n">
-        <v>48.173</v>
+        <v>45.42731</v>
       </c>
       <c r="W37" t="n">
-        <v>-78.14212999999999</v>
+        <v>-70.92610999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1767</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1095</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Clinton V</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3388,12 +3388,12 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
+          <t>Cu 3%, Ag 168.00 g/t, Zn 2%, Pb 0.672%, Au 0.28 g/t</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3430,23 +3430,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
         <v>55</v>
       </c>
       <c r="V38" t="n">
-        <v>48.32328</v>
+        <v>45.43447</v>
       </c>
       <c r="W38" t="n">
-        <v>-79.44637</v>
+        <v>-70.9088</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1106</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lac Barlow</t>
+          <t>Fraser (Zones 3, 4 &amp; 5)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3466,12 +3466,12 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Zinc, Lead, Silver, Gold, Mercury, Antimony, Arsenic</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Au 3.70 g/t, Ag 1.00 g/t</t>
+          <t>Au 32.01 g/t, Ag 319.30 g/t, Pb 19.6%, Zn 6.2%, Cu 1.1%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3517,14 +3517,14 @@
         <v>55</v>
       </c>
       <c r="V39" t="n">
-        <v>49.94431</v>
+        <v>48.32289</v>
       </c>
       <c r="W39" t="n">
-        <v>-74.71456000000001</v>
+        <v>-67.05</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=90</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1080</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sond. SER-21-040</t>
+          <t>Clinton D</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -3544,12 +3544,12 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Au 8.71 g/t</t>
+          <t>Cu 9.6%, Zn 1.88%, Ag 17.70 g/t, Pb 0.25%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3595,14 +3595,14 @@
         <v>55</v>
       </c>
       <c r="V40" t="n">
-        <v>53.08409</v>
+        <v>45.43568</v>
       </c>
       <c r="W40" t="n">
-        <v>-77.20562</v>
+        <v>-70.91788</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67301</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1105</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Clinton E</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3622,12 +3622,12 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Tungsten</t>
+          <t>Zinc, Copper, Silver</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 29.25 g/t, W 0.122%</t>
+          <t>Cu 3.2%, Zn 2.8%, Ag 20.57 g/t</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3673,14 +3673,14 @@
         <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>52.64108</v>
+        <v>45.42257</v>
       </c>
       <c r="W41" t="n">
-        <v>-75.67010999999999</v>
+        <v>-70.92541</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=7</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1096</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lac Yasinski-NE</t>
+          <t>Twin</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3700,12 +3700,12 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Au 12.40 g/t, Cu 6.5%, Ag 38.90 g/t</t>
+          <t>Au 1715.00 g/t, Ag 392.00 g/t, Cu 0.32%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3742,23 +3742,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U42" t="n">
         <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>53.35887</v>
+        <v>48.32328</v>
       </c>
       <c r="W42" t="n">
-        <v>-77.31016</v>
+        <v>-79.44637</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5994</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=5930</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mont Opémiska No 1</t>
+          <t>Lac Retty - Lac Bleu</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3778,12 +3778,12 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Niobium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Niobium, Platinum, Palladium, Egp, Copper, Nickel, Cobalt</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Cu 3.6%, Zn 5.85%, Au 1.54 g/t, Ag 11.70 g/t, Pb 0.233%</t>
+          <t>Cu 5%, Pd 4.40 g/t, Ni 0.75%, Pt 0.80 g/t, EGP 0.000519%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3829,14 +3829,14 @@
         <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>49.95224</v>
+        <v>55.22879</v>
       </c>
       <c r="W43" t="n">
-        <v>-74.8797</v>
+        <v>-66.12246</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=39</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1676</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sheillan</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Copper, Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Au 90.30 g/t</t>
+          <t>Au 69.78 g/t, Cu 0.281%, Ag 6.50 g/t</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3907,14 +3907,14 @@
         <v>55</v>
       </c>
       <c r="V44" t="n">
-        <v>49.10861</v>
+        <v>54.8722</v>
       </c>
       <c r="W44" t="n">
-        <v>-76.22864</v>
+        <v>-69.81637000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=67165</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=11036</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AT-32-91</t>
+          <t>Lac Walsh-Ouest</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3934,12 +3934,12 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel, Copper</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Au 5.09 g/t</t>
+          <t>Cu 3.05%, Ni 0.67%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3976,23 +3976,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U45" t="n">
         <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>48.89509</v>
+        <v>55.15269</v>
       </c>
       <c r="W45" t="n">
-        <v>-78.79843</v>
+        <v>-66.35399</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=4206</t>
+          <t>https://sigeom.mines.gouv.qc.ca/signet/classes/I1102_afchDetlLien?l=f&amp;entt=I0001_corpsMineralise&amp;noSeqnEntt=1678</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H-1429-046</t>
+          <t>Jedi Extension</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4012,12 +4012,12 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>